--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Deero DS Course\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Deero DS Course\Practical Excel Data Analytics Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Dashboard" sheetId="5" r:id="rId5"/>
     <sheet name="Findings" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clean_Data '!$A$1:$A$295</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2285" uniqueCount="313">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -962,6 +965,12 @@
   </si>
   <si>
     <t>CUS00097</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>CUS00190</t>
   </si>
 </sst>
 </file>
@@ -972,7 +981,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -985,8 +994,23 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -996,6 +1020,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
       </patternFill>
     </fill>
   </fills>
@@ -1008,21 +1037,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7938,15 +8004,6525 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="5" customFormat="1">
+      <c r="A1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45677</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1024.44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3">
+        <v>827.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46173</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3">
+        <v>661.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45954</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3">
+        <v>295.45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46006</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3">
+        <v>481.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1067.9000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45861</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3">
+        <v>444.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45902</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>911.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45970</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3">
+        <v>415.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1315.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45781</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3">
+        <v>176.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45807</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1075.0899999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45747</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="3">
+        <v>863.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="3">
+        <v>255.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3">
+        <v>719.42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1041.8399999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45937</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3">
+        <v>265.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45679</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2040.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45998</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1210.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45715</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="3">
+        <v>732.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45773</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="3">
+        <v>998.38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45731</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1023.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46068</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1170.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45691</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3">
+        <v>526.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46082</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3">
+        <v>558.07000000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45925</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="3">
+        <v>656.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="3">
+        <v>442.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31">
+        <v>53</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45884</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32">
+        <v>49</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1610.81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45809</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="3">
+        <v>706.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45881</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>36</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="3">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="B35" s="2">
+        <v>46038</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45671</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45691</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1086.56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1321.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="3">
+        <v>2015.04</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="B41" s="2">
+        <v>45982</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41">
+        <v>30</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1396.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45958</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="3">
+        <v>265.83999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43">
+        <v>40</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="3">
+        <v>644.95000000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46031</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44">
+        <v>57</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="3">
+        <v>128.41999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45846</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>62</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1032.69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46067</v>
+      </c>
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1164.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45824</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="3">
+        <v>453.51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45975</v>
+      </c>
+      <c r="D48">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="3">
+        <v>395.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46061</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="3">
+        <v>253.15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>59</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="3">
+        <v>239.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>45</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3">
+        <v>200.87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45729</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" s="3">
+        <v>963.66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45976</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>53</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="3">
+        <v>247.93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46103</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <v>64</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" t="s">
+        <v>30</v>
+      </c>
+      <c r="G54" s="3">
+        <v>727.81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="B55" s="2">
+        <v>45957</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55">
+        <v>68</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="3">
+        <v>947.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>55</v>
+      </c>
+      <c r="E56" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="3">
+        <v>325.43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45715</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57">
+        <v>34</v>
+      </c>
+      <c r="E57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="3">
+        <v>835.61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="B58" s="2">
+        <v>46222</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="3">
+        <v>586.78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45744</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59">
+        <v>39</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="3">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45884</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60">
+        <v>21</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1429.26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45822</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="3">
+        <v>870.42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45703</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1214.6199999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D63">
+        <v>26</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1045.8599999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45881</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64">
+        <v>25</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="3">
+        <v>665.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45772</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" s="3">
+        <v>930.93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45678</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>53</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>44</v>
+      </c>
+      <c r="G66" s="3">
+        <v>926.65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45742</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1984.53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="3">
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45665</v>
+      </c>
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69">
+        <v>66</v>
+      </c>
+      <c r="E69" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1964.48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45918</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70">
+        <v>40</v>
+      </c>
+      <c r="E70" t="s">
+        <v>39</v>
+      </c>
+      <c r="F70" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="3">
+        <v>677.55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="B71" s="2">
+        <v>46060</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71">
+        <v>23</v>
+      </c>
+      <c r="E71" t="s">
+        <v>39</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="3">
+        <v>528.86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46048</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72">
+        <v>47</v>
+      </c>
+      <c r="F72" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="3">
+        <v>728.06</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" s="2">
+        <v>45858</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73">
+        <v>64</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>44</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1421.07</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74">
+        <v>70</v>
+      </c>
+      <c r="E74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" t="s">
+        <v>30</v>
+      </c>
+      <c r="G74" s="3">
+        <v>1249.32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="2">
+        <v>45942</v>
+      </c>
+      <c r="D75">
+        <v>24</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" t="s">
+        <v>44</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1155.95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" s="2">
+        <v>45991</v>
+      </c>
+      <c r="C76" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76">
+        <v>41</v>
+      </c>
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="3">
+        <v>374.63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77">
+        <v>52</v>
+      </c>
+      <c r="E77" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" s="3">
+        <v>216.93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45771</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>38</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="3">
+        <v>680.77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45966</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1234.8800000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45828</v>
+      </c>
+      <c r="C80" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80">
+        <v>36</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="3">
+        <v>256.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>97</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>62</v>
+      </c>
+      <c r="E81" t="s">
+        <v>74</v>
+      </c>
+      <c r="F81" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="3">
+        <v>595.70000000000005</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45913</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82">
+        <v>62</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1156.93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45791</v>
+      </c>
+      <c r="C83" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="3">
+        <v>895.53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46001</v>
+      </c>
+      <c r="C84" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84">
+        <v>55</v>
+      </c>
+      <c r="E84" t="s">
+        <v>39</v>
+      </c>
+      <c r="F84" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1229.76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45998</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85">
+        <v>32</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1651.76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86">
+        <v>45</v>
+      </c>
+      <c r="E86" t="s">
+        <v>74</v>
+      </c>
+      <c r="F86" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="3">
+        <v>978.74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87">
+        <v>46</v>
+      </c>
+      <c r="E87" t="s">
+        <v>39</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="3">
+        <v>645.54999999999995</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>104</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88">
+        <v>62</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="3">
+        <v>881.22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89">
+        <v>63</v>
+      </c>
+      <c r="E89" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1127.6500000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>106</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46187</v>
+      </c>
+      <c r="C90" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>32</v>
+      </c>
+      <c r="E90" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="3">
+        <v>201.16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91">
+        <v>55</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="3">
+        <v>618.42999999999995</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92">
+        <v>48</v>
+      </c>
+      <c r="E92" t="s">
+        <v>74</v>
+      </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" s="3">
+        <v>759.9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>109</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45928</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93">
+        <v>61</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="3">
+        <v>667.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94">
+        <v>38</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="3">
+        <v>752.98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>111</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45673</v>
+      </c>
+      <c r="C95" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>43</v>
+      </c>
+      <c r="E95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="3">
+        <v>127.29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>112</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45968</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96">
+        <v>32</v>
+      </c>
+      <c r="E96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="3">
+        <v>790.7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" t="s">
+        <v>74</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="3">
+        <v>661.71</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98" s="2">
+        <v>45877</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98">
+        <v>29</v>
+      </c>
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="3"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" s="2">
+        <v>45874</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99">
+        <v>45</v>
+      </c>
+      <c r="E99" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="3">
+        <v>839.71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100">
+        <v>62</v>
+      </c>
+      <c r="E100" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" t="s">
+        <v>44</v>
+      </c>
+      <c r="G100" s="3">
+        <v>632.38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" s="2">
+        <v>45723</v>
+      </c>
+      <c r="D101">
+        <v>59</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="3">
+        <v>952.9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102" s="2">
+        <v>45951</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102">
+        <v>26</v>
+      </c>
+      <c r="E102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="3">
+        <v>896.23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103" s="2">
+        <v>45767</v>
+      </c>
+      <c r="C103" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103">
+        <v>37</v>
+      </c>
+      <c r="E103" t="s">
+        <v>74</v>
+      </c>
+      <c r="F103" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103" s="3">
+        <v>1470.86</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C104" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104">
+        <v>43</v>
+      </c>
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104" s="3">
+        <v>1377.65</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" s="2">
+        <v>45950</v>
+      </c>
+      <c r="C105" t="s">
+        <v>114</v>
+      </c>
+      <c r="D105">
+        <v>21</v>
+      </c>
+      <c r="E105" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" t="s">
+        <v>30</v>
+      </c>
+      <c r="G105" s="3">
+        <v>1996.92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46124</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106">
+        <v>24</v>
+      </c>
+      <c r="E106" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" t="s">
+        <v>44</v>
+      </c>
+      <c r="G106" s="3">
+        <v>1411.64</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107" s="2">
+        <v>45802</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107">
+        <v>38</v>
+      </c>
+      <c r="E107" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" t="s">
+        <v>44</v>
+      </c>
+      <c r="G107" s="3">
+        <v>836.33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>125</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108">
+        <v>55</v>
+      </c>
+      <c r="E108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="3">
+        <v>1021.22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109" s="2">
+        <v>45735</v>
+      </c>
+      <c r="C109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109">
+        <v>61</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" s="3">
+        <v>265.87</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110">
+        <v>43</v>
+      </c>
+      <c r="E110" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" s="3">
+        <v>169.21</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="2">
+        <v>45763</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111">
+        <v>65</v>
+      </c>
+      <c r="E111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="3">
+        <v>799.53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+      <c r="B112" s="2">
+        <v>45777</v>
+      </c>
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112">
+        <v>41</v>
+      </c>
+      <c r="F112" t="s">
+        <v>10</v>
+      </c>
+      <c r="G112" s="3">
+        <v>1081.02</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="B113" s="2">
+        <v>45908</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113">
+        <v>32</v>
+      </c>
+      <c r="E113" t="s">
+        <v>74</v>
+      </c>
+      <c r="F113" t="s">
+        <v>30</v>
+      </c>
+      <c r="G113" s="3">
+        <v>1614.28</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+      <c r="B114" s="2">
+        <v>45847</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114">
+        <v>42</v>
+      </c>
+      <c r="E114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="3">
+        <v>648.44000000000005</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>131</v>
+      </c>
+      <c r="B115" s="2">
+        <v>45846</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115">
+        <v>18</v>
+      </c>
+      <c r="E115" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" s="3">
+        <v>275.93</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>132</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46065</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116">
+        <v>22</v>
+      </c>
+      <c r="E116" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="3">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+      <c r="B117" s="2">
+        <v>45943</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117">
+        <v>123</v>
+      </c>
+      <c r="E117" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" t="s">
+        <v>44</v>
+      </c>
+      <c r="G117" s="3">
+        <v>796.52</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45681</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118">
+        <v>19</v>
+      </c>
+      <c r="E118" t="s">
+        <v>74</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="3">
+        <v>579.54999999999995</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>135</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45886</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119">
+        <v>60</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" t="s">
+        <v>21</v>
+      </c>
+      <c r="G119" s="3">
+        <v>712.55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="B120" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120">
+        <v>50</v>
+      </c>
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" t="s">
+        <v>21</v>
+      </c>
+      <c r="G120" s="3">
+        <v>917.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>136</v>
+      </c>
+      <c r="B121" s="2">
+        <v>45801</v>
+      </c>
+      <c r="C121" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121">
+        <v>21</v>
+      </c>
+      <c r="E121" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" t="s">
+        <v>44</v>
+      </c>
+      <c r="G121" s="3">
+        <v>890.48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>137</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122">
+        <v>61</v>
+      </c>
+      <c r="E122" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" s="3">
+        <v>294.94</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>138</v>
+      </c>
+      <c r="B123" s="2">
+        <v>45840</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" t="s">
+        <v>21</v>
+      </c>
+      <c r="G123" s="3">
+        <v>756.75</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>139</v>
+      </c>
+      <c r="B124" s="2">
+        <v>45820</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124">
+        <v>58</v>
+      </c>
+      <c r="E124" t="s">
+        <v>39</v>
+      </c>
+      <c r="F124" t="s">
+        <v>30</v>
+      </c>
+      <c r="G124" s="3">
+        <v>1316.09</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>140</v>
+      </c>
+      <c r="B125" s="2"/>
+      <c r="C125" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125">
+        <v>33</v>
+      </c>
+      <c r="E125" t="s">
+        <v>39</v>
+      </c>
+      <c r="F125" t="s">
+        <v>21</v>
+      </c>
+      <c r="G125" s="3">
+        <v>753.73</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>141</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46052</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126">
+        <v>49</v>
+      </c>
+      <c r="E126" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" t="s">
+        <v>21</v>
+      </c>
+      <c r="G126" s="3">
+        <v>527.12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>142</v>
+      </c>
+      <c r="B127" s="2">
+        <v>45706</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127">
+        <v>35</v>
+      </c>
+      <c r="E127" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" t="s">
+        <v>143</v>
+      </c>
+      <c r="G127" s="3">
+        <v>646.07000000000005</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" s="2">
+        <v>45827</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128">
+        <v>42</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="3">
+        <v>1155.3399999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>145</v>
+      </c>
+      <c r="B129" s="2">
+        <v>45983</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129">
+        <v>50</v>
+      </c>
+      <c r="E129" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" t="s">
+        <v>30</v>
+      </c>
+      <c r="G129" s="3"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>146</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46037</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130">
+        <v>21</v>
+      </c>
+      <c r="E130" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="3">
+        <v>845.86</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>147</v>
+      </c>
+      <c r="B131" s="2">
+        <v>45661</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131">
+        <v>46</v>
+      </c>
+      <c r="F131" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" s="3">
+        <v>1455.22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>148</v>
+      </c>
+      <c r="B132" s="2">
+        <v>45768</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132">
+        <v>39</v>
+      </c>
+      <c r="E132" t="s">
+        <v>39</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" s="3">
+        <v>120.06</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>149</v>
+      </c>
+      <c r="B133" s="2">
+        <v>45890</v>
+      </c>
+      <c r="C133" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133">
+        <v>60</v>
+      </c>
+      <c r="E133" t="s">
+        <v>150</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" s="3"/>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>151</v>
+      </c>
+      <c r="B134" s="2">
+        <v>45719</v>
+      </c>
+      <c r="C134" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134">
+        <v>46</v>
+      </c>
+      <c r="F134" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="3">
+        <v>675.77</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" s="2">
+        <v>45709</v>
+      </c>
+      <c r="C135" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" t="s">
+        <v>20</v>
+      </c>
+      <c r="F135" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="3">
+        <v>409.49</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B136" s="2">
+        <v>45763</v>
+      </c>
+      <c r="D136">
+        <v>41</v>
+      </c>
+      <c r="E136" t="s">
+        <v>20</v>
+      </c>
+      <c r="F136" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="3">
+        <v>10006</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>154</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46033</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137">
+        <v>70</v>
+      </c>
+      <c r="E137" t="s">
+        <v>20</v>
+      </c>
+      <c r="F137" t="s">
+        <v>30</v>
+      </c>
+      <c r="G137" s="3">
+        <v>1956.52</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" s="2">
+        <v>45812</v>
+      </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138">
+        <v>19</v>
+      </c>
+      <c r="E138" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" s="3"/>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139" s="2">
+        <v>45875</v>
+      </c>
+      <c r="C139" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139">
+        <v>59</v>
+      </c>
+      <c r="E139" t="s">
+        <v>20</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="3"/>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46026</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140">
+        <v>65</v>
+      </c>
+      <c r="F140" t="s">
+        <v>21</v>
+      </c>
+      <c r="G140" s="3">
+        <v>810.64</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46064</v>
+      </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141">
+        <v>30</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="3">
+        <v>855.02</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142" s="2">
+        <v>45938</v>
+      </c>
+      <c r="C142" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142">
+        <v>52</v>
+      </c>
+      <c r="E142" t="s">
+        <v>39</v>
+      </c>
+      <c r="F142" t="s">
+        <v>18</v>
+      </c>
+      <c r="G142" s="3">
+        <v>316.74</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" s="2"/>
+      <c r="C143" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143">
+        <v>31</v>
+      </c>
+      <c r="E143" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" t="s">
+        <v>30</v>
+      </c>
+      <c r="G143" s="3">
+        <v>1961.76</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>161</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46173</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144">
+        <v>34</v>
+      </c>
+      <c r="E144" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" t="s">
+        <v>44</v>
+      </c>
+      <c r="G144" s="3">
+        <v>1390.38</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B145" s="2">
+        <v>45752</v>
+      </c>
+      <c r="C145" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" t="s">
+        <v>39</v>
+      </c>
+      <c r="F145" t="s">
+        <v>30</v>
+      </c>
+      <c r="G145" s="3">
+        <v>1852.82</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="2">
+        <v>45931</v>
+      </c>
+      <c r="C146" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146">
+        <v>68</v>
+      </c>
+      <c r="E146" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="3">
+        <v>843.99</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="B147" s="2"/>
+      <c r="C147" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147">
+        <v>50</v>
+      </c>
+      <c r="E147" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" t="s">
+        <v>30</v>
+      </c>
+      <c r="G147" s="3">
+        <v>1828.2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>164</v>
+      </c>
+      <c r="B148" s="2">
+        <v>45864</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148">
+        <v>60</v>
+      </c>
+      <c r="E148" t="s">
+        <v>15</v>
+      </c>
+      <c r="F148" t="s">
+        <v>30</v>
+      </c>
+      <c r="G148" s="3">
+        <v>785.37</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>165</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46020</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149">
+        <v>70</v>
+      </c>
+      <c r="E149" t="s">
+        <v>20</v>
+      </c>
+      <c r="F149" t="s">
+        <v>30</v>
+      </c>
+      <c r="G149" s="3">
+        <v>924.95</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" s="2">
+        <v>45771</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" t="s">
+        <v>74</v>
+      </c>
+      <c r="F150" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="3">
+        <v>758.44</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>167</v>
+      </c>
+      <c r="B151" s="2">
+        <v>45982</v>
+      </c>
+      <c r="C151" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151">
+        <v>35</v>
+      </c>
+      <c r="E151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" t="s">
+        <v>30</v>
+      </c>
+      <c r="G151" s="3">
+        <v>1086.6400000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>168</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46000</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152">
+        <v>43</v>
+      </c>
+      <c r="E152" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" t="s">
+        <v>44</v>
+      </c>
+      <c r="G152" s="3">
+        <v>624.91999999999996</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>169</v>
+      </c>
+      <c r="B153" s="2">
+        <v>45676</v>
+      </c>
+      <c r="C153" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" t="s">
+        <v>30</v>
+      </c>
+      <c r="G153" s="3">
+        <v>1015.92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>170</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46081</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154">
+        <v>62</v>
+      </c>
+      <c r="E154" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" s="3">
+        <v>1371.98</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>171</v>
+      </c>
+      <c r="B155" s="2">
+        <v>45680</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155">
+        <v>28</v>
+      </c>
+      <c r="E155" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="3">
+        <v>836.87</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>172</v>
+      </c>
+      <c r="B156" s="2">
+        <v>45892</v>
+      </c>
+      <c r="C156" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156" t="s">
+        <v>30</v>
+      </c>
+      <c r="G156" s="3">
+        <v>895.93</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>173</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46157</v>
+      </c>
+      <c r="D157">
+        <v>65</v>
+      </c>
+      <c r="E157" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" t="s">
+        <v>30</v>
+      </c>
+      <c r="G157" s="3">
+        <v>1137.32</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>174</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46041</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158">
+        <v>28</v>
+      </c>
+      <c r="E158" t="s">
+        <v>54</v>
+      </c>
+      <c r="F158" t="s">
+        <v>21</v>
+      </c>
+      <c r="G158" s="3">
+        <v>785.95</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>175</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46230</v>
+      </c>
+      <c r="D159">
+        <v>70</v>
+      </c>
+      <c r="E159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="3">
+        <v>1087.08</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>176</v>
+      </c>
+      <c r="B160" s="2">
+        <v>45839</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="3">
+        <v>648.57000000000005</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>177</v>
+      </c>
+      <c r="B161" s="2">
+        <v>45873</v>
+      </c>
+      <c r="C161" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161">
+        <v>52</v>
+      </c>
+      <c r="E161" t="s">
+        <v>39</v>
+      </c>
+      <c r="F161" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="3">
+        <v>1064.4100000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="B162" s="2">
+        <v>45878</v>
+      </c>
+      <c r="C162" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162">
+        <v>53</v>
+      </c>
+      <c r="E162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" t="s">
+        <v>21</v>
+      </c>
+      <c r="G162" s="3">
+        <v>944.96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46059</v>
+      </c>
+      <c r="C163" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163">
+        <v>36</v>
+      </c>
+      <c r="E163" t="s">
+        <v>15</v>
+      </c>
+      <c r="F163" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="3">
+        <v>508.34</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>179</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164">
+        <v>52</v>
+      </c>
+      <c r="E164" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" s="3">
+        <v>934.22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>180</v>
+      </c>
+      <c r="B165" s="2">
+        <v>45795</v>
+      </c>
+      <c r="C165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165">
+        <v>26</v>
+      </c>
+      <c r="E165" t="s">
+        <v>39</v>
+      </c>
+      <c r="F165" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" s="3">
+        <v>267.12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>181</v>
+      </c>
+      <c r="B166" s="2">
+        <v>45879</v>
+      </c>
+      <c r="C166" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166">
+        <v>42</v>
+      </c>
+      <c r="E166" t="s">
+        <v>15</v>
+      </c>
+      <c r="F166" t="s">
+        <v>30</v>
+      </c>
+      <c r="G166" s="3">
+        <v>1672.71</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>182</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167">
+        <v>29</v>
+      </c>
+      <c r="E167" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="3">
+        <v>794.1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>183</v>
+      </c>
+      <c r="B168" s="2">
+        <v>45868</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168">
+        <v>59</v>
+      </c>
+      <c r="E168" t="s">
+        <v>15</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="3">
+        <v>856.56</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>184</v>
+      </c>
+      <c r="B169" s="2">
+        <v>45731</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169">
+        <v>66</v>
+      </c>
+      <c r="E169" t="s">
+        <v>15</v>
+      </c>
+      <c r="F169" t="s">
+        <v>21</v>
+      </c>
+      <c r="G169" s="3">
+        <v>457.6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>185</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46017</v>
+      </c>
+      <c r="C170" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170">
+        <v>60</v>
+      </c>
+      <c r="E170" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" t="s">
+        <v>18</v>
+      </c>
+      <c r="G170" s="3">
+        <v>175.19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>186</v>
+      </c>
+      <c r="B171" s="2">
+        <v>45753</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171">
+        <v>48</v>
+      </c>
+      <c r="E171" t="s">
+        <v>74</v>
+      </c>
+      <c r="F171" t="s">
+        <v>23</v>
+      </c>
+      <c r="G171" s="3">
+        <v>746.26</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>187</v>
+      </c>
+      <c r="B172" s="2">
+        <v>45850</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172">
+        <v>55</v>
+      </c>
+      <c r="E172" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" t="s">
+        <v>30</v>
+      </c>
+      <c r="G172" s="3">
+        <v>1137.1600000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>188</v>
+      </c>
+      <c r="B173" s="2">
+        <v>45871</v>
+      </c>
+      <c r="C173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173">
+        <v>30</v>
+      </c>
+      <c r="E173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" s="3">
+        <v>167.65</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>189</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C174" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>31</v>
+      </c>
+      <c r="E174" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="3">
+        <v>638.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>190</v>
+      </c>
+      <c r="B175" s="2">
+        <v>45696</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175">
+        <v>62</v>
+      </c>
+      <c r="E175" t="s">
+        <v>15</v>
+      </c>
+      <c r="F175" t="s">
+        <v>18</v>
+      </c>
+      <c r="G175" s="3">
+        <v>210.96</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>191</v>
+      </c>
+      <c r="B176" s="2">
+        <v>45857</v>
+      </c>
+      <c r="C176" t="s">
+        <v>192</v>
+      </c>
+      <c r="D176">
+        <v>28</v>
+      </c>
+      <c r="E176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" t="s">
+        <v>18</v>
+      </c>
+      <c r="G176" s="3">
+        <v>152.91999999999999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>193</v>
+      </c>
+      <c r="B177" s="2">
+        <v>45896</v>
+      </c>
+      <c r="C177" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177">
+        <v>26</v>
+      </c>
+      <c r="E177" t="s">
+        <v>20</v>
+      </c>
+      <c r="F177" t="s">
+        <v>44</v>
+      </c>
+      <c r="G177" s="3">
+        <v>1481.76</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>194</v>
+      </c>
+      <c r="B178" s="2"/>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178">
+        <v>33</v>
+      </c>
+      <c r="E178" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" t="s">
+        <v>195</v>
+      </c>
+      <c r="G178" s="3">
+        <v>964.35</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>196</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C179" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179">
+        <v>69</v>
+      </c>
+      <c r="E179" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="3">
+        <v>1244.97</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>197</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180">
+        <v>18</v>
+      </c>
+      <c r="E180" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" t="s">
+        <v>30</v>
+      </c>
+      <c r="G180" s="3">
+        <v>721.99</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>198</v>
+      </c>
+      <c r="B181" s="2">
+        <v>45932</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181">
+        <v>33</v>
+      </c>
+      <c r="E181" t="s">
+        <v>74</v>
+      </c>
+      <c r="F181" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="3">
+        <v>1332.38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>199</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45930</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182">
+        <v>66</v>
+      </c>
+      <c r="E182" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" t="s">
+        <v>30</v>
+      </c>
+      <c r="G182" s="3">
+        <v>969.34</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>200</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45804</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183">
+        <v>65</v>
+      </c>
+      <c r="E183" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" t="s">
+        <v>44</v>
+      </c>
+      <c r="G183" s="3">
+        <v>790.75</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>201</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45899</v>
+      </c>
+      <c r="C184" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184">
+        <v>67</v>
+      </c>
+      <c r="E184" t="s">
+        <v>39</v>
+      </c>
+      <c r="F184" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="3">
+        <v>828.77</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>202</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45720</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185">
+        <v>37</v>
+      </c>
+      <c r="E185" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" t="s">
+        <v>30</v>
+      </c>
+      <c r="G185" s="3">
+        <v>1800.86</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="B186" s="2">
+        <v>45945</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186">
+        <v>41</v>
+      </c>
+      <c r="E186" t="s">
+        <v>20</v>
+      </c>
+      <c r="F186" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="3">
+        <v>1200.17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>203</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45780</v>
+      </c>
+      <c r="C187" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187">
+        <v>67</v>
+      </c>
+      <c r="E187" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" t="s">
+        <v>23</v>
+      </c>
+      <c r="G187" s="3"/>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>204</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46021</v>
+      </c>
+      <c r="C188" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" t="s">
+        <v>74</v>
+      </c>
+      <c r="F188" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="3">
+        <v>853.76</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="B189" s="2">
+        <v>45728</v>
+      </c>
+      <c r="C189" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189">
+        <v>21</v>
+      </c>
+      <c r="E189" t="s">
+        <v>39</v>
+      </c>
+      <c r="F189" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="3">
+        <v>1144.9100000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>205</v>
+      </c>
+      <c r="B190" s="2">
+        <v>45845</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190">
+        <v>56</v>
+      </c>
+      <c r="E190" t="s">
+        <v>39</v>
+      </c>
+      <c r="F190" t="s">
+        <v>30</v>
+      </c>
+      <c r="G190" s="3">
+        <v>660.22</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>206</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45805</v>
+      </c>
+      <c r="C191" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191">
+        <v>41</v>
+      </c>
+      <c r="E191" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="3">
+        <v>868.55</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>207</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45665</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192">
+        <v>40</v>
+      </c>
+      <c r="E192" t="s">
+        <v>20</v>
+      </c>
+      <c r="F192" t="s">
+        <v>23</v>
+      </c>
+      <c r="G192" s="3">
+        <v>789.1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>208</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46019</v>
+      </c>
+      <c r="C193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193">
+        <v>38</v>
+      </c>
+      <c r="E193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" t="s">
+        <v>21</v>
+      </c>
+      <c r="G193" s="3">
+        <v>748.35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>209</v>
+      </c>
+      <c r="B194" s="2">
+        <v>45998</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194">
+        <v>37</v>
+      </c>
+      <c r="E194" t="s">
+        <v>74</v>
+      </c>
+      <c r="F194" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="3">
+        <v>853.86</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>210</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46073</v>
+      </c>
+      <c r="C195" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195">
+        <v>30</v>
+      </c>
+      <c r="E195" t="s">
+        <v>20</v>
+      </c>
+      <c r="F195" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="3">
+        <v>1315.27</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>211</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46014</v>
+      </c>
+      <c r="C196" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196">
+        <v>55</v>
+      </c>
+      <c r="E196" t="s">
+        <v>15</v>
+      </c>
+      <c r="F196" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="3">
+        <v>775.19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>212</v>
+      </c>
+      <c r="B197" s="2">
+        <v>45734</v>
+      </c>
+      <c r="C197" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197">
+        <v>32</v>
+      </c>
+      <c r="E197" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" t="s">
+        <v>23</v>
+      </c>
+      <c r="G197" s="3">
+        <v>707.01</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>213</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C198" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198">
+        <v>65</v>
+      </c>
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="3">
+        <v>742.69</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>214</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46014</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199">
+        <v>60</v>
+      </c>
+      <c r="E199" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" t="s">
+        <v>44</v>
+      </c>
+      <c r="G199" s="3">
+        <v>599.34</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>215</v>
+      </c>
+      <c r="B200" s="2">
+        <v>45984</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200">
+        <v>39</v>
+      </c>
+      <c r="E200" t="s">
+        <v>39</v>
+      </c>
+      <c r="F200" t="s">
+        <v>44</v>
+      </c>
+      <c r="G200" s="3">
+        <v>797.52</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>216</v>
+      </c>
+      <c r="B201" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201">
+        <v>51</v>
+      </c>
+      <c r="E201" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" t="s">
+        <v>30</v>
+      </c>
+      <c r="G201" s="3">
+        <v>1547.72</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>217</v>
+      </c>
+      <c r="B202" s="2">
+        <v>45694</v>
+      </c>
+      <c r="C202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202">
+        <v>20</v>
+      </c>
+      <c r="E202" t="s">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>23</v>
+      </c>
+      <c r="G202" s="3"/>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>218</v>
+      </c>
+      <c r="B203" s="2">
+        <v>45848</v>
+      </c>
+      <c r="C203" t="s">
+        <v>8</v>
+      </c>
+      <c r="D203">
+        <v>18</v>
+      </c>
+      <c r="E203" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203" t="s">
+        <v>18</v>
+      </c>
+      <c r="G203" s="3">
+        <v>108.23</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>219</v>
+      </c>
+      <c r="B204" s="2">
+        <v>45833</v>
+      </c>
+      <c r="C204" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204">
+        <v>28</v>
+      </c>
+      <c r="E204" t="s">
+        <v>74</v>
+      </c>
+      <c r="F204" t="s">
+        <v>13</v>
+      </c>
+      <c r="G204" s="3">
+        <v>919.61</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>220</v>
+      </c>
+      <c r="B205" s="2">
+        <v>45765</v>
+      </c>
+      <c r="C205" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" t="s">
+        <v>54</v>
+      </c>
+      <c r="E205" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" t="s">
+        <v>21</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>221</v>
+      </c>
+      <c r="B206" s="2">
+        <v>45932</v>
+      </c>
+      <c r="C206" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206">
+        <v>54</v>
+      </c>
+      <c r="E206" t="s">
+        <v>39</v>
+      </c>
+      <c r="F206" t="s">
+        <v>23</v>
+      </c>
+      <c r="G206" s="3">
+        <v>1108.6199999999999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>222</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46060</v>
+      </c>
+      <c r="D207">
+        <v>33</v>
+      </c>
+      <c r="E207" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" t="s">
+        <v>23</v>
+      </c>
+      <c r="G207" s="3">
+        <v>930.02</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>223</v>
+      </c>
+      <c r="B208" s="2"/>
+      <c r="C208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208">
+        <v>55</v>
+      </c>
+      <c r="E208" t="s">
+        <v>39</v>
+      </c>
+      <c r="F208" t="s">
+        <v>44</v>
+      </c>
+      <c r="G208" s="3">
+        <v>1603.75</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>224</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46014</v>
+      </c>
+      <c r="C209" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209">
+        <v>46</v>
+      </c>
+      <c r="F209" t="s">
+        <v>30</v>
+      </c>
+      <c r="G209" s="3">
+        <v>1509.47</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>225</v>
+      </c>
+      <c r="B210" s="2">
+        <v>45821</v>
+      </c>
+      <c r="C210" t="s">
+        <v>226</v>
+      </c>
+      <c r="D210">
+        <v>48</v>
+      </c>
+      <c r="E210" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" t="s">
+        <v>13</v>
+      </c>
+      <c r="G210" s="3">
+        <v>921.62</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" t="s">
+        <v>227</v>
+      </c>
+      <c r="B211" s="2"/>
+      <c r="C211" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211">
+        <v>57</v>
+      </c>
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="3">
+        <v>502.04</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>228</v>
+      </c>
+      <c r="B212" s="2">
+        <v>45749</v>
+      </c>
+      <c r="C212" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212">
+        <v>42</v>
+      </c>
+      <c r="E212" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" t="s">
+        <v>30</v>
+      </c>
+      <c r="G212" s="3">
+        <v>1091.0999999999999</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" t="s">
+        <v>229</v>
+      </c>
+      <c r="B213" s="2">
+        <v>45925</v>
+      </c>
+      <c r="C213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213">
+        <v>58</v>
+      </c>
+      <c r="E213" t="s">
+        <v>9</v>
+      </c>
+      <c r="F213" t="s">
+        <v>30</v>
+      </c>
+      <c r="G213" s="3">
+        <v>1013.28</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>230</v>
+      </c>
+      <c r="B214" s="2">
+        <v>45960</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214">
+        <v>30</v>
+      </c>
+      <c r="E214" t="s">
+        <v>15</v>
+      </c>
+      <c r="F214" t="s">
+        <v>21</v>
+      </c>
+      <c r="G214" s="3">
+        <v>728.45</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>231</v>
+      </c>
+      <c r="B215" s="2">
+        <v>45830</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215">
+        <v>67</v>
+      </c>
+      <c r="E215" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
+        <v>44</v>
+      </c>
+      <c r="G215" s="3"/>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>232</v>
+      </c>
+      <c r="B216" s="2">
+        <v>45832</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216">
+        <v>39</v>
+      </c>
+      <c r="E216" t="s">
+        <v>39</v>
+      </c>
+      <c r="G216" s="3">
+        <v>838.84</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" t="s">
+        <v>233</v>
+      </c>
+      <c r="B217" s="2">
+        <v>45919</v>
+      </c>
+      <c r="C217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217">
+        <v>19</v>
+      </c>
+      <c r="E217" t="s">
+        <v>15</v>
+      </c>
+      <c r="F217" t="s">
+        <v>23</v>
+      </c>
+      <c r="G217" s="3">
+        <v>916.62</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>234</v>
+      </c>
+      <c r="B218" s="2">
+        <v>45682</v>
+      </c>
+      <c r="C218" t="s">
+        <v>17</v>
+      </c>
+      <c r="D218">
+        <v>63</v>
+      </c>
+      <c r="E218" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="3">
+        <v>954.9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" t="s">
+        <v>235</v>
+      </c>
+      <c r="B219" s="2">
+        <v>45792</v>
+      </c>
+      <c r="C219" t="s">
+        <v>8</v>
+      </c>
+      <c r="D219">
+        <v>33</v>
+      </c>
+      <c r="E219" t="s">
+        <v>9</v>
+      </c>
+      <c r="G219" s="3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" t="s">
+        <v>236</v>
+      </c>
+      <c r="B220" s="2">
+        <v>45900</v>
+      </c>
+      <c r="C220" t="s">
+        <v>17</v>
+      </c>
+      <c r="D220">
+        <v>22</v>
+      </c>
+      <c r="E220" t="s">
+        <v>15</v>
+      </c>
+      <c r="G220" s="3">
+        <v>721.11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" t="s">
+        <v>237</v>
+      </c>
+      <c r="B221" s="2">
+        <v>45875</v>
+      </c>
+      <c r="C221" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221">
+        <v>48</v>
+      </c>
+      <c r="E221" t="s">
+        <v>15</v>
+      </c>
+      <c r="F221" t="s">
+        <v>195</v>
+      </c>
+      <c r="G221" s="3"/>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" t="s">
+        <v>238</v>
+      </c>
+      <c r="B222" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C222" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222">
+        <v>32</v>
+      </c>
+      <c r="E222" t="s">
+        <v>74</v>
+      </c>
+      <c r="F222" t="s">
+        <v>30</v>
+      </c>
+      <c r="G222" s="3">
+        <v>2091.58</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" t="s">
+        <v>239</v>
+      </c>
+      <c r="B223" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C223" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223">
+        <v>53</v>
+      </c>
+      <c r="E223" t="s">
+        <v>15</v>
+      </c>
+      <c r="F223" t="s">
+        <v>30</v>
+      </c>
+      <c r="G223" s="3">
+        <v>901.36</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" t="s">
+        <v>240</v>
+      </c>
+      <c r="B224" s="2">
+        <v>45893</v>
+      </c>
+      <c r="C224" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224">
+        <v>39</v>
+      </c>
+      <c r="E224" t="s">
+        <v>15</v>
+      </c>
+      <c r="F224" t="s">
+        <v>44</v>
+      </c>
+      <c r="G224" s="3">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" t="s">
+        <v>241</v>
+      </c>
+      <c r="B225" s="2">
+        <v>45884</v>
+      </c>
+      <c r="C225" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225">
+        <v>59</v>
+      </c>
+      <c r="E225" t="s">
+        <v>15</v>
+      </c>
+      <c r="F225" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" s="3">
+        <v>508.66</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" t="s">
+        <v>242</v>
+      </c>
+      <c r="B226" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C226" t="s">
+        <v>17</v>
+      </c>
+      <c r="D226">
+        <v>43</v>
+      </c>
+      <c r="E226" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" t="s">
+        <v>13</v>
+      </c>
+      <c r="G226" s="3">
+        <v>778.23</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="B227" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C227" t="s">
+        <v>17</v>
+      </c>
+      <c r="D227">
+        <v>61</v>
+      </c>
+      <c r="E227" t="s">
+        <v>15</v>
+      </c>
+      <c r="F227" t="s">
+        <v>18</v>
+      </c>
+      <c r="G227" s="3">
+        <v>176.82</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" t="s">
+        <v>243</v>
+      </c>
+      <c r="B228" s="2">
+        <v>45895</v>
+      </c>
+      <c r="C228" t="s">
+        <v>17</v>
+      </c>
+      <c r="D228">
+        <v>61</v>
+      </c>
+      <c r="E228" t="s">
+        <v>9</v>
+      </c>
+      <c r="F228" t="s">
+        <v>13</v>
+      </c>
+      <c r="G228" s="3"/>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" t="s">
+        <v>244</v>
+      </c>
+      <c r="B229" s="2">
+        <v>45874</v>
+      </c>
+      <c r="C229" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229">
+        <v>52</v>
+      </c>
+      <c r="E229" t="s">
+        <v>12</v>
+      </c>
+      <c r="G229" s="3">
+        <v>481.21</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" t="s">
+        <v>245</v>
+      </c>
+      <c r="B230" s="2">
+        <v>45771</v>
+      </c>
+      <c r="C230" t="s">
+        <v>8</v>
+      </c>
+      <c r="D230">
+        <v>47</v>
+      </c>
+      <c r="E230" t="s">
+        <v>39</v>
+      </c>
+      <c r="F230" t="s">
+        <v>18</v>
+      </c>
+      <c r="G230" s="3">
+        <v>129.81</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" t="s">
+        <v>246</v>
+      </c>
+      <c r="B231" s="2">
+        <v>45778</v>
+      </c>
+      <c r="C231" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231">
+        <v>55</v>
+      </c>
+      <c r="F231" t="s">
+        <v>44</v>
+      </c>
+      <c r="G231" s="3">
+        <v>1436.28</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="B232" s="2">
+        <v>45773</v>
+      </c>
+      <c r="C232" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232">
+        <v>38</v>
+      </c>
+      <c r="E232" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232" s="3">
+        <v>920.19</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
+        <v>247</v>
+      </c>
+      <c r="B233" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C233" t="s">
+        <v>17</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>21</v>
+      </c>
+      <c r="G233" s="3">
+        <v>727.06</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" t="s">
+        <v>248</v>
+      </c>
+      <c r="B234" s="2">
+        <v>46037</v>
+      </c>
+      <c r="C234" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234">
+        <v>63</v>
+      </c>
+      <c r="E234" t="s">
+        <v>74</v>
+      </c>
+      <c r="F234" t="s">
+        <v>249</v>
+      </c>
+      <c r="G234" s="3">
+        <v>306.45999999999998</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" t="s">
+        <v>250</v>
+      </c>
+      <c r="B235" s="2">
+        <v>45876</v>
+      </c>
+      <c r="C235" t="s">
+        <v>8</v>
+      </c>
+      <c r="D235">
+        <v>50</v>
+      </c>
+      <c r="E235" t="s">
+        <v>39</v>
+      </c>
+      <c r="F235" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" s="3">
+        <v>818.19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" t="s">
+        <v>251</v>
+      </c>
+      <c r="B236" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C236" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236">
+        <v>42</v>
+      </c>
+      <c r="E236" t="s">
+        <v>20</v>
+      </c>
+      <c r="F236" t="s">
+        <v>30</v>
+      </c>
+      <c r="G236" s="3"/>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" t="s">
+        <v>252</v>
+      </c>
+      <c r="B237" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C237" t="s">
+        <v>17</v>
+      </c>
+      <c r="D237">
+        <v>36</v>
+      </c>
+      <c r="E237" t="s">
+        <v>15</v>
+      </c>
+      <c r="G237" s="3">
+        <v>216.82</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="B238" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C238" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238">
+        <v>63</v>
+      </c>
+      <c r="E238" t="s">
+        <v>15</v>
+      </c>
+      <c r="F238" t="s">
+        <v>18</v>
+      </c>
+      <c r="G238" s="3">
+        <v>268.75</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>253</v>
+      </c>
+      <c r="B239" s="2">
+        <v>45776</v>
+      </c>
+      <c r="C239" t="s">
+        <v>17</v>
+      </c>
+      <c r="D239">
+        <v>43</v>
+      </c>
+      <c r="E239" t="s">
+        <v>39</v>
+      </c>
+      <c r="F239" t="s">
+        <v>44</v>
+      </c>
+      <c r="G239" s="3">
+        <v>781.63</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>254</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45758</v>
+      </c>
+      <c r="D240">
+        <v>40</v>
+      </c>
+      <c r="E240" t="s">
+        <v>39</v>
+      </c>
+      <c r="F240" t="s">
+        <v>23</v>
+      </c>
+      <c r="G240" s="3">
+        <v>641.59</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>255</v>
+      </c>
+      <c r="B241" s="2">
+        <v>45670</v>
+      </c>
+      <c r="C241" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241">
+        <v>19</v>
+      </c>
+      <c r="E241" t="s">
+        <v>39</v>
+      </c>
+      <c r="F241" t="s">
+        <v>256</v>
+      </c>
+      <c r="G241" s="3">
+        <v>278.61</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>257</v>
+      </c>
+      <c r="B242" s="2">
+        <v>45744</v>
+      </c>
+      <c r="C242" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242">
+        <v>20</v>
+      </c>
+      <c r="E242" t="s">
+        <v>15</v>
+      </c>
+      <c r="F242" t="s">
+        <v>23</v>
+      </c>
+      <c r="G242" s="3">
+        <v>389.22</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>258</v>
+      </c>
+      <c r="B243" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C243" t="s">
+        <v>8</v>
+      </c>
+      <c r="D243">
+        <v>19</v>
+      </c>
+      <c r="E243" t="s">
+        <v>9</v>
+      </c>
+      <c r="F243" t="s">
+        <v>44</v>
+      </c>
+      <c r="G243" s="3">
+        <v>1315.74</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>259</v>
+      </c>
+      <c r="B244" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C244" t="s">
+        <v>8</v>
+      </c>
+      <c r="D244">
+        <v>70</v>
+      </c>
+      <c r="E244" t="s">
+        <v>39</v>
+      </c>
+      <c r="F244" t="s">
+        <v>30</v>
+      </c>
+      <c r="G244" s="3">
+        <v>891.18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>260</v>
+      </c>
+      <c r="B245" s="2"/>
+      <c r="C245" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245">
+        <v>24</v>
+      </c>
+      <c r="E245" t="s">
+        <v>20</v>
+      </c>
+      <c r="F245" t="s">
+        <v>44</v>
+      </c>
+      <c r="G245" s="3">
+        <v>608.08000000000004</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>261</v>
+      </c>
+      <c r="B246" s="2">
+        <v>45664</v>
+      </c>
+      <c r="C246" t="s">
+        <v>8</v>
+      </c>
+      <c r="D246">
+        <v>30</v>
+      </c>
+      <c r="E246" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" t="s">
+        <v>44</v>
+      </c>
+      <c r="G246" s="3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>262</v>
+      </c>
+      <c r="B247" s="2">
+        <v>45917</v>
+      </c>
+      <c r="C247" t="s">
+        <v>17</v>
+      </c>
+      <c r="D247">
+        <v>32</v>
+      </c>
+      <c r="E247" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" t="s">
+        <v>44</v>
+      </c>
+      <c r="G247" s="3">
+        <v>1425.97</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>263</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C248" t="s">
+        <v>17</v>
+      </c>
+      <c r="D248">
+        <v>45</v>
+      </c>
+      <c r="E248" t="s">
+        <v>20</v>
+      </c>
+      <c r="F248" t="s">
+        <v>21</v>
+      </c>
+      <c r="G248" s="3">
+        <v>671.87</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>264</v>
+      </c>
+      <c r="B249" s="2">
+        <v>45833</v>
+      </c>
+      <c r="D249">
+        <v>43</v>
+      </c>
+      <c r="E249" t="s">
+        <v>9</v>
+      </c>
+      <c r="F249" t="s">
+        <v>23</v>
+      </c>
+      <c r="G249" s="3">
+        <v>885.26</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>265</v>
+      </c>
+      <c r="B250" s="2">
+        <v>45963</v>
+      </c>
+      <c r="C250" t="s">
+        <v>17</v>
+      </c>
+      <c r="D250">
+        <v>40</v>
+      </c>
+      <c r="E250" t="s">
+        <v>20</v>
+      </c>
+      <c r="F250" t="s">
+        <v>21</v>
+      </c>
+      <c r="G250" s="3">
+        <v>463.46</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>266</v>
+      </c>
+      <c r="B251" s="2">
+        <v>45837</v>
+      </c>
+      <c r="C251" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251">
+        <v>54</v>
+      </c>
+      <c r="E251" t="s">
+        <v>39</v>
+      </c>
+      <c r="F251" t="s">
+        <v>13</v>
+      </c>
+      <c r="G251" s="3">
+        <v>464.6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>267</v>
+      </c>
+      <c r="B252" s="2">
+        <v>45816</v>
+      </c>
+      <c r="D252">
+        <v>38</v>
+      </c>
+      <c r="E252" t="s">
+        <v>12</v>
+      </c>
+      <c r="F252" t="s">
+        <v>13</v>
+      </c>
+      <c r="G252" s="3">
+        <v>453.74</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>268</v>
+      </c>
+      <c r="B253" s="2">
+        <v>45732</v>
+      </c>
+      <c r="C253" t="s">
+        <v>8</v>
+      </c>
+      <c r="D253">
+        <v>21</v>
+      </c>
+      <c r="E253" t="s">
+        <v>9</v>
+      </c>
+      <c r="G253" s="3">
+        <v>1300.93</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>269</v>
+      </c>
+      <c r="B254" s="2">
+        <v>45892</v>
+      </c>
+      <c r="C254" t="s">
+        <v>8</v>
+      </c>
+      <c r="D254">
+        <v>43</v>
+      </c>
+      <c r="E254" t="s">
+        <v>39</v>
+      </c>
+      <c r="F254" t="s">
+        <v>10</v>
+      </c>
+      <c r="G254" s="3">
+        <v>1126.8900000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>270</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C255" t="s">
+        <v>8</v>
+      </c>
+      <c r="D255">
+        <v>61</v>
+      </c>
+      <c r="E255" t="s">
+        <v>9</v>
+      </c>
+      <c r="F255" t="s">
+        <v>23</v>
+      </c>
+      <c r="G255" s="3">
+        <v>1071.8599999999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" t="s">
+        <v>271</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C256" t="s">
+        <v>17</v>
+      </c>
+      <c r="D256">
+        <v>29</v>
+      </c>
+      <c r="E256" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" t="s">
+        <v>21</v>
+      </c>
+      <c r="G256" s="3">
+        <v>1143.8399999999999</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>272</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46057</v>
+      </c>
+      <c r="C257" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257">
+        <v>47</v>
+      </c>
+      <c r="E257" t="s">
+        <v>9</v>
+      </c>
+      <c r="F257" t="s">
+        <v>44</v>
+      </c>
+      <c r="G257" s="3"/>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" t="s">
+        <v>273</v>
+      </c>
+      <c r="B258" s="2">
+        <v>45752</v>
+      </c>
+      <c r="C258" t="s">
+        <v>17</v>
+      </c>
+      <c r="D258">
+        <v>39</v>
+      </c>
+      <c r="E258" t="s">
+        <v>74</v>
+      </c>
+      <c r="F258" t="s">
+        <v>23</v>
+      </c>
+      <c r="G258" s="3">
+        <v>396.11</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>274</v>
+      </c>
+      <c r="B259" s="2">
+        <v>46008</v>
+      </c>
+      <c r="D259">
+        <v>64</v>
+      </c>
+      <c r="E259" t="s">
+        <v>20</v>
+      </c>
+      <c r="F259" t="s">
+        <v>21</v>
+      </c>
+      <c r="G259" s="3">
+        <v>638.53</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" t="s">
+        <v>275</v>
+      </c>
+      <c r="B260" s="2">
+        <v>45721</v>
+      </c>
+      <c r="D260">
+        <v>29</v>
+      </c>
+      <c r="E260" t="s">
+        <v>9</v>
+      </c>
+      <c r="F260" t="s">
+        <v>44</v>
+      </c>
+      <c r="G260" s="3">
+        <v>1516.2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>276</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C261" t="s">
+        <v>17</v>
+      </c>
+      <c r="D261">
+        <v>28</v>
+      </c>
+      <c r="E261" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261" t="s">
+        <v>23</v>
+      </c>
+      <c r="G261" s="3">
+        <v>647.6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>277</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46039</v>
+      </c>
+      <c r="C262" t="s">
+        <v>17</v>
+      </c>
+      <c r="D262">
+        <v>37</v>
+      </c>
+      <c r="E262" t="s">
+        <v>20</v>
+      </c>
+      <c r="F262" t="s">
+        <v>18</v>
+      </c>
+      <c r="G262" s="3"/>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" t="s">
+        <v>278</v>
+      </c>
+      <c r="B263" s="2">
+        <v>45674</v>
+      </c>
+      <c r="D263">
+        <v>18</v>
+      </c>
+      <c r="E263" t="s">
+        <v>74</v>
+      </c>
+      <c r="F263" t="s">
+        <v>18</v>
+      </c>
+      <c r="G263" s="3">
+        <v>312.77</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>279</v>
+      </c>
+      <c r="B264" s="2">
+        <v>45883</v>
+      </c>
+      <c r="C264" t="s">
+        <v>8</v>
+      </c>
+      <c r="D264">
+        <v>61</v>
+      </c>
+      <c r="E264" t="s">
+        <v>9</v>
+      </c>
+      <c r="F264" t="s">
+        <v>21</v>
+      </c>
+      <c r="G264" s="3">
+        <v>961.13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>280</v>
+      </c>
+      <c r="B265" s="2">
+        <v>45884</v>
+      </c>
+      <c r="C265" t="s">
+        <v>8</v>
+      </c>
+      <c r="D265">
+        <v>44</v>
+      </c>
+      <c r="E265" t="s">
+        <v>9</v>
+      </c>
+      <c r="F265" t="s">
+        <v>30</v>
+      </c>
+      <c r="G265" s="3">
+        <v>1300.01</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>281</v>
+      </c>
+      <c r="B266" s="2">
+        <v>45772</v>
+      </c>
+      <c r="C266" t="s">
+        <v>8</v>
+      </c>
+      <c r="D266">
+        <v>56</v>
+      </c>
+      <c r="E266" t="s">
+        <v>9</v>
+      </c>
+      <c r="F266" t="s">
+        <v>21</v>
+      </c>
+      <c r="G266" s="3">
+        <v>1318.45</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>282</v>
+      </c>
+      <c r="B267" s="2">
+        <v>45705</v>
+      </c>
+      <c r="C267" t="s">
+        <v>8</v>
+      </c>
+      <c r="D267">
+        <v>52</v>
+      </c>
+      <c r="E267" t="s">
+        <v>74</v>
+      </c>
+      <c r="G267" s="3">
+        <v>494.83</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>283</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D268">
+        <v>49</v>
+      </c>
+      <c r="E268" t="s">
+        <v>39</v>
+      </c>
+      <c r="F268" t="s">
+        <v>21</v>
+      </c>
+      <c r="G268" s="3">
+        <v>1046.17</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>284</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C269" t="s">
+        <v>17</v>
+      </c>
+      <c r="D269">
+        <v>44</v>
+      </c>
+      <c r="E269" t="s">
+        <v>15</v>
+      </c>
+      <c r="F269" t="s">
+        <v>30</v>
+      </c>
+      <c r="G269" s="3">
+        <v>746.07</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>285</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C270" t="s">
+        <v>8</v>
+      </c>
+      <c r="E270" t="s">
+        <v>15</v>
+      </c>
+      <c r="F270" t="s">
+        <v>18</v>
+      </c>
+      <c r="G270" s="3">
+        <v>149.24</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>286</v>
+      </c>
+      <c r="B271" s="2">
+        <v>45941</v>
+      </c>
+      <c r="C271" t="s">
+        <v>8</v>
+      </c>
+      <c r="D271">
+        <v>20</v>
+      </c>
+      <c r="E271" t="s">
+        <v>15</v>
+      </c>
+      <c r="F271" t="s">
+        <v>21</v>
+      </c>
+      <c r="G271" s="3">
+        <v>438.08</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>287</v>
+      </c>
+      <c r="B272" s="2"/>
+      <c r="C272" t="s">
+        <v>17</v>
+      </c>
+      <c r="D272">
+        <v>53</v>
+      </c>
+      <c r="E272" t="s">
+        <v>20</v>
+      </c>
+      <c r="F272" t="s">
+        <v>44</v>
+      </c>
+      <c r="G272" s="3">
+        <v>776.84</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>288</v>
+      </c>
+      <c r="B273" s="2">
+        <v>46041</v>
+      </c>
+      <c r="C273" t="s">
+        <v>17</v>
+      </c>
+      <c r="D273">
+        <v>36</v>
+      </c>
+      <c r="F273" t="s">
+        <v>13</v>
+      </c>
+      <c r="G273" s="3">
+        <v>922.87</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>289</v>
+      </c>
+      <c r="B274" s="2">
+        <v>45662</v>
+      </c>
+      <c r="C274" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274">
+        <v>33</v>
+      </c>
+      <c r="E274" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" t="s">
+        <v>10</v>
+      </c>
+      <c r="G274" s="3">
+        <v>1250.21</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>290</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46080</v>
+      </c>
+      <c r="C275" t="s">
+        <v>17</v>
+      </c>
+      <c r="D275">
+        <v>60</v>
+      </c>
+      <c r="E275" t="s">
+        <v>20</v>
+      </c>
+      <c r="F275" t="s">
+        <v>10</v>
+      </c>
+      <c r="G275" s="3">
+        <v>854.23</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>174</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46041</v>
+      </c>
+      <c r="C276" t="s">
+        <v>17</v>
+      </c>
+      <c r="D276">
+        <v>28</v>
+      </c>
+      <c r="F276" t="s">
+        <v>21</v>
+      </c>
+      <c r="G276" s="3">
+        <v>785.95</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>291</v>
+      </c>
+      <c r="B277" s="2">
+        <v>46022</v>
+      </c>
+      <c r="D277">
+        <v>33</v>
+      </c>
+      <c r="E277" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277" t="s">
+        <v>13</v>
+      </c>
+      <c r="G277" s="3">
+        <v>790.38</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>292</v>
+      </c>
+      <c r="B278" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C278" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278">
+        <v>50</v>
+      </c>
+      <c r="E278" t="s">
+        <v>74</v>
+      </c>
+      <c r="F278" t="s">
+        <v>44</v>
+      </c>
+      <c r="G278" s="3">
+        <v>644.80999999999995</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>293</v>
+      </c>
+      <c r="B279" s="2"/>
+      <c r="C279" t="s">
+        <v>8</v>
+      </c>
+      <c r="D279">
+        <v>107</v>
+      </c>
+      <c r="E279" t="s">
+        <v>74</v>
+      </c>
+      <c r="F279" t="s">
+        <v>44</v>
+      </c>
+      <c r="G279" s="3">
+        <v>632.26</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>294</v>
+      </c>
+      <c r="B280" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C280" t="s">
+        <v>17</v>
+      </c>
+      <c r="D280">
+        <v>43</v>
+      </c>
+      <c r="E280" t="s">
+        <v>9</v>
+      </c>
+      <c r="F280" t="s">
+        <v>10</v>
+      </c>
+      <c r="G280" s="3">
+        <v>1069.08</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>295</v>
+      </c>
+      <c r="B281" s="2">
+        <v>45862</v>
+      </c>
+      <c r="C281" t="s">
+        <v>17</v>
+      </c>
+      <c r="D281">
+        <v>69</v>
+      </c>
+      <c r="E281" t="s">
+        <v>296</v>
+      </c>
+      <c r="G281" s="3">
+        <v>691.63</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>297</v>
+      </c>
+      <c r="B282" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C282" t="s">
+        <v>8</v>
+      </c>
+      <c r="E282" t="s">
+        <v>15</v>
+      </c>
+      <c r="F282" t="s">
+        <v>10</v>
+      </c>
+      <c r="G282" s="3">
+        <v>1263.1099999999999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>298</v>
+      </c>
+      <c r="B283" s="2">
+        <v>45703</v>
+      </c>
+      <c r="C283" t="s">
+        <v>8</v>
+      </c>
+      <c r="D283">
+        <v>66</v>
+      </c>
+      <c r="E283" t="s">
+        <v>15</v>
+      </c>
+      <c r="F283" t="s">
+        <v>10</v>
+      </c>
+      <c r="G283" s="3">
+        <v>1215.9100000000001</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>299</v>
+      </c>
+      <c r="B284" s="2">
+        <v>45973</v>
+      </c>
+      <c r="C284" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284">
+        <v>20</v>
+      </c>
+      <c r="E284" t="s">
+        <v>39</v>
+      </c>
+      <c r="F284" t="s">
+        <v>23</v>
+      </c>
+      <c r="G284" s="3">
+        <v>872.34</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>300</v>
+      </c>
+      <c r="B285" s="2">
+        <v>45934</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285">
+        <v>27</v>
+      </c>
+      <c r="E285" t="s">
+        <v>20</v>
+      </c>
+      <c r="F285" t="s">
+        <v>23</v>
+      </c>
+      <c r="G285" s="3">
+        <v>897.29</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>301</v>
+      </c>
+      <c r="B286" s="2">
+        <v>45741</v>
+      </c>
+      <c r="C286" t="s">
+        <v>17</v>
+      </c>
+      <c r="D286">
+        <v>48</v>
+      </c>
+      <c r="E286" t="s">
+        <v>12</v>
+      </c>
+      <c r="F286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G286" s="3">
+        <v>523.37</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>302</v>
+      </c>
+      <c r="B287" s="2">
+        <v>45775</v>
+      </c>
+      <c r="C287" t="s">
+        <v>17</v>
+      </c>
+      <c r="D287">
+        <v>58</v>
+      </c>
+      <c r="E287" t="s">
+        <v>39</v>
+      </c>
+      <c r="F287" t="s">
+        <v>44</v>
+      </c>
+      <c r="G287" s="3">
+        <v>622.54999999999995</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>303</v>
+      </c>
+      <c r="B288" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C288" t="s">
+        <v>17</v>
+      </c>
+      <c r="D288">
+        <v>18</v>
+      </c>
+      <c r="E288" t="s">
+        <v>9</v>
+      </c>
+      <c r="F288" t="s">
+        <v>23</v>
+      </c>
+      <c r="G288" s="3">
+        <v>1155.56</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>304</v>
+      </c>
+      <c r="B289" s="2">
+        <v>45956</v>
+      </c>
+      <c r="C289" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289">
+        <v>34</v>
+      </c>
+      <c r="E289" t="s">
+        <v>20</v>
+      </c>
+      <c r="F289" t="s">
+        <v>23</v>
+      </c>
+      <c r="G289" s="3">
+        <v>862.99</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>305</v>
+      </c>
+      <c r="B290" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C290" t="s">
+        <v>8</v>
+      </c>
+      <c r="D290">
+        <v>67</v>
+      </c>
+      <c r="E290" t="s">
+        <v>9</v>
+      </c>
+      <c r="F290" t="s">
+        <v>23</v>
+      </c>
+      <c r="G290" s="3">
+        <v>857.27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>306</v>
+      </c>
+      <c r="B291" s="2">
+        <v>45745</v>
+      </c>
+      <c r="C291" t="s">
+        <v>17</v>
+      </c>
+      <c r="D291">
+        <v>32</v>
+      </c>
+      <c r="E291" t="s">
+        <v>9</v>
+      </c>
+      <c r="F291" t="s">
+        <v>307</v>
+      </c>
+      <c r="G291" s="3">
+        <v>1235.8900000000001</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>308</v>
+      </c>
+      <c r="B292" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C292" t="s">
+        <v>17</v>
+      </c>
+      <c r="D292">
+        <v>57</v>
+      </c>
+      <c r="E292" t="s">
+        <v>39</v>
+      </c>
+      <c r="F292" t="s">
+        <v>30</v>
+      </c>
+      <c r="G292" s="3">
+        <v>749.33</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>113</v>
+      </c>
+      <c r="B293" s="2">
+        <v>45757</v>
+      </c>
+      <c r="C293" t="s">
+        <v>17</v>
+      </c>
+      <c r="D293">
+        <v>33</v>
+      </c>
+      <c r="E293" t="s">
+        <v>74</v>
+      </c>
+      <c r="F293" t="s">
+        <v>23</v>
+      </c>
+      <c r="G293" s="3">
+        <v>661.71</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>309</v>
+      </c>
+      <c r="B294" s="2">
+        <v>46022</v>
+      </c>
+      <c r="C294" t="s">
+        <v>17</v>
+      </c>
+      <c r="D294">
+        <v>41</v>
+      </c>
+      <c r="E294" t="s">
+        <v>12</v>
+      </c>
+      <c r="F294" t="s">
+        <v>21</v>
+      </c>
+      <c r="G294" s="3">
+        <v>455.83</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>310</v>
+      </c>
+      <c r="B295" s="2">
+        <v>45750</v>
+      </c>
+      <c r="C295" t="s">
+        <v>8</v>
+      </c>
+      <c r="D295">
+        <v>49</v>
+      </c>
+      <c r="E295" t="s">
+        <v>20</v>
+      </c>
+      <c r="F295" t="s">
+        <v>18</v>
+      </c>
+      <c r="G295" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A295"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="350">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -23709,7 +23709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -23718,15 +23718,12 @@
     <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="16" customFormat="1" ht="15.75">
+    <row r="1" spans="1:3" s="16" customFormat="1" ht="15.75">
       <c r="A1" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="H1" s="16" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
         <v>337</v>
       </c>
@@ -23737,7 +23734,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="14" t="s">
         <v>318</v>
       </c>
@@ -23749,7 +23746,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="4" spans="1:3" ht="15.75">
       <c r="A4" s="14" t="s">
         <v>319</v>
       </c>
@@ -23761,7 +23758,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75">
+    <row r="5" spans="1:3" ht="15.75">
       <c r="A5" s="14" t="s">
         <v>324</v>
       </c>
@@ -23773,7 +23770,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75">
+    <row r="6" spans="1:3" ht="15.75">
       <c r="A6" s="14" t="s">
         <v>326</v>
       </c>
@@ -23785,7 +23782,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75">
       <c r="A7" s="14" t="s">
         <v>335</v>
       </c>
@@ -23797,7 +23794,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="14" t="s">
         <v>329</v>
       </c>
@@ -23809,7 +23806,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75">
+    <row r="9" spans="1:3" ht="15.75">
       <c r="A9" s="14" t="s">
         <v>331</v>
       </c>
@@ -23821,7 +23818,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75">
       <c r="A10" s="14" t="s">
         <v>333</v>
       </c>
@@ -23833,7 +23830,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:3">
       <c r="A11" s="13"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -21,6 +21,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clean_Data '!$F$1:$F$294</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="365">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -1085,6 +1086,51 @@
   </si>
   <si>
     <t>Female and income &gt;= 1000</t>
+  </si>
+  <si>
+    <t>DATE ANALYSIS</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Current date</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Current date &amp; time</t>
+  </si>
+  <si>
+    <t>Registration day</t>
+  </si>
+  <si>
+    <t>Year (row 2)</t>
+  </si>
+  <si>
+    <t>Registration year</t>
+  </si>
+  <si>
+    <t>Registration Month</t>
+  </si>
+  <si>
+    <t>Month(row 2)</t>
+  </si>
+  <si>
+    <t>Day (row 2)</t>
+  </si>
+  <si>
+    <t>Build a date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example DATE </t>
+  </si>
+  <si>
+    <t>Working days since reg (row 2)</t>
+  </si>
+  <si>
+    <t>Workdays from registration to today</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1141,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1146,6 +1192,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri "/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1185,7 +1235,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1210,6 +1260,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1219,6 +1272,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="60% - Accent5" xfId="2" builtinId="48"/>
@@ -5347,6 +5403,35 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Raw_Data"/>
+      <sheetName val="Clean_Data "/>
+      <sheetName val="Analysis"/>
+      <sheetName val="PivotTables"/>
+      <sheetName val="Dashboard"/>
+      <sheetName val="Findings"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="B2">
+            <v>45677</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -23709,17 +23794,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="16" customFormat="1" ht="15.75">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" s="17" customFormat="1" ht="15.75">
+      <c r="A1" s="17" t="s">
         <v>317</v>
       </c>
     </row>
@@ -23735,105 +23820,105 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <f>SUM('[1]Clean_Data '!G:G)</f>
         <v>270693.18999999989</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <f>AVERAGE('[1]Clean_Data '!G:G)</f>
         <v>923.86754266211562</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <f>AVERAGE('[1]Clean_Data '!D:D)</f>
         <v>44.228668941979521</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <f>COUNTA('[1]Clean_Data '!A:A)-1</f>
         <v>279</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <f>MIN('[1]Clean_Data '!D:D)</f>
         <v>18</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <f>MAX('[1]Clean_Data '!D:D)</f>
         <v>123</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <f>MIN('[1]Clean_Data '!G:G)</f>
         <v>108.23</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <f>MAX('[1]Clean_Data '!G:G)</f>
         <v>10013</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
     </row>
     <row r="17" spans="1:3" s="10" customFormat="1">
       <c r="A17" s="10" t="s">
@@ -23884,7 +23969,7 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="C24" s="12"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" s="10" customFormat="1">
       <c r="A25" s="10" t="s">
@@ -23924,6 +24009,106 @@
       </c>
       <c r="C28" t="s">
         <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="10" customFormat="1">
+      <c r="A31" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>351</v>
+      </c>
+      <c r="B33" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46249</v>
+      </c>
+      <c r="C33" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>353</v>
+      </c>
+      <c r="B34" s="19">
+        <f ca="1">NOW()</f>
+        <v>46249.637818171293</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>360</v>
+      </c>
+      <c r="B35">
+        <f>DAY('[2]Clean_Data '!B2)</f>
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>356</v>
+      </c>
+      <c r="B36">
+        <f>YEAR('[2]Clean_Data '!B2)</f>
+        <v>2025</v>
+      </c>
+      <c r="C36" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>359</v>
+      </c>
+      <c r="B37">
+        <f>MONTH('[2]Clean_Data '!B2)</f>
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" s="18">
+        <f>DATE(2025,1,20)</f>
+        <v>45677</v>
+      </c>
+      <c r="C38" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>363</v>
+      </c>
+      <c r="B39">
+        <f ca="1">NETWORKDAYS('[2]Clean_Data '!B2,TODAY())</f>
+        <v>410</v>
+      </c>
+      <c r="C39" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -1293,7 +1293,97 @@
     <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -23800,10 +23890,148 @@
     <sortCondition ref="B2:B294"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CBE43EE1-593C-434C-A461-81BCE20AA1CA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{11A4E547-5A7A-44F7-9AAB-C31D35F57467}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9B40E47E-5BA8-4437-A968-697F4DECC02D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{CBE43EE1-593C-434C-A461-81BCE20AA1CA}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{11A4E547-5A7A-44F7-9AAB-C31D35F57467}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9B40E47E-5BA8-4437-A968-697F4DECC02D}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -23825,7 +24053,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="6" customFormat="1">
+    <row r="2" spans="1:3">
       <c r="A2" s="12" t="s">
         <v>337</v>
       </c>
@@ -23836,7 +24064,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="10" t="s">
         <v>318</v>
       </c>
@@ -23848,7 +24076,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="4" spans="1:3" ht="15.75">
       <c r="A4" s="10" t="s">
         <v>319</v>
       </c>
@@ -23860,7 +24088,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="5" spans="1:3" ht="15.75">
       <c r="A5" s="10" t="s">
         <v>324</v>
       </c>
@@ -23872,7 +24100,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="6" spans="1:3" ht="15.75">
       <c r="A6" s="10" t="s">
         <v>326</v>
       </c>
@@ -23884,7 +24112,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75">
       <c r="A7" s="10" t="s">
         <v>335</v>
       </c>
@@ -23896,7 +24124,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="10" t="s">
         <v>329</v>
       </c>
@@ -23908,7 +24136,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="9" spans="1:3" ht="15.75">
       <c r="A9" s="10" t="s">
         <v>331</v>
       </c>
@@ -23920,7 +24148,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="6" customFormat="1" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75">
       <c r="A10" s="10" t="s">
         <v>333</v>
       </c>
@@ -23932,7 +24160,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="6" customFormat="1">
+    <row r="11" spans="1:3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -23942,7 +24170,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="6" customFormat="1">
+    <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
         <v>337</v>
       </c>
@@ -23953,7 +24181,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="6" customFormat="1">
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
         <v>338</v>
       </c>
@@ -23965,7 +24193,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="6" customFormat="1">
+    <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
         <v>341</v>
       </c>
@@ -23973,7 +24201,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="6" customFormat="1">
+    <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
         <v>342</v>
       </c>
@@ -23985,7 +24213,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="6" customFormat="1">
+    <row r="24" spans="1:3">
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3" s="13" customFormat="1">
@@ -23993,7 +24221,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="6" customFormat="1">
+    <row r="26" spans="1:3">
       <c r="A26" s="12" t="s">
         <v>337</v>
       </c>
@@ -24004,7 +24232,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="6" customFormat="1">
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
         <v>344</v>
       </c>
@@ -24016,7 +24244,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="6" customFormat="1">
+    <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
         <v>348</v>
       </c>
@@ -24033,7 +24261,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="6" customFormat="1">
+    <row r="32" spans="1:3">
       <c r="A32" s="12" t="s">
         <v>337</v>
       </c>
@@ -24044,7 +24272,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="6" customFormat="1">
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
         <v>351</v>
       </c>
@@ -24056,19 +24284,19 @@
         <v>352</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="6" customFormat="1">
+    <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
         <v>353</v>
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46249.650530092593</v>
+        <v>46249.679538310185</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="6" customFormat="1">
+    <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
         <v>360</v>
       </c>
@@ -24080,7 +24308,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="6" customFormat="1">
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
         <v>356</v>
       </c>
@@ -24092,7 +24320,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="6" customFormat="1">
+    <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
         <v>359</v>
       </c>
@@ -24104,7 +24332,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="6" customFormat="1">
+    <row r="38" spans="1:3">
       <c r="A38" s="17" t="s">
         <v>362</v>
       </c>
@@ -24116,7 +24344,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="6" customFormat="1">
+    <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
         <v>363</v>
       </c>

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -1293,7 +1293,168 @@
     <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -12523,15 +12684,15 @@
         <v>1455.22</v>
       </c>
       <c r="H2" s="6" t="str">
-        <f>PROPER(TRIM(C2))</f>
+        <f t="shared" ref="H2:H65" si="0">PROPER(TRIM(C2))</f>
         <v>Female</v>
       </c>
       <c r="I2" s="6" t="str">
-        <f>PROPER(TRIM(E2))</f>
+        <f t="shared" ref="I2:I65" si="1">PROPER(TRIM(E2))</f>
         <v>Missing</v>
       </c>
       <c r="J2" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F2,"CS","Civil Servant")))</f>
+        <f t="shared" ref="J2:J65" si="2">PROPER(TRIM(SUBSTITUTE(F2,"CS","Civil Servant")))</f>
         <v>Business Owner</v>
       </c>
       <c r="K2" s="6" t="str">
@@ -12562,19 +12723,19 @@
         <v>1250.21</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f>PROPER(TRIM(C3))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I3" s="6" t="str">
-        <f>PROPER(TRIM(E3))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J3" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F3,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K3" s="6" t="str">
-        <f>IF(G3&gt;=1500,"High",IF(G3&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K2:K65" si="3">IF(G3&gt;=1500,"High",IF(G3&gt;=800,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -12601,19 +12762,19 @@
         <v>602</v>
       </c>
       <c r="H4" s="6" t="str">
-        <f>PROPER(TRIM(C4))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I4" s="6" t="str">
-        <f>PROPER(TRIM(E4))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J4" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F4,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K4" s="6" t="str">
-        <f>IF(G4&gt;=1500,"High",IF(G4&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -12640,19 +12801,19 @@
         <v>789.1</v>
       </c>
       <c r="H5" s="6" t="str">
-        <f>PROPER(TRIM(C5))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I5" s="6" t="str">
-        <f>PROPER(TRIM(E5))</f>
+        <f t="shared" si="1"/>
         <v>Bosaso</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F5,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K5" s="6" t="str">
-        <f>IF(G5&gt;=1500,"High",IF(G5&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -12679,19 +12840,19 @@
         <v>1964.48</v>
       </c>
       <c r="H6" s="6" t="str">
-        <f>PROPER(TRIM(C6))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I6" s="6" t="str">
-        <f>PROPER(TRIM(E6))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J6" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F6,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K6" s="6" t="str">
-        <f>IF(G6&gt;=1500,"High",IF(G6&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -12718,19 +12879,19 @@
         <v>1547.72</v>
       </c>
       <c r="H7" s="6" t="str">
-        <f>PROPER(TRIM(C7))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I7" s="6" t="str">
-        <f>PROPER(TRIM(E7))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J7" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F7,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K7" s="6" t="str">
-        <f>IF(G7&gt;=1500,"High",IF(G7&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -12757,19 +12918,19 @@
         <v>881.22</v>
       </c>
       <c r="H8" s="6" t="str">
-        <f>PROPER(TRIM(C8))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I8" s="6" t="str">
-        <f>PROPER(TRIM(E8))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J8" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F8,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K8" s="6" t="str">
-        <f>IF(G8&gt;=1500,"High",IF(G8&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -12796,19 +12957,19 @@
         <v>278.61</v>
       </c>
       <c r="H9" s="6" t="str">
-        <f>PROPER(TRIM(C9))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I9" s="6" t="str">
-        <f>PROPER(TRIM(E9))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J9" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F9,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K9" s="6" t="str">
-        <f>IF(G9&gt;=1500,"High",IF(G9&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -12835,19 +12996,19 @@
         <v>923.87</v>
       </c>
       <c r="H10" s="6" t="str">
-        <f>PROPER(TRIM(C10))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I10" s="6" t="str">
-        <f>PROPER(TRIM(E10))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J10" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F10,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K10" s="6" t="str">
-        <f>IF(G10&gt;=1500,"High",IF(G10&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -12874,19 +13035,19 @@
         <v>127.29</v>
       </c>
       <c r="H11" s="6" t="str">
-        <f>PROPER(TRIM(C11))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I11" s="6" t="str">
-        <f>PROPER(TRIM(E11))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J11" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F11,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K11" s="6" t="str">
-        <f>IF(G11&gt;=1500,"High",IF(G11&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -12913,19 +13074,19 @@
         <v>312.77</v>
       </c>
       <c r="H12" s="6" t="str">
-        <f>PROPER(TRIM(C12))</f>
+        <f t="shared" si="0"/>
         <v>Missing</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f>PROPER(TRIM(E12))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J12" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F12,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K12" s="6" t="str">
-        <f>IF(G12&gt;=1500,"High",IF(G12&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -12952,19 +13113,19 @@
         <v>1015.92</v>
       </c>
       <c r="H13" s="6" t="str">
-        <f>PROPER(TRIM(C13))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I13" s="6" t="str">
-        <f>PROPER(TRIM(E13))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J13" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F13,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K13" s="6" t="str">
-        <f>IF(G13&gt;=1500,"High",IF(G13&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -12991,19 +13152,19 @@
         <v>1024.44</v>
       </c>
       <c r="H14" s="6" t="str">
-        <f>PROPER(TRIM(C14))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I14" s="6" t="str">
-        <f>PROPER(TRIM(E14))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J14" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F14,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K14" s="6" t="str">
-        <f>IF(G14&gt;=1500,"High",IF(G14&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13030,19 +13191,19 @@
         <v>926.65</v>
       </c>
       <c r="H15" s="6" t="str">
-        <f>PROPER(TRIM(C15))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I15" s="6" t="str">
-        <f>PROPER(TRIM(E15))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J15" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F15,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K15" s="6" t="str">
-        <f>IF(G15&gt;=1500,"High",IF(G15&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13069,19 +13230,19 @@
         <v>2040.09</v>
       </c>
       <c r="H16" s="6" t="str">
-        <f>PROPER(TRIM(C16))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I16" s="6" t="str">
-        <f>PROPER(TRIM(E16))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J16" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F16,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K16" s="6" t="str">
-        <f>IF(G16&gt;=1500,"High",IF(G16&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -13108,19 +13269,19 @@
         <v>836.87</v>
       </c>
       <c r="H17" s="6" t="str">
-        <f>PROPER(TRIM(C17))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I17" s="6" t="str">
-        <f>PROPER(TRIM(E17))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J17" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F17,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K17" s="6" t="str">
-        <f>IF(G17&gt;=1500,"High",IF(G17&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13147,19 +13308,19 @@
         <v>579.54999999999995</v>
       </c>
       <c r="H18" s="6" t="str">
-        <f>PROPER(TRIM(C18))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I18" s="6" t="str">
-        <f>PROPER(TRIM(E18))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J18" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F18,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K18" s="6" t="str">
-        <f>IF(G18&gt;=1500,"High",IF(G18&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13186,19 +13347,19 @@
         <v>954.9</v>
       </c>
       <c r="H19" s="6" t="str">
-        <f>PROPER(TRIM(C19))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I19" s="6" t="str">
-        <f>PROPER(TRIM(E19))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J19" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F19,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K19" s="6" t="str">
-        <f>IF(G19&gt;=1500,"High",IF(G19&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13225,19 +13386,19 @@
         <v>526.37</v>
       </c>
       <c r="H20" s="6" t="str">
-        <f>PROPER(TRIM(C20))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I20" s="6" t="str">
-        <f>PROPER(TRIM(E20))</f>
+        <f t="shared" si="1"/>
         <v>Missing</v>
       </c>
       <c r="J20" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F20,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K20" s="6" t="str">
-        <f>IF(G20&gt;=1500,"High",IF(G20&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13264,19 +13425,19 @@
         <v>1086.56</v>
       </c>
       <c r="H21" s="6" t="str">
-        <f>PROPER(TRIM(C21))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I21" s="6" t="str">
-        <f>PROPER(TRIM(E21))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J21" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F21,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K21" s="6" t="str">
-        <f>IF(G21&gt;=1500,"High",IF(G21&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13303,19 +13464,19 @@
         <v>923.87</v>
       </c>
       <c r="H22" s="6" t="str">
-        <f>PROPER(TRIM(C22))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I22" s="6" t="str">
-        <f>PROPER(TRIM(E22))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J22" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F22,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K22" s="6" t="str">
-        <f>IF(G22&gt;=1500,"High",IF(G22&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13342,19 +13503,19 @@
         <v>210.96</v>
       </c>
       <c r="H23" s="6" t="str">
-        <f>PROPER(TRIM(C23))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I23" s="6" t="str">
-        <f>PROPER(TRIM(E23))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J23" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F23,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K23" s="6" t="str">
-        <f>IF(G23&gt;=1500,"High",IF(G23&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13381,19 +13542,19 @@
         <v>1214.6199999999999</v>
       </c>
       <c r="H24" s="6" t="str">
-        <f>PROPER(TRIM(C24))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I24" s="6" t="str">
-        <f>PROPER(TRIM(E24))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J24" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F24,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K24" s="6" t="str">
-        <f>IF(G24&gt;=1500,"High",IF(G24&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13420,19 +13581,19 @@
         <v>1215.9100000000001</v>
       </c>
       <c r="H25" s="6" t="str">
-        <f>PROPER(TRIM(C25))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I25" s="6" t="str">
-        <f>PROPER(TRIM(E25))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J25" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F25,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K25" s="6" t="str">
-        <f>IF(G25&gt;=1500,"High",IF(G25&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13459,19 +13620,19 @@
         <v>494.83</v>
       </c>
       <c r="H26" s="6" t="str">
-        <f>PROPER(TRIM(C26))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I26" s="6" t="str">
-        <f>PROPER(TRIM(E26))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J26" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F26,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Missing</v>
       </c>
       <c r="K26" s="6" t="str">
-        <f>IF(G26&gt;=1500,"High",IF(G26&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13498,19 +13659,19 @@
         <v>646.07000000000005</v>
       </c>
       <c r="H27" s="6" t="str">
-        <f>PROPER(TRIM(C27))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I27" s="6" t="str">
-        <f>PROPER(TRIM(E27))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J27" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F27,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K27" s="6" t="str">
-        <f>IF(G27&gt;=1500,"High",IF(G27&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13537,19 +13698,19 @@
         <v>409.49</v>
       </c>
       <c r="H28" s="6" t="str">
-        <f>PROPER(TRIM(C28))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I28" s="6" t="str">
-        <f>PROPER(TRIM(E28))</f>
+        <f t="shared" si="1"/>
         <v>Bosaso</v>
       </c>
       <c r="J28" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F28,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K28" s="6" t="str">
-        <f>IF(G28&gt;=1500,"High",IF(G28&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13576,19 +13737,19 @@
         <v>835.61</v>
       </c>
       <c r="H29" s="6" t="str">
-        <f>PROPER(TRIM(C29))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I29" s="6" t="str">
-        <f>PROPER(TRIM(E29))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J29" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F29,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K29" s="6" t="str">
-        <f>IF(G29&gt;=1500,"High",IF(G29&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13615,19 +13776,19 @@
         <v>923.87</v>
       </c>
       <c r="H30" s="6" t="str">
-        <f>PROPER(TRIM(C30))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I30" s="6" t="str">
-        <f>PROPER(TRIM(E30))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J30" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F30,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K30" s="6" t="str">
-        <f>IF(G30&gt;=1500,"High",IF(G30&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13654,19 +13815,19 @@
         <v>675.77</v>
       </c>
       <c r="H31" s="6" t="str">
-        <f>PROPER(TRIM(C31))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I31" s="6" t="str">
-        <f>PROPER(TRIM(E31))</f>
+        <f t="shared" si="1"/>
         <v>Missing</v>
       </c>
       <c r="J31" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F31,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K31" s="6" t="str">
-        <f>IF(G31&gt;=1500,"High",IF(G31&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13693,19 +13854,19 @@
         <v>1800.86</v>
       </c>
       <c r="H32" s="6" t="str">
-        <f>PROPER(TRIM(C32))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I32" s="6" t="str">
-        <f>PROPER(TRIM(E32))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J32" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F32,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K32" s="6" t="str">
-        <f>IF(G32&gt;=1500,"High",IF(G32&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -13732,19 +13893,19 @@
         <v>1516.2</v>
       </c>
       <c r="H33" s="6" t="str">
-        <f>PROPER(TRIM(C33))</f>
+        <f t="shared" si="0"/>
         <v>Missing</v>
       </c>
       <c r="I33" s="6" t="str">
-        <f>PROPER(TRIM(E33))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J33" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F33,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K33" s="6" t="str">
-        <f>IF(G33&gt;=1500,"High",IF(G33&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -13771,19 +13932,19 @@
         <v>952.9</v>
       </c>
       <c r="H34" s="6" t="str">
-        <f>PROPER(TRIM(C34))</f>
+        <f t="shared" si="0"/>
         <v>Missing</v>
       </c>
       <c r="I34" s="6" t="str">
-        <f>PROPER(TRIM(E34))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J34" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F34,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K34" s="6" t="str">
-        <f>IF(G34&gt;=1500,"High",IF(G34&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13807,19 +13968,19 @@
         <v>1144.9100000000001</v>
       </c>
       <c r="H35" s="6" t="str">
-        <f>PROPER(TRIM(C35))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I35" s="6" t="str">
-        <f>PROPER(TRIM(E35))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J35" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F35,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K35" s="6" t="str">
-        <f>IF(G35&gt;=1500,"High",IF(G35&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13846,19 +14007,19 @@
         <v>963.66</v>
       </c>
       <c r="H36" s="6" t="str">
-        <f>PROPER(TRIM(C36))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I36" s="6" t="str">
-        <f>PROPER(TRIM(E36))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J36" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F36,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Engineer</v>
       </c>
       <c r="K36" s="6" t="str">
-        <f>IF(G36&gt;=1500,"High",IF(G36&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13885,19 +14046,19 @@
         <v>1023.35</v>
       </c>
       <c r="H37" s="6" t="str">
-        <f>PROPER(TRIM(C37))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I37" s="6" t="str">
-        <f>PROPER(TRIM(E37))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J37" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F37,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K37" s="6" t="str">
-        <f>IF(G37&gt;=1500,"High",IF(G37&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -13924,19 +14085,19 @@
         <v>457.6</v>
       </c>
       <c r="H38" s="6" t="str">
-        <f>PROPER(TRIM(C38))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I38" s="6" t="str">
-        <f>PROPER(TRIM(E38))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J38" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F38,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K38" s="6" t="str">
-        <f>IF(G38&gt;=1500,"High",IF(G38&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -13963,19 +14124,19 @@
         <v>1300.93</v>
       </c>
       <c r="H39" s="6" t="str">
-        <f>PROPER(TRIM(C39))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I39" s="6" t="str">
-        <f>PROPER(TRIM(E39))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J39" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F39,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Missing</v>
       </c>
       <c r="K39" s="6" t="str">
-        <f>IF(G39&gt;=1500,"High",IF(G39&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14002,19 +14163,19 @@
         <v>707.01</v>
       </c>
       <c r="H40" s="6" t="str">
-        <f>PROPER(TRIM(C40))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I40" s="6" t="str">
-        <f>PROPER(TRIM(E40))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J40" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F40,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K40" s="6" t="str">
-        <f>IF(G40&gt;=1500,"High",IF(G40&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14041,19 +14202,19 @@
         <v>265.87</v>
       </c>
       <c r="H41" s="6" t="str">
-        <f>PROPER(TRIM(C41))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I41" s="6" t="str">
-        <f>PROPER(TRIM(E41))</f>
+        <f t="shared" si="1"/>
         <v>Missing</v>
       </c>
       <c r="J41" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F41,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K41" s="6" t="str">
-        <f>IF(G41&gt;=1500,"High",IF(G41&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14080,19 +14241,19 @@
         <v>523.37</v>
       </c>
       <c r="H42" s="6" t="str">
-        <f>PROPER(TRIM(C42))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I42" s="6" t="str">
-        <f>PROPER(TRIM(E42))</f>
+        <f t="shared" si="1"/>
         <v>Baidoa</v>
       </c>
       <c r="J42" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F42,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K42" s="6" t="str">
-        <f>IF(G42&gt;=1500,"High",IF(G42&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14119,19 +14280,19 @@
         <v>1984.53</v>
       </c>
       <c r="H43" s="6" t="str">
-        <f>PROPER(TRIM(C43))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I43" s="6" t="str">
-        <f>PROPER(TRIM(E43))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J43" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F43,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K43" s="6" t="str">
-        <f>IF(G43&gt;=1500,"High",IF(G43&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -14158,19 +14319,19 @@
         <v>389.22</v>
       </c>
       <c r="H44" s="6" t="str">
-        <f>PROPER(TRIM(C44))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I44" s="6" t="str">
-        <f>PROPER(TRIM(E44))</f>
+        <f t="shared" si="1"/>
         <v>Hargeisa</v>
       </c>
       <c r="J44" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F44,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K44" s="6" t="str">
-        <f>IF(G44&gt;=1500,"High",IF(G44&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14197,19 +14358,19 @@
         <v>10013</v>
       </c>
       <c r="H45" s="6" t="str">
-        <f>PROPER(TRIM(C45))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I45" s="6" t="str">
-        <f>PROPER(TRIM(E45))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J45" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F45,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K45" s="6" t="str">
-        <f>IF(G45&gt;=1500,"High",IF(G45&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -14236,19 +14397,19 @@
         <v>1235.8900000000001</v>
       </c>
       <c r="H46" s="6" t="str">
-        <f>PROPER(TRIM(C46))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I46" s="6" t="str">
-        <f>PROPER(TRIM(E46))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J46" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F46,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K46" s="6" t="str">
-        <f>IF(G46&gt;=1500,"High",IF(G46&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14275,19 +14436,19 @@
         <v>863.68</v>
       </c>
       <c r="H47" s="6" t="str">
-        <f>PROPER(TRIM(C47))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I47" s="6" t="str">
-        <f>PROPER(TRIM(E47))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J47" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F47,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Missing</v>
       </c>
       <c r="K47" s="6" t="str">
-        <f>IF(G47&gt;=1500,"High",IF(G47&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14314,19 +14475,19 @@
         <v>1091.0999999999999</v>
       </c>
       <c r="H48" s="6" t="str">
-        <f>PROPER(TRIM(C48))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I48" s="6" t="str">
-        <f>PROPER(TRIM(E48))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J48" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F48,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K48" s="6" t="str">
-        <f>IF(G48&gt;=1500,"High",IF(G48&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14353,19 +14514,19 @@
         <v>923.87</v>
       </c>
       <c r="H49" s="6" t="str">
-        <f>PROPER(TRIM(C49))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I49" s="6" t="str">
-        <f>PROPER(TRIM(E49))</f>
+        <f t="shared" si="1"/>
         <v>Bosaso</v>
       </c>
       <c r="J49" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F49,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K49" s="6" t="str">
-        <f>IF(G49&gt;=1500,"High",IF(G49&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14392,19 +14553,19 @@
         <v>396.11</v>
       </c>
       <c r="H50" s="6" t="str">
-        <f>PROPER(TRIM(C50))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I50" s="6" t="str">
-        <f>PROPER(TRIM(E50))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J50" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F50,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K50" s="6" t="str">
-        <f>IF(G50&gt;=1500,"High",IF(G50&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14431,19 +14592,19 @@
         <v>1852.82</v>
       </c>
       <c r="H51" s="6" t="str">
-        <f>PROPER(TRIM(C51))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I51" s="6" t="str">
-        <f>PROPER(TRIM(E51))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J51" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F51,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K51" s="6" t="str">
-        <f>IF(G51&gt;=1500,"High",IF(G51&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -14470,19 +14631,19 @@
         <v>746.26</v>
       </c>
       <c r="H52" s="6" t="str">
-        <f>PROPER(TRIM(C52))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I52" s="6" t="str">
-        <f>PROPER(TRIM(E52))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J52" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F52,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K52" s="6" t="str">
-        <f>IF(G52&gt;=1500,"High",IF(G52&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14509,19 +14670,19 @@
         <v>661.71</v>
       </c>
       <c r="H53" s="6" t="str">
-        <f>PROPER(TRIM(C53))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I53" s="6" t="str">
-        <f>PROPER(TRIM(E53))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J53" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F53,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K53" s="6" t="str">
-        <f>IF(G53&gt;=1500,"High",IF(G53&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14548,19 +14709,19 @@
         <v>641.59</v>
       </c>
       <c r="H54" s="6" t="str">
-        <f>PROPER(TRIM(C54))</f>
+        <f t="shared" si="0"/>
         <v>Missing</v>
       </c>
       <c r="I54" s="6" t="str">
-        <f>PROPER(TRIM(E54))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J54" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F54,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Civil Servant</v>
       </c>
       <c r="K54" s="6" t="str">
-        <f>IF(G54&gt;=1500,"High",IF(G54&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14587,19 +14748,19 @@
         <v>10006</v>
       </c>
       <c r="H55" s="6" t="str">
-        <f>PROPER(TRIM(C55))</f>
+        <f t="shared" si="0"/>
         <v>Missing</v>
       </c>
       <c r="I55" s="6" t="str">
-        <f>PROPER(TRIM(E55))</f>
+        <f t="shared" si="1"/>
         <v>Bosaso</v>
       </c>
       <c r="J55" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F55,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Healthcare</v>
       </c>
       <c r="K55" s="6" t="str">
-        <f>IF(G55&gt;=1500,"High",IF(G55&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>High</v>
       </c>
     </row>
@@ -14626,19 +14787,19 @@
         <v>799.53</v>
       </c>
       <c r="H56" s="6" t="str">
-        <f>PROPER(TRIM(C56))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I56" s="6" t="str">
-        <f>PROPER(TRIM(E56))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J56" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F56,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K56" s="6" t="str">
-        <f>IF(G56&gt;=1500,"High",IF(G56&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14665,19 +14826,19 @@
         <v>923.87</v>
       </c>
       <c r="H57" s="6" t="str">
-        <f>PROPER(TRIM(C57))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I57" s="6" t="str">
-        <f>PROPER(TRIM(E57))</f>
+        <f t="shared" si="1"/>
         <v>Bosaso</v>
       </c>
       <c r="J57" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F57,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K57" s="6" t="str">
-        <f>IF(G57&gt;=1500,"High",IF(G57&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14704,19 +14865,19 @@
         <v>1470.86</v>
       </c>
       <c r="H58" s="6" t="str">
-        <f>PROPER(TRIM(C58))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I58" s="6" t="str">
-        <f>PROPER(TRIM(E58))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J58" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F58,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K58" s="6" t="str">
-        <f>IF(G58&gt;=1500,"High",IF(G58&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14743,19 +14904,19 @@
         <v>120.06</v>
       </c>
       <c r="H59" s="6" t="str">
-        <f>PROPER(TRIM(C59))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I59" s="6" t="str">
-        <f>PROPER(TRIM(E59))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J59" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F59,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K59" s="6" t="str">
-        <f>IF(G59&gt;=1500,"High",IF(G59&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14782,19 +14943,19 @@
         <v>680.77</v>
       </c>
       <c r="H60" s="6" t="str">
-        <f>PROPER(TRIM(C60))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I60" s="6" t="str">
-        <f>PROPER(TRIM(E60))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J60" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F60,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K60" s="6" t="str">
-        <f>IF(G60&gt;=1500,"High",IF(G60&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14821,19 +14982,19 @@
         <v>758.44</v>
       </c>
       <c r="H61" s="6" t="str">
-        <f>PROPER(TRIM(C61))</f>
+        <f t="shared" si="0"/>
         <v>Female</v>
       </c>
       <c r="I61" s="6" t="str">
-        <f>PROPER(TRIM(E61))</f>
+        <f t="shared" si="1"/>
         <v>Garowe</v>
       </c>
       <c r="J61" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F61,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K61" s="6" t="str">
-        <f>IF(G61&gt;=1500,"High",IF(G61&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14860,19 +15021,19 @@
         <v>129.81</v>
       </c>
       <c r="H62" s="6" t="str">
-        <f>PROPER(TRIM(C62))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I62" s="6" t="str">
-        <f>PROPER(TRIM(E62))</f>
+        <f t="shared" si="1"/>
         <v>Kismayo</v>
       </c>
       <c r="J62" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F62,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Student</v>
       </c>
       <c r="K62" s="6" t="str">
-        <f>IF(G62&gt;=1500,"High",IF(G62&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Low</v>
       </c>
     </row>
@@ -14899,19 +15060,19 @@
         <v>930.93</v>
       </c>
       <c r="H63" s="6" t="str">
-        <f>PROPER(TRIM(C63))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I63" s="6" t="str">
-        <f>PROPER(TRIM(E63))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J63" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F63,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Business Owner</v>
       </c>
       <c r="K63" s="6" t="str">
-        <f>IF(G63&gt;=1500,"High",IF(G63&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14938,19 +15099,19 @@
         <v>1318.45</v>
       </c>
       <c r="H64" s="6" t="str">
-        <f>PROPER(TRIM(C64))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I64" s="6" t="str">
-        <f>PROPER(TRIM(E64))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J64" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F64,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Self-Employed</v>
       </c>
       <c r="K64" s="6" t="str">
-        <f>IF(G64&gt;=1500,"High",IF(G64&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -14974,19 +15135,19 @@
         <v>920.19</v>
       </c>
       <c r="H65" s="6" t="str">
-        <f>PROPER(TRIM(C65))</f>
+        <f t="shared" si="0"/>
         <v>Male</v>
       </c>
       <c r="I65" s="6" t="str">
-        <f>PROPER(TRIM(E65))</f>
+        <f t="shared" si="1"/>
         <v>Mogadishu</v>
       </c>
       <c r="J65" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F65,"CS","Civil Servant")))</f>
+        <f t="shared" si="2"/>
         <v>Teacher</v>
       </c>
       <c r="K65" s="6" t="str">
-        <f>IF(G65&gt;=1500,"High",IF(G65&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15013,19 +15174,19 @@
         <v>998.38</v>
       </c>
       <c r="H66" s="6" t="str">
-        <f>PROPER(TRIM(C66))</f>
+        <f t="shared" ref="H66:H129" si="4">PROPER(TRIM(C66))</f>
         <v>Female</v>
       </c>
       <c r="I66" s="6" t="str">
-        <f>PROPER(TRIM(E66))</f>
+        <f t="shared" ref="I66:I129" si="5">PROPER(TRIM(E66))</f>
         <v>Mogadishu</v>
       </c>
       <c r="J66" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F66,"CS","Civil Servant")))</f>
+        <f t="shared" ref="J66:J129" si="6">PROPER(TRIM(SUBSTITUTE(F66,"CS","Civil Servant")))</f>
         <v>Engineer</v>
       </c>
       <c r="K66" s="6" t="str">
-        <f>IF(G66&gt;=1500,"High",IF(G66&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K66:K129" si="7">IF(G66&gt;=1500,"High",IF(G66&gt;=800,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -15052,19 +15213,19 @@
         <v>622.54999999999995</v>
       </c>
       <c r="H67" s="6" t="str">
-        <f>PROPER(TRIM(C67))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I67" s="6" t="str">
-        <f>PROPER(TRIM(E67))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J67" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F67,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K67" s="6" t="str">
-        <f>IF(G67&gt;=1500,"High",IF(G67&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15091,19 +15252,19 @@
         <v>781.63</v>
       </c>
       <c r="H68" s="6" t="str">
-        <f>PROPER(TRIM(C68))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I68" s="6" t="str">
-        <f>PROPER(TRIM(E68))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J68" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F68,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K68" s="6" t="str">
-        <f>IF(G68&gt;=1500,"High",IF(G68&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15130,19 +15291,19 @@
         <v>1081.02</v>
       </c>
       <c r="H69" s="6" t="str">
-        <f>PROPER(TRIM(C69))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I69" s="6" t="str">
-        <f>PROPER(TRIM(E69))</f>
+        <f t="shared" si="5"/>
         <v>Missing</v>
       </c>
       <c r="J69" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F69,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Healthcare</v>
       </c>
       <c r="K69" s="6" t="str">
-        <f>IF(G69&gt;=1500,"High",IF(G69&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15169,19 +15330,19 @@
         <v>752.98</v>
       </c>
       <c r="H70" s="6" t="str">
-        <f>PROPER(TRIM(C70))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I70" s="6" t="str">
-        <f>PROPER(TRIM(E70))</f>
+        <f t="shared" si="5"/>
         <v>Missing</v>
       </c>
       <c r="J70" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F70,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K70" s="6" t="str">
-        <f>IF(G70&gt;=1500,"High",IF(G70&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15208,19 +15369,19 @@
         <v>1436.28</v>
       </c>
       <c r="H71" s="6" t="str">
-        <f>PROPER(TRIM(C71))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I71" s="6" t="str">
-        <f>PROPER(TRIM(E71))</f>
+        <f t="shared" si="5"/>
         <v>Missing</v>
       </c>
       <c r="J71" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F71,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K71" s="6" t="str">
-        <f>IF(G71&gt;=1500,"High",IF(G71&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15247,19 +15408,19 @@
         <v>1041.8399999999999</v>
       </c>
       <c r="H72" s="6" t="str">
-        <f>PROPER(TRIM(C72))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I72" s="6" t="str">
-        <f>PROPER(TRIM(E72))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J72" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F72,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K72" s="6" t="str">
-        <f>IF(G72&gt;=1500,"High",IF(G72&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15286,19 +15447,19 @@
         <v>923.87</v>
       </c>
       <c r="H73" s="6" t="str">
-        <f>PROPER(TRIM(C73))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I73" s="6" t="str">
-        <f>PROPER(TRIM(E73))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J73" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F73,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K73" s="6" t="str">
-        <f>IF(G73&gt;=1500,"High",IF(G73&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15325,19 +15486,19 @@
         <v>176.95</v>
       </c>
       <c r="H74" s="6" t="str">
-        <f>PROPER(TRIM(C74))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I74" s="6" t="str">
-        <f>PROPER(TRIM(E74))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J74" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F74,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Missing</v>
       </c>
       <c r="K74" s="6" t="str">
-        <f>IF(G74&gt;=1500,"High",IF(G74&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15364,19 +15525,19 @@
         <v>895.53</v>
       </c>
       <c r="H75" s="6" t="str">
-        <f>PROPER(TRIM(C75))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I75" s="6" t="str">
-        <f>PROPER(TRIM(E75))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J75" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F75,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K75" s="6" t="str">
-        <f>IF(G75&gt;=1500,"High",IF(G75&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15403,19 +15564,19 @@
         <v>519</v>
       </c>
       <c r="H76" s="6" t="str">
-        <f>PROPER(TRIM(C76))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I76" s="6" t="str">
-        <f>PROPER(TRIM(E76))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J76" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F76,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Missing</v>
       </c>
       <c r="K76" s="6" t="str">
-        <f>IF(G76&gt;=1500,"High",IF(G76&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15442,19 +15603,19 @@
         <v>267.12</v>
       </c>
       <c r="H77" s="6" t="str">
-        <f>PROPER(TRIM(C77))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I77" s="6" t="str">
-        <f>PROPER(TRIM(E77))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J77" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F77,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K77" s="6" t="str">
-        <f>IF(G77&gt;=1500,"High",IF(G77&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15481,19 +15642,19 @@
         <v>890.48</v>
       </c>
       <c r="H78" s="6" t="str">
-        <f>PROPER(TRIM(C78))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I78" s="6" t="str">
-        <f>PROPER(TRIM(E78))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J78" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F78,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K78" s="6" t="str">
-        <f>IF(G78&gt;=1500,"High",IF(G78&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15520,19 +15681,19 @@
         <v>836.33</v>
       </c>
       <c r="H79" s="6" t="str">
-        <f>PROPER(TRIM(C79))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I79" s="6" t="str">
-        <f>PROPER(TRIM(E79))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J79" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F79,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K79" s="6" t="str">
-        <f>IF(G79&gt;=1500,"High",IF(G79&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15559,19 +15720,19 @@
         <v>790.75</v>
       </c>
       <c r="H80" s="6" t="str">
-        <f>PROPER(TRIM(C80))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I80" s="6" t="str">
-        <f>PROPER(TRIM(E80))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J80" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F80,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K80" s="6" t="str">
-        <f>IF(G80&gt;=1500,"High",IF(G80&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15598,19 +15759,19 @@
         <v>868.55</v>
       </c>
       <c r="H81" s="6" t="str">
-        <f>PROPER(TRIM(C81))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I81" s="6" t="str">
-        <f>PROPER(TRIM(E81))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J81" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F81,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K81" s="6" t="str">
-        <f>IF(G81&gt;=1500,"High",IF(G81&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15637,19 +15798,19 @@
         <v>1075.0899999999999</v>
       </c>
       <c r="H82" s="6" t="str">
-        <f>PROPER(TRIM(C82))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I82" s="6" t="str">
-        <f>PROPER(TRIM(E82))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J82" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F82,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K82" s="6" t="str">
-        <f>IF(G82&gt;=1500,"High",IF(G82&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15676,19 +15837,19 @@
         <v>706.35</v>
       </c>
       <c r="H83" s="6" t="str">
-        <f>PROPER(TRIM(C83))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I83" s="6" t="str">
-        <f>PROPER(TRIM(E83))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J83" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F83,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K83" s="6" t="str">
-        <f>IF(G83&gt;=1500,"High",IF(G83&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15715,19 +15876,19 @@
         <v>923.87</v>
       </c>
       <c r="H84" s="6" t="str">
-        <f>PROPER(TRIM(C84))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I84" s="6" t="str">
-        <f>PROPER(TRIM(E84))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J84" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F84,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K84" s="6" t="str">
-        <f>IF(G84&gt;=1500,"High",IF(G84&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15754,19 +15915,19 @@
         <v>453.74</v>
       </c>
       <c r="H85" s="6" t="str">
-        <f>PROPER(TRIM(C85))</f>
+        <f t="shared" si="4"/>
         <v>Missing</v>
       </c>
       <c r="I85" s="6" t="str">
-        <f>PROPER(TRIM(E85))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J85" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F85,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K85" s="6" t="str">
-        <f>IF(G85&gt;=1500,"High",IF(G85&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15793,19 +15954,19 @@
         <v>1316.09</v>
       </c>
       <c r="H86" s="6" t="str">
-        <f>PROPER(TRIM(C86))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I86" s="6" t="str">
-        <f>PROPER(TRIM(E86))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J86" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F86,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K86" s="6" t="str">
-        <f>IF(G86&gt;=1500,"High",IF(G86&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15832,19 +15993,19 @@
         <v>921.62</v>
       </c>
       <c r="H87" s="6" t="str">
-        <f>PROPER(TRIM(C87))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I87" s="6" t="str">
-        <f>PROPER(TRIM(E87))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J87" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F87,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K87" s="6" t="str">
-        <f>IF(G87&gt;=1500,"High",IF(G87&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15871,19 +16032,19 @@
         <v>870.42</v>
       </c>
       <c r="H88" s="6" t="str">
-        <f>PROPER(TRIM(C88))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I88" s="6" t="str">
-        <f>PROPER(TRIM(E88))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J88" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F88,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K88" s="6" t="str">
-        <f>IF(G88&gt;=1500,"High",IF(G88&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15910,19 +16071,19 @@
         <v>453.51</v>
       </c>
       <c r="H89" s="6" t="str">
-        <f>PROPER(TRIM(C89))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I89" s="6" t="str">
-        <f>PROPER(TRIM(E89))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J89" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F89,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K89" s="6" t="str">
-        <f>IF(G89&gt;=1500,"High",IF(G89&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -15949,19 +16110,19 @@
         <v>1155.3399999999999</v>
       </c>
       <c r="H90" s="6" t="str">
-        <f>PROPER(TRIM(C90))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I90" s="6" t="str">
-        <f>PROPER(TRIM(E90))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J90" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F90,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Healthcare</v>
       </c>
       <c r="K90" s="6" t="str">
-        <f>IF(G90&gt;=1500,"High",IF(G90&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -15988,19 +16149,19 @@
         <v>256.8</v>
       </c>
       <c r="H91" s="6" t="str">
-        <f>PROPER(TRIM(C91))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I91" s="6" t="str">
-        <f>PROPER(TRIM(E91))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J91" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F91,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K91" s="6" t="str">
-        <f>IF(G91&gt;=1500,"High",IF(G91&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16027,19 +16188,19 @@
         <v>923.87</v>
       </c>
       <c r="H92" s="6" t="str">
-        <f>PROPER(TRIM(C92))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I92" s="6" t="str">
-        <f>PROPER(TRIM(E92))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J92" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F92,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K92" s="6" t="str">
-        <f>IF(G92&gt;=1500,"High",IF(G92&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16066,19 +16227,19 @@
         <v>838.84</v>
       </c>
       <c r="H93" s="6" t="str">
-        <f>PROPER(TRIM(C93))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I93" s="6" t="str">
-        <f>PROPER(TRIM(E93))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J93" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F93,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Missing</v>
       </c>
       <c r="K93" s="6" t="str">
-        <f>IF(G93&gt;=1500,"High",IF(G93&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16105,19 +16266,19 @@
         <v>919.61</v>
       </c>
       <c r="H94" s="6" t="str">
-        <f>PROPER(TRIM(C94))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I94" s="6" t="str">
-        <f>PROPER(TRIM(E94))</f>
+        <f t="shared" si="5"/>
         <v>Garowe</v>
       </c>
       <c r="J94" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F94,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K94" s="6" t="str">
-        <f>IF(G94&gt;=1500,"High",IF(G94&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16144,19 +16305,19 @@
         <v>885.26</v>
       </c>
       <c r="H95" s="6" t="str">
-        <f>PROPER(TRIM(C95))</f>
+        <f t="shared" si="4"/>
         <v>Missing</v>
       </c>
       <c r="I95" s="6" t="str">
-        <f>PROPER(TRIM(E95))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J95" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F95,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K95" s="6" t="str">
-        <f>IF(G95&gt;=1500,"High",IF(G95&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16183,19 +16344,19 @@
         <v>464.6</v>
       </c>
       <c r="H96" s="6" t="str">
-        <f>PROPER(TRIM(C96))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I96" s="6" t="str">
-        <f>PROPER(TRIM(E96))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J96" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F96,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K96" s="6" t="str">
-        <f>IF(G96&gt;=1500,"High",IF(G96&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16222,19 +16383,19 @@
         <v>648.57000000000005</v>
       </c>
       <c r="H97" s="6" t="str">
-        <f>PROPER(TRIM(C97))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I97" s="6" t="str">
-        <f>PROPER(TRIM(E97))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J97" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F97,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K97" s="6" t="str">
-        <f>IF(G97&gt;=1500,"High",IF(G97&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16261,19 +16422,19 @@
         <v>756.75</v>
       </c>
       <c r="H98" s="6" t="str">
-        <f>PROPER(TRIM(C98))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I98" s="6" t="str">
-        <f>PROPER(TRIM(E98))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J98" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F98,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K98" s="6" t="str">
-        <f>IF(G98&gt;=1500,"High",IF(G98&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16300,19 +16461,19 @@
         <v>660.22</v>
       </c>
       <c r="H99" s="6" t="str">
-        <f>PROPER(TRIM(C99))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I99" s="6" t="str">
-        <f>PROPER(TRIM(E99))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J99" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F99,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K99" s="6" t="str">
-        <f>IF(G99&gt;=1500,"High",IF(G99&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16339,19 +16500,19 @@
         <v>275.93</v>
       </c>
       <c r="H100" s="6" t="str">
-        <f>PROPER(TRIM(C100))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I100" s="6" t="str">
-        <f>PROPER(TRIM(E100))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J100" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F100,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K100" s="6" t="str">
-        <f>IF(G100&gt;=1500,"High",IF(G100&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16378,19 +16539,19 @@
         <v>1032.69</v>
       </c>
       <c r="H101" s="6" t="str">
-        <f>PROPER(TRIM(C101))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I101" s="6" t="str">
-        <f>PROPER(TRIM(E101))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J101" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F101,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K101" s="6" t="str">
-        <f>IF(G101&gt;=1500,"High",IF(G101&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16417,19 +16578,19 @@
         <v>648.44000000000005</v>
       </c>
       <c r="H102" s="6" t="str">
-        <f>PROPER(TRIM(C102))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I102" s="6" t="str">
-        <f>PROPER(TRIM(E102))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J102" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F102,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K102" s="6" t="str">
-        <f>IF(G102&gt;=1500,"High",IF(G102&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16456,19 +16617,19 @@
         <v>108.23</v>
       </c>
       <c r="H103" s="6" t="str">
-        <f>PROPER(TRIM(C103))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I103" s="6" t="str">
-        <f>PROPER(TRIM(E103))</f>
+        <f t="shared" si="5"/>
         <v>Bosaso</v>
       </c>
       <c r="J103" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F103,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K103" s="6" t="str">
-        <f>IF(G103&gt;=1500,"High",IF(G103&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16495,19 +16656,19 @@
         <v>1137.1600000000001</v>
       </c>
       <c r="H104" s="6" t="str">
-        <f>PROPER(TRIM(C104))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I104" s="6" t="str">
-        <f>PROPER(TRIM(E104))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J104" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F104,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K104" s="6" t="str">
-        <f>IF(G104&gt;=1500,"High",IF(G104&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16534,19 +16695,19 @@
         <v>152.91999999999999</v>
       </c>
       <c r="H105" s="6" t="str">
-        <f>PROPER(TRIM(C105))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I105" s="6" t="str">
-        <f>PROPER(TRIM(E105))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J105" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F105,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K105" s="6" t="str">
-        <f>IF(G105&gt;=1500,"High",IF(G105&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16573,19 +16734,19 @@
         <v>1421.07</v>
       </c>
       <c r="H106" s="6" t="str">
-        <f>PROPER(TRIM(C106))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I106" s="6" t="str">
-        <f>PROPER(TRIM(E106))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J106" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F106,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K106" s="6" t="str">
-        <f>IF(G106&gt;=1500,"High",IF(G106&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16612,19 +16773,19 @@
         <v>444.76</v>
       </c>
       <c r="H107" s="6" t="str">
-        <f>PROPER(TRIM(C107))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I107" s="6" t="str">
-        <f>PROPER(TRIM(E107))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J107" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F107,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K107" s="6" t="str">
-        <f>IF(G107&gt;=1500,"High",IF(G107&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16651,19 +16812,19 @@
         <v>691.63</v>
       </c>
       <c r="H108" s="6" t="str">
-        <f>PROPER(TRIM(C108))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I108" s="6" t="str">
-        <f>PROPER(TRIM(E108))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J108" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F108,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Missing</v>
       </c>
       <c r="K108" s="6" t="str">
-        <f>IF(G108&gt;=1500,"High",IF(G108&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16690,19 +16851,19 @@
         <v>785.37</v>
       </c>
       <c r="H109" s="6" t="str">
-        <f>PROPER(TRIM(C109))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I109" s="6" t="str">
-        <f>PROPER(TRIM(E109))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J109" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F109,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K109" s="6" t="str">
-        <f>IF(G109&gt;=1500,"High",IF(G109&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16729,19 +16890,19 @@
         <v>856.56</v>
       </c>
       <c r="H110" s="6" t="str">
-        <f>PROPER(TRIM(C110))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I110" s="6" t="str">
-        <f>PROPER(TRIM(E110))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J110" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F110,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K110" s="6" t="str">
-        <f>IF(G110&gt;=1500,"High",IF(G110&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16768,19 +16929,19 @@
         <v>167.65</v>
       </c>
       <c r="H111" s="6" t="str">
-        <f>PROPER(TRIM(C111))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I111" s="6" t="str">
-        <f>PROPER(TRIM(E111))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J111" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F111,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K111" s="6" t="str">
-        <f>IF(G111&gt;=1500,"High",IF(G111&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16807,19 +16968,19 @@
         <v>1064.4100000000001</v>
       </c>
       <c r="H112" s="6" t="str">
-        <f>PROPER(TRIM(C112))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I112" s="6" t="str">
-        <f>PROPER(TRIM(E112))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J112" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F112,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Healthcare</v>
       </c>
       <c r="K112" s="6" t="str">
-        <f>IF(G112&gt;=1500,"High",IF(G112&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16846,19 +17007,19 @@
         <v>839.71</v>
       </c>
       <c r="H113" s="6" t="str">
-        <f>PROPER(TRIM(C113))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I113" s="6" t="str">
-        <f>PROPER(TRIM(E113))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J113" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F113,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K113" s="6" t="str">
-        <f>IF(G113&gt;=1500,"High",IF(G113&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16885,19 +17046,19 @@
         <v>481.21</v>
       </c>
       <c r="H114" s="6" t="str">
-        <f>PROPER(TRIM(C114))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I114" s="6" t="str">
-        <f>PROPER(TRIM(E114))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J114" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F114,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Missing</v>
       </c>
       <c r="K114" s="6" t="str">
-        <f>IF(G114&gt;=1500,"High",IF(G114&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -16924,19 +17085,19 @@
         <v>923.87</v>
       </c>
       <c r="H115" s="6" t="str">
-        <f>PROPER(TRIM(C115))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I115" s="6" t="str">
-        <f>PROPER(TRIM(E115))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J115" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F115,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Civil Servant</v>
       </c>
       <c r="K115" s="6" t="str">
-        <f>IF(G115&gt;=1500,"High",IF(G115&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -16963,19 +17124,19 @@
         <v>923.87</v>
       </c>
       <c r="H116" s="6" t="str">
-        <f>PROPER(TRIM(C116))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I116" s="6" t="str">
-        <f>PROPER(TRIM(E116))</f>
+        <f t="shared" si="5"/>
         <v>Bosaso</v>
       </c>
       <c r="J116" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F116,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K116" s="6" t="str">
-        <f>IF(G116&gt;=1500,"High",IF(G116&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17002,19 +17163,19 @@
         <v>818.19</v>
       </c>
       <c r="H117" s="6" t="str">
-        <f>PROPER(TRIM(C117))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I117" s="6" t="str">
-        <f>PROPER(TRIM(E117))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J117" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F117,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K117" s="6" t="str">
-        <f>IF(G117&gt;=1500,"High",IF(G117&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17041,19 +17202,19 @@
         <v>923.87</v>
       </c>
       <c r="H118" s="6" t="str">
-        <f>PROPER(TRIM(C118))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I118" s="6" t="str">
-        <f>PROPER(TRIM(E118))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J118" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F118,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K118" s="6" t="str">
-        <f>IF(G118&gt;=1500,"High",IF(G118&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17077,19 +17238,19 @@
         <v>944.96</v>
       </c>
       <c r="H119" s="6" t="str">
-        <f>PROPER(TRIM(C119))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I119" s="6" t="str">
-        <f>PROPER(TRIM(E119))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J119" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F119,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K119" s="6" t="str">
-        <f>IF(G119&gt;=1500,"High",IF(G119&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17116,19 +17277,19 @@
         <v>1672.71</v>
       </c>
       <c r="H120" s="6" t="str">
-        <f>PROPER(TRIM(C120))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I120" s="6" t="str">
-        <f>PROPER(TRIM(E120))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J120" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F120,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K120" s="6" t="str">
-        <f>IF(G120&gt;=1500,"High",IF(G120&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>High</v>
       </c>
     </row>
@@ -17155,19 +17316,19 @@
         <v>665.8</v>
       </c>
       <c r="H121" s="6" t="str">
-        <f>PROPER(TRIM(C121))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I121" s="6" t="str">
-        <f>PROPER(TRIM(E121))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J121" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F121,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K121" s="6" t="str">
-        <f>IF(G121&gt;=1500,"High",IF(G121&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -17194,19 +17355,19 @@
         <v>183.1</v>
       </c>
       <c r="H122" s="6" t="str">
-        <f>PROPER(TRIM(C122))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I122" s="6" t="str">
-        <f>PROPER(TRIM(E122))</f>
+        <f t="shared" si="5"/>
         <v>Missing</v>
       </c>
       <c r="J122" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F122,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K122" s="6" t="str">
-        <f>IF(G122&gt;=1500,"High",IF(G122&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -17233,19 +17394,19 @@
         <v>961.13</v>
       </c>
       <c r="H123" s="6" t="str">
-        <f>PROPER(TRIM(C123))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I123" s="6" t="str">
-        <f>PROPER(TRIM(E123))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J123" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F123,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K123" s="6" t="str">
-        <f>IF(G123&gt;=1500,"High",IF(G123&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17272,19 +17433,19 @@
         <v>1429.26</v>
       </c>
       <c r="H124" s="6" t="str">
-        <f>PROPER(TRIM(C124))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I124" s="6" t="str">
-        <f>PROPER(TRIM(E124))</f>
+        <f t="shared" si="5"/>
         <v>Baidoa</v>
       </c>
       <c r="J124" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F124,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K124" s="6" t="str">
-        <f>IF(G124&gt;=1500,"High",IF(G124&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17311,19 +17472,19 @@
         <v>1300.01</v>
       </c>
       <c r="H125" s="6" t="str">
-        <f>PROPER(TRIM(C125))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I125" s="6" t="str">
-        <f>PROPER(TRIM(E125))</f>
+        <f t="shared" si="5"/>
         <v>Mogadishu</v>
       </c>
       <c r="J125" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F125,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Business Owner</v>
       </c>
       <c r="K125" s="6" t="str">
-        <f>IF(G125&gt;=1500,"High",IF(G125&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17350,19 +17511,19 @@
         <v>1610.81</v>
       </c>
       <c r="H126" s="6" t="str">
-        <f>PROPER(TRIM(C126))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I126" s="6" t="str">
-        <f>PROPER(TRIM(E126))</f>
+        <f t="shared" si="5"/>
         <v>Kismayo</v>
       </c>
       <c r="J126" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F126,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Engineer</v>
       </c>
       <c r="K126" s="6" t="str">
-        <f>IF(G126&gt;=1500,"High",IF(G126&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>High</v>
       </c>
     </row>
@@ -17389,19 +17550,19 @@
         <v>508.66</v>
       </c>
       <c r="H127" s="6" t="str">
-        <f>PROPER(TRIM(C127))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I127" s="6" t="str">
-        <f>PROPER(TRIM(E127))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J127" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F127,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Teacher</v>
       </c>
       <c r="K127" s="6" t="str">
-        <f>IF(G127&gt;=1500,"High",IF(G127&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -17428,19 +17589,19 @@
         <v>712.55</v>
       </c>
       <c r="H128" s="6" t="str">
-        <f>PROPER(TRIM(C128))</f>
+        <f t="shared" si="4"/>
         <v>Female</v>
       </c>
       <c r="I128" s="6" t="str">
-        <f>PROPER(TRIM(E128))</f>
+        <f t="shared" si="5"/>
         <v>Hargeisa</v>
       </c>
       <c r="J128" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F128,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Self-Employed</v>
       </c>
       <c r="K128" s="6" t="str">
-        <f>IF(G128&gt;=1500,"High",IF(G128&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Low</v>
       </c>
     </row>
@@ -17467,19 +17628,19 @@
         <v>923.87</v>
       </c>
       <c r="H129" s="6" t="str">
-        <f>PROPER(TRIM(C129))</f>
+        <f t="shared" si="4"/>
         <v>Male</v>
       </c>
       <c r="I129" s="6" t="str">
-        <f>PROPER(TRIM(E129))</f>
+        <f t="shared" si="5"/>
         <v>Missing</v>
       </c>
       <c r="J129" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F129,"CS","Civil Servant")))</f>
+        <f t="shared" si="6"/>
         <v>Student</v>
       </c>
       <c r="K129" s="6" t="str">
-        <f>IF(G129&gt;=1500,"High",IF(G129&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17506,19 +17667,19 @@
         <v>1126.8900000000001</v>
       </c>
       <c r="H130" s="6" t="str">
-        <f>PROPER(TRIM(C130))</f>
+        <f t="shared" ref="H130:H193" si="8">PROPER(TRIM(C130))</f>
         <v>Male</v>
       </c>
       <c r="I130" s="6" t="str">
-        <f>PROPER(TRIM(E130))</f>
+        <f t="shared" ref="I130:I193" si="9">PROPER(TRIM(E130))</f>
         <v>Kismayo</v>
       </c>
       <c r="J130" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F130,"CS","Civil Servant")))</f>
+        <f t="shared" ref="J130:J193" si="10">PROPER(TRIM(SUBSTITUTE(F130,"CS","Civil Servant")))</f>
         <v>Healthcare</v>
       </c>
       <c r="K130" s="6" t="str">
-        <f>IF(G130&gt;=1500,"High",IF(G130&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K130:K193" si="11">IF(G130&gt;=1500,"High",IF(G130&gt;=800,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -17545,19 +17706,19 @@
         <v>895.93</v>
       </c>
       <c r="H131" s="6" t="str">
-        <f>PROPER(TRIM(C131))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I131" s="6" t="str">
-        <f>PROPER(TRIM(E131))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J131" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F131,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K131" s="6" t="str">
-        <f>IF(G131&gt;=1500,"High",IF(G131&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17584,19 +17745,19 @@
         <v>1386</v>
       </c>
       <c r="H132" s="6" t="str">
-        <f>PROPER(TRIM(C132))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I132" s="6" t="str">
-        <f>PROPER(TRIM(E132))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J132" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F132,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K132" s="6" t="str">
-        <f>IF(G132&gt;=1500,"High",IF(G132&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17623,19 +17784,19 @@
         <v>923.87</v>
       </c>
       <c r="H133" s="6" t="str">
-        <f>PROPER(TRIM(C133))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I133" s="6" t="str">
-        <f>PROPER(TRIM(E133))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J133" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F133,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K133" s="6" t="str">
-        <f>IF(G133&gt;=1500,"High",IF(G133&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17662,19 +17823,19 @@
         <v>1481.76</v>
       </c>
       <c r="H134" s="6" t="str">
-        <f>PROPER(TRIM(C134))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I134" s="6" t="str">
-        <f>PROPER(TRIM(E134))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J134" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F134,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K134" s="6" t="str">
-        <f>IF(G134&gt;=1500,"High",IF(G134&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17701,19 +17862,19 @@
         <v>828.77</v>
       </c>
       <c r="H135" s="6" t="str">
-        <f>PROPER(TRIM(C135))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I135" s="6" t="str">
-        <f>PROPER(TRIM(E135))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J135" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F135,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K135" s="6" t="str">
-        <f>IF(G135&gt;=1500,"High",IF(G135&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17740,19 +17901,19 @@
         <v>721.11</v>
       </c>
       <c r="H136" s="6" t="str">
-        <f>PROPER(TRIM(C136))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I136" s="6" t="str">
-        <f>PROPER(TRIM(E136))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J136" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F136,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Missing</v>
       </c>
       <c r="K136" s="6" t="str">
-        <f>IF(G136&gt;=1500,"High",IF(G136&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -17779,19 +17940,19 @@
         <v>911.36</v>
       </c>
       <c r="H137" s="6" t="str">
-        <f>PROPER(TRIM(C137))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I137" s="6" t="str">
-        <f>PROPER(TRIM(E137))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J137" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F137,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Missing</v>
       </c>
       <c r="K137" s="6" t="str">
-        <f>IF(G137&gt;=1500,"High",IF(G137&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17815,19 +17976,19 @@
         <v>1614.28</v>
       </c>
       <c r="H138" s="6" t="str">
-        <f>PROPER(TRIM(C138))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I138" s="6" t="str">
-        <f>PROPER(TRIM(E138))</f>
+        <f t="shared" si="9"/>
         <v>Garowe</v>
       </c>
       <c r="J138" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F138,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K138" s="6" t="str">
-        <f>IF(G138&gt;=1500,"High",IF(G138&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>High</v>
       </c>
     </row>
@@ -17854,19 +18015,19 @@
         <v>1156.93</v>
       </c>
       <c r="H139" s="6" t="str">
-        <f>PROPER(TRIM(C139))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I139" s="6" t="str">
-        <f>PROPER(TRIM(E139))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J139" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F139,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K139" s="6" t="str">
-        <f>IF(G139&gt;=1500,"High",IF(G139&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17893,19 +18054,19 @@
         <v>1425.97</v>
       </c>
       <c r="H140" s="6" t="str">
-        <f>PROPER(TRIM(C140))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I140" s="6" t="str">
-        <f>PROPER(TRIM(E140))</f>
+        <f t="shared" si="9"/>
         <v>Baidoa</v>
       </c>
       <c r="J140" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F140,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K140" s="6" t="str">
-        <f>IF(G140&gt;=1500,"High",IF(G140&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -17932,19 +18093,19 @@
         <v>677.55</v>
       </c>
       <c r="H141" s="6" t="str">
-        <f>PROPER(TRIM(C141))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I141" s="6" t="str">
-        <f>PROPER(TRIM(E141))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J141" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F141,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K141" s="6" t="str">
-        <f>IF(G141&gt;=1500,"High",IF(G141&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -17971,19 +18132,19 @@
         <v>916.62</v>
       </c>
       <c r="H142" s="6" t="str">
-        <f>PROPER(TRIM(C142))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I142" s="6" t="str">
-        <f>PROPER(TRIM(E142))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J142" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F142,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K142" s="6" t="str">
-        <f>IF(G142&gt;=1500,"High",IF(G142&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18010,19 +18171,19 @@
         <v>1013.28</v>
       </c>
       <c r="H143" s="6" t="str">
-        <f>PROPER(TRIM(C143))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I143" s="6" t="str">
-        <f>PROPER(TRIM(E143))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J143" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F143,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K143" s="6" t="str">
-        <f>IF(G143&gt;=1500,"High",IF(G143&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18049,19 +18210,19 @@
         <v>656.1</v>
       </c>
       <c r="H144" s="6" t="str">
-        <f>PROPER(TRIM(C144))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I144" s="6" t="str">
-        <f>PROPER(TRIM(E144))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J144" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F144,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K144" s="6" t="str">
-        <f>IF(G144&gt;=1500,"High",IF(G144&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18088,19 +18249,19 @@
         <v>667.7</v>
       </c>
       <c r="H145" s="6" t="str">
-        <f>PROPER(TRIM(C145))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I145" s="6" t="str">
-        <f>PROPER(TRIM(E145))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J145" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F145,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Missing</v>
       </c>
       <c r="K145" s="6" t="str">
-        <f>IF(G145&gt;=1500,"High",IF(G145&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18127,19 +18288,19 @@
         <v>969.34</v>
       </c>
       <c r="H146" s="6" t="str">
-        <f>PROPER(TRIM(C146))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I146" s="6" t="str">
-        <f>PROPER(TRIM(E146))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J146" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F146,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K146" s="6" t="str">
-        <f>IF(G146&gt;=1500,"High",IF(G146&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18166,19 +18327,19 @@
         <v>843.99</v>
       </c>
       <c r="H147" s="6" t="str">
-        <f>PROPER(TRIM(C147))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I147" s="6" t="str">
-        <f>PROPER(TRIM(E147))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J147" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F147,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Missing</v>
       </c>
       <c r="K147" s="6" t="str">
-        <f>IF(G147&gt;=1500,"High",IF(G147&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18205,19 +18366,19 @@
         <v>1332.38</v>
       </c>
       <c r="H148" s="6" t="str">
-        <f>PROPER(TRIM(C148))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I148" s="6" t="str">
-        <f>PROPER(TRIM(E148))</f>
+        <f t="shared" si="9"/>
         <v>Garowe</v>
       </c>
       <c r="J148" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F148,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K148" s="6" t="str">
-        <f>IF(G148&gt;=1500,"High",IF(G148&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18244,19 +18405,19 @@
         <v>1108.6199999999999</v>
       </c>
       <c r="H149" s="6" t="str">
-        <f>PROPER(TRIM(C149))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I149" s="6" t="str">
-        <f>PROPER(TRIM(E149))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J149" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F149,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K149" s="6" t="str">
-        <f>IF(G149&gt;=1500,"High",IF(G149&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18283,19 +18444,19 @@
         <v>897.29</v>
       </c>
       <c r="H150" s="6" t="str">
-        <f>PROPER(TRIM(C150))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I150" s="6" t="str">
-        <f>PROPER(TRIM(E150))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J150" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F150,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K150" s="6" t="str">
-        <f>IF(G150&gt;=1500,"High",IF(G150&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18322,19 +18483,19 @@
         <v>265.52</v>
       </c>
       <c r="H151" s="6" t="str">
-        <f>PROPER(TRIM(C151))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I151" s="6" t="str">
-        <f>PROPER(TRIM(E151))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J151" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F151,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K151" s="6" t="str">
-        <f>IF(G151&gt;=1500,"High",IF(G151&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18361,19 +18522,19 @@
         <v>316.74</v>
       </c>
       <c r="H152" s="6" t="str">
-        <f>PROPER(TRIM(C152))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I152" s="6" t="str">
-        <f>PROPER(TRIM(E152))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J152" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F152,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K152" s="6" t="str">
-        <f>IF(G152&gt;=1500,"High",IF(G152&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18400,19 +18561,19 @@
         <v>438.08</v>
       </c>
       <c r="H153" s="6" t="str">
-        <f>PROPER(TRIM(C153))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I153" s="6" t="str">
-        <f>PROPER(TRIM(E153))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J153" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F153,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K153" s="6" t="str">
-        <f>IF(G153&gt;=1500,"High",IF(G153&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18439,19 +18600,19 @@
         <v>1155.95</v>
       </c>
       <c r="H154" s="6" t="str">
-        <f>PROPER(TRIM(C154))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I154" s="6" t="str">
-        <f>PROPER(TRIM(E154))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J154" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F154,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K154" s="6" t="str">
-        <f>IF(G154&gt;=1500,"High",IF(G154&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18478,19 +18639,19 @@
         <v>796.52</v>
       </c>
       <c r="H155" s="6" t="str">
-        <f>PROPER(TRIM(C155))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I155" s="6" t="str">
-        <f>PROPER(TRIM(E155))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J155" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F155,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K155" s="6" t="str">
-        <f>IF(G155&gt;=1500,"High",IF(G155&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18514,19 +18675,19 @@
         <v>1200.17</v>
       </c>
       <c r="H156" s="6" t="str">
-        <f>PROPER(TRIM(C156))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I156" s="6" t="str">
-        <f>PROPER(TRIM(E156))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J156" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F156,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K156" s="6" t="str">
-        <f>IF(G156&gt;=1500,"High",IF(G156&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18553,19 +18714,19 @@
         <v>1996.92</v>
       </c>
       <c r="H157" s="6" t="str">
-        <f>PROPER(TRIM(C157))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I157" s="6" t="str">
-        <f>PROPER(TRIM(E157))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J157" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F157,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K157" s="6" t="str">
-        <f>IF(G157&gt;=1500,"High",IF(G157&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>High</v>
       </c>
     </row>
@@ -18592,19 +18753,19 @@
         <v>896.23</v>
       </c>
       <c r="H158" s="6" t="str">
-        <f>PROPER(TRIM(C158))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I158" s="6" t="str">
-        <f>PROPER(TRIM(E158))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J158" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F158,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K158" s="6" t="str">
-        <f>IF(G158&gt;=1500,"High",IF(G158&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18631,19 +18792,19 @@
         <v>295.45</v>
       </c>
       <c r="H159" s="6" t="str">
-        <f>PROPER(TRIM(C159))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I159" s="6" t="str">
-        <f>PROPER(TRIM(E159))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J159" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F159,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K159" s="6" t="str">
-        <f>IF(G159&gt;=1500,"High",IF(G159&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18670,19 +18831,19 @@
         <v>862.99</v>
       </c>
       <c r="H160" s="6" t="str">
-        <f>PROPER(TRIM(C160))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I160" s="6" t="str">
-        <f>PROPER(TRIM(E160))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J160" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F160,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K160" s="6" t="str">
-        <f>IF(G160&gt;=1500,"High",IF(G160&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18706,19 +18867,19 @@
         <v>947.64</v>
       </c>
       <c r="H161" s="6" t="str">
-        <f>PROPER(TRIM(C161))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I161" s="6" t="str">
-        <f>PROPER(TRIM(E161))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J161" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F161,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K161" s="6" t="str">
-        <f>IF(G161&gt;=1500,"High",IF(G161&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18745,19 +18906,19 @@
         <v>265.83999999999997</v>
       </c>
       <c r="H162" s="6" t="str">
-        <f>PROPER(TRIM(C162))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I162" s="6" t="str">
-        <f>PROPER(TRIM(E162))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J162" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F162,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K162" s="6" t="str">
-        <f>IF(G162&gt;=1500,"High",IF(G162&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18784,19 +18945,19 @@
         <v>728.45</v>
       </c>
       <c r="H163" s="6" t="str">
-        <f>PROPER(TRIM(C163))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I163" s="6" t="str">
-        <f>PROPER(TRIM(E163))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J163" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F163,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K163" s="6" t="str">
-        <f>IF(G163&gt;=1500,"High",IF(G163&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18823,19 +18984,19 @@
         <v>463.46</v>
       </c>
       <c r="H164" s="6" t="str">
-        <f>PROPER(TRIM(C164))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I164" s="6" t="str">
-        <f>PROPER(TRIM(E164))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J164" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F164,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K164" s="6" t="str">
-        <f>IF(G164&gt;=1500,"High",IF(G164&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18862,19 +19023,19 @@
         <v>1234.8800000000001</v>
       </c>
       <c r="H165" s="6" t="str">
-        <f>PROPER(TRIM(C165))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I165" s="6" t="str">
-        <f>PROPER(TRIM(E165))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J165" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F165,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K165" s="6" t="str">
-        <f>IF(G165&gt;=1500,"High",IF(G165&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -18901,19 +19062,19 @@
         <v>790.7</v>
       </c>
       <c r="H166" s="6" t="str">
-        <f>PROPER(TRIM(C166))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I166" s="6" t="str">
-        <f>PROPER(TRIM(E166))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J166" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F166,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K166" s="6" t="str">
-        <f>IF(G166&gt;=1500,"High",IF(G166&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18940,19 +19101,19 @@
         <v>415.78</v>
       </c>
       <c r="H167" s="6" t="str">
-        <f>PROPER(TRIM(C167))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I167" s="6" t="str">
-        <f>PROPER(TRIM(E167))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J167" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F167,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K167" s="6" t="str">
-        <f>IF(G167&gt;=1500,"High",IF(G167&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -18979,19 +19140,19 @@
         <v>872.34</v>
       </c>
       <c r="H168" s="6" t="str">
-        <f>PROPER(TRIM(C168))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I168" s="6" t="str">
-        <f>PROPER(TRIM(E168))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J168" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F168,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K168" s="6" t="str">
-        <f>IF(G168&gt;=1500,"High",IF(G168&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19018,19 +19179,19 @@
         <v>395.84</v>
       </c>
       <c r="H169" s="6" t="str">
-        <f>PROPER(TRIM(C169))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I169" s="6" t="str">
-        <f>PROPER(TRIM(E169))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J169" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F169,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Civil Servant</v>
       </c>
       <c r="K169" s="6" t="str">
-        <f>IF(G169&gt;=1500,"High",IF(G169&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19057,19 +19218,19 @@
         <v>247.93</v>
       </c>
       <c r="H170" s="6" t="str">
-        <f>PROPER(TRIM(C170))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I170" s="6" t="str">
-        <f>PROPER(TRIM(E170))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J170" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F170,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K170" s="6" t="str">
-        <f>IF(G170&gt;=1500,"High",IF(G170&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19096,19 +19257,19 @@
         <v>1045.8599999999999</v>
       </c>
       <c r="H171" s="6" t="str">
-        <f>PROPER(TRIM(C171))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I171" s="6" t="str">
-        <f>PROPER(TRIM(E171))</f>
+        <f t="shared" si="9"/>
         <v>Baidoa</v>
       </c>
       <c r="J171" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F171,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K171" s="6" t="str">
-        <f>IF(G171&gt;=1500,"High",IF(G171&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19132,19 +19293,19 @@
         <v>1396.84</v>
       </c>
       <c r="H172" s="6" t="str">
-        <f>PROPER(TRIM(C172))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I172" s="6" t="str">
-        <f>PROPER(TRIM(E172))</f>
+        <f t="shared" si="9"/>
         <v>Baidoa</v>
       </c>
       <c r="J172" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F172,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K172" s="6" t="str">
-        <f>IF(G172&gt;=1500,"High",IF(G172&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19171,19 +19332,19 @@
         <v>1086.6400000000001</v>
       </c>
       <c r="H173" s="6" t="str">
-        <f>PROPER(TRIM(C173))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I173" s="6" t="str">
-        <f>PROPER(TRIM(E173))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J173" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F173,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K173" s="6" t="str">
-        <f>IF(G173&gt;=1500,"High",IF(G173&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19210,19 +19371,19 @@
         <v>923.87</v>
       </c>
       <c r="H174" s="6" t="str">
-        <f>PROPER(TRIM(C174))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I174" s="6" t="str">
-        <f>PROPER(TRIM(E174))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J174" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F174,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K174" s="6" t="str">
-        <f>IF(G174&gt;=1500,"High",IF(G174&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19249,19 +19410,19 @@
         <v>797.52</v>
       </c>
       <c r="H175" s="6" t="str">
-        <f>PROPER(TRIM(C175))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I175" s="6" t="str">
-        <f>PROPER(TRIM(E175))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J175" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F175,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K175" s="6" t="str">
-        <f>IF(G175&gt;=1500,"High",IF(G175&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19288,19 +19449,19 @@
         <v>374.63</v>
       </c>
       <c r="H176" s="6" t="str">
-        <f>PROPER(TRIM(C176))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I176" s="6" t="str">
-        <f>PROPER(TRIM(E176))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J176" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F176,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K176" s="6" t="str">
-        <f>IF(G176&gt;=1500,"High",IF(G176&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19327,19 +19488,19 @@
         <v>1651.76</v>
       </c>
       <c r="H177" s="6" t="str">
-        <f>PROPER(TRIM(C177))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I177" s="6" t="str">
-        <f>PROPER(TRIM(E177))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J177" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F177,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K177" s="6" t="str">
-        <f>IF(G177&gt;=1500,"High",IF(G177&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>High</v>
       </c>
     </row>
@@ -19366,19 +19527,19 @@
         <v>853.86</v>
       </c>
       <c r="H178" s="6" t="str">
-        <f>PROPER(TRIM(C178))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I178" s="6" t="str">
-        <f>PROPER(TRIM(E178))</f>
+        <f t="shared" si="9"/>
         <v>Garowe</v>
       </c>
       <c r="J178" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F178,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K178" s="6" t="str">
-        <f>IF(G178&gt;=1500,"High",IF(G178&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19405,19 +19566,19 @@
         <v>1210.32</v>
       </c>
       <c r="H179" s="6" t="str">
-        <f>PROPER(TRIM(C179))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I179" s="6" t="str">
-        <f>PROPER(TRIM(E179))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J179" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F179,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K179" s="6" t="str">
-        <f>IF(G179&gt;=1500,"High",IF(G179&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19444,19 +19605,19 @@
         <v>624.91999999999996</v>
       </c>
       <c r="H180" s="6" t="str">
-        <f>PROPER(TRIM(C180))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I180" s="6" t="str">
-        <f>PROPER(TRIM(E180))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J180" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F180,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K180" s="6" t="str">
-        <f>IF(G180&gt;=1500,"High",IF(G180&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19483,19 +19644,19 @@
         <v>1229.76</v>
       </c>
       <c r="H181" s="6" t="str">
-        <f>PROPER(TRIM(C181))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I181" s="6" t="str">
-        <f>PROPER(TRIM(E181))</f>
+        <f t="shared" si="9"/>
         <v>Kismayo</v>
       </c>
       <c r="J181" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F181,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K181" s="6" t="str">
-        <f>IF(G181&gt;=1500,"High",IF(G181&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19522,19 +19683,19 @@
         <v>481.99</v>
       </c>
       <c r="H182" s="6" t="str">
-        <f>PROPER(TRIM(C182))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I182" s="6" t="str">
-        <f>PROPER(TRIM(E182))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J182" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F182,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K182" s="6" t="str">
-        <f>IF(G182&gt;=1500,"High",IF(G182&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19561,19 +19722,19 @@
         <v>638.53</v>
       </c>
       <c r="H183" s="6" t="str">
-        <f>PROPER(TRIM(C183))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I183" s="6" t="str">
-        <f>PROPER(TRIM(E183))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J183" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F183,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K183" s="6" t="str">
-        <f>IF(G183&gt;=1500,"High",IF(G183&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19600,19 +19761,19 @@
         <v>1509.47</v>
       </c>
       <c r="H184" s="6" t="str">
-        <f>PROPER(TRIM(C184))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I184" s="6" t="str">
-        <f>PROPER(TRIM(E184))</f>
+        <f t="shared" si="9"/>
         <v>Missing</v>
       </c>
       <c r="J184" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F184,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K184" s="6" t="str">
-        <f>IF(G184&gt;=1500,"High",IF(G184&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>High</v>
       </c>
     </row>
@@ -19639,19 +19800,19 @@
         <v>775.19</v>
       </c>
       <c r="H185" s="6" t="str">
-        <f>PROPER(TRIM(C185))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I185" s="6" t="str">
-        <f>PROPER(TRIM(E185))</f>
+        <f t="shared" si="9"/>
         <v>Hargeisa</v>
       </c>
       <c r="J185" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F185,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K185" s="6" t="str">
-        <f>IF(G185&gt;=1500,"High",IF(G185&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19678,19 +19839,19 @@
         <v>599.34</v>
       </c>
       <c r="H186" s="6" t="str">
-        <f>PROPER(TRIM(C186))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I186" s="6" t="str">
-        <f>PROPER(TRIM(E186))</f>
+        <f t="shared" si="9"/>
         <v>Baidoa</v>
       </c>
       <c r="J186" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F186,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Engineer</v>
       </c>
       <c r="K186" s="6" t="str">
-        <f>IF(G186&gt;=1500,"High",IF(G186&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19717,19 +19878,19 @@
         <v>175.19</v>
       </c>
       <c r="H187" s="6" t="str">
-        <f>PROPER(TRIM(C187))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I187" s="6" t="str">
-        <f>PROPER(TRIM(E187))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J187" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F187,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Student</v>
       </c>
       <c r="K187" s="6" t="str">
-        <f>IF(G187&gt;=1500,"High",IF(G187&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19756,19 +19917,19 @@
         <v>748.35</v>
       </c>
       <c r="H188" s="6" t="str">
-        <f>PROPER(TRIM(C188))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I188" s="6" t="str">
-        <f>PROPER(TRIM(E188))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J188" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F188,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K188" s="6" t="str">
-        <f>IF(G188&gt;=1500,"High",IF(G188&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19795,19 +19956,19 @@
         <v>924.95</v>
       </c>
       <c r="H189" s="6" t="str">
-        <f>PROPER(TRIM(C189))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I189" s="6" t="str">
-        <f>PROPER(TRIM(E189))</f>
+        <f t="shared" si="9"/>
         <v>Bosaso</v>
       </c>
       <c r="J189" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F189,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Business Owner</v>
       </c>
       <c r="K189" s="6" t="str">
-        <f>IF(G189&gt;=1500,"High",IF(G189&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19834,19 +19995,19 @@
         <v>853.76</v>
       </c>
       <c r="H190" s="6" t="str">
-        <f>PROPER(TRIM(C190))</f>
+        <f t="shared" si="8"/>
         <v>Male</v>
       </c>
       <c r="I190" s="6" t="str">
-        <f>PROPER(TRIM(E190))</f>
+        <f t="shared" si="9"/>
         <v>Garowe</v>
       </c>
       <c r="J190" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F190,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Healthcare</v>
       </c>
       <c r="K190" s="6" t="str">
-        <f>IF(G190&gt;=1500,"High",IF(G190&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19873,19 +20034,19 @@
         <v>790.38</v>
       </c>
       <c r="H191" s="6" t="str">
-        <f>PROPER(TRIM(C191))</f>
+        <f t="shared" si="8"/>
         <v>Missing</v>
       </c>
       <c r="I191" s="6" t="str">
-        <f>PROPER(TRIM(E191))</f>
+        <f t="shared" si="9"/>
         <v>Mogadishu</v>
       </c>
       <c r="J191" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F191,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Teacher</v>
       </c>
       <c r="K191" s="6" t="str">
-        <f>IF(G191&gt;=1500,"High",IF(G191&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19912,19 +20073,19 @@
         <v>455.83</v>
       </c>
       <c r="H192" s="6" t="str">
-        <f>PROPER(TRIM(C192))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I192" s="6" t="str">
-        <f>PROPER(TRIM(E192))</f>
+        <f t="shared" si="9"/>
         <v>Baidoa</v>
       </c>
       <c r="J192" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F192,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K192" s="6" t="str">
-        <f>IF(G192&gt;=1500,"High",IF(G192&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Low</v>
       </c>
     </row>
@@ -19951,19 +20112,19 @@
         <v>810.64</v>
       </c>
       <c r="H193" s="6" t="str">
-        <f>PROPER(TRIM(C193))</f>
+        <f t="shared" si="8"/>
         <v>Female</v>
       </c>
       <c r="I193" s="6" t="str">
-        <f>PROPER(TRIM(E193))</f>
+        <f t="shared" si="9"/>
         <v>Missing</v>
       </c>
       <c r="J193" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F193,"CS","Civil Servant")))</f>
+        <f t="shared" si="10"/>
         <v>Self-Employed</v>
       </c>
       <c r="K193" s="6" t="str">
-        <f>IF(G193&gt;=1500,"High",IF(G193&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
     </row>
@@ -19990,19 +20151,19 @@
         <v>128.41999999999999</v>
       </c>
       <c r="H194" s="6" t="str">
-        <f>PROPER(TRIM(C194))</f>
+        <f t="shared" ref="H194:H257" si="12">PROPER(TRIM(C194))</f>
         <v>Female</v>
       </c>
       <c r="I194" s="6" t="str">
-        <f>PROPER(TRIM(E194))</f>
+        <f t="shared" ref="I194:I257" si="13">PROPER(TRIM(E194))</f>
         <v>Baidoa</v>
       </c>
       <c r="J194" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F194,"CS","Civil Servant")))</f>
+        <f t="shared" ref="J194:J257" si="14">PROPER(TRIM(SUBSTITUTE(F194,"CS","Civil Servant")))</f>
         <v>Student</v>
       </c>
       <c r="K194" s="6" t="str">
-        <f>IF(G194&gt;=1500,"High",IF(G194&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K194:K257" si="15">IF(G194&gt;=1500,"High",IF(G194&gt;=800,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
@@ -20029,19 +20190,19 @@
         <v>1956.52</v>
       </c>
       <c r="H195" s="6" t="str">
-        <f>PROPER(TRIM(C195))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I195" s="6" t="str">
-        <f>PROPER(TRIM(E195))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J195" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F195,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K195" s="6" t="str">
-        <f>IF(G195&gt;=1500,"High",IF(G195&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>High</v>
       </c>
     </row>
@@ -20068,19 +20229,19 @@
         <v>845.86</v>
       </c>
       <c r="H196" s="6" t="str">
-        <f>PROPER(TRIM(C196))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I196" s="6" t="str">
-        <f>PROPER(TRIM(E196))</f>
+        <f t="shared" si="13"/>
         <v>Baidoa</v>
       </c>
       <c r="J196" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F196,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K196" s="6" t="str">
-        <f>IF(G196&gt;=1500,"High",IF(G196&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20107,19 +20268,19 @@
         <v>306.45999999999998</v>
       </c>
       <c r="H197" s="6" t="str">
-        <f>PROPER(TRIM(C197))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I197" s="6" t="str">
-        <f>PROPER(TRIM(E197))</f>
+        <f t="shared" si="13"/>
         <v>Garowe</v>
       </c>
       <c r="J197" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F197,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K197" s="6" t="str">
-        <f>IF(G197&gt;=1500,"High",IF(G197&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20143,19 +20304,19 @@
         <v>923.87</v>
       </c>
       <c r="H198" s="6" t="str">
-        <f>PROPER(TRIM(C198))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I198" s="6" t="str">
-        <f>PROPER(TRIM(E198))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J198" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F198,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K198" s="6" t="str">
-        <f>IF(G198&gt;=1500,"High",IF(G198&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20182,19 +20343,19 @@
         <v>923.87</v>
       </c>
       <c r="H199" s="6" t="str">
-        <f>PROPER(TRIM(C199))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I199" s="6" t="str">
-        <f>PROPER(TRIM(E199))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J199" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F199,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K199" s="6" t="str">
-        <f>IF(G199&gt;=1500,"High",IF(G199&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20221,19 +20382,19 @@
         <v>785.95</v>
       </c>
       <c r="H200" s="6" t="str">
-        <f>PROPER(TRIM(C200))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I200" s="6" t="str">
-        <f>PROPER(TRIM(E200))</f>
+        <f t="shared" si="13"/>
         <v>Missing</v>
       </c>
       <c r="J200" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F200,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K200" s="6" t="str">
-        <f>IF(G200&gt;=1500,"High",IF(G200&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20260,19 +20421,19 @@
         <v>922.87</v>
       </c>
       <c r="H201" s="6" t="str">
-        <f>PROPER(TRIM(C201))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I201" s="6" t="str">
-        <f>PROPER(TRIM(E201))</f>
+        <f t="shared" si="13"/>
         <v>Missing</v>
       </c>
       <c r="J201" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F201,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K201" s="6" t="str">
-        <f>IF(G201&gt;=1500,"High",IF(G201&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20299,19 +20460,19 @@
         <v>728.06</v>
       </c>
       <c r="H202" s="6" t="str">
-        <f>PROPER(TRIM(C202))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I202" s="6" t="str">
-        <f>PROPER(TRIM(E202))</f>
+        <f t="shared" si="13"/>
         <v>Missing</v>
       </c>
       <c r="J202" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F202,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K202" s="6" t="str">
-        <f>IF(G202&gt;=1500,"High",IF(G202&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20338,19 +20499,19 @@
         <v>527.12</v>
       </c>
       <c r="H203" s="6" t="str">
-        <f>PROPER(TRIM(C203))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I203" s="6" t="str">
-        <f>PROPER(TRIM(E203))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J203" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F203,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K203" s="6" t="str">
-        <f>IF(G203&gt;=1500,"High",IF(G203&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20377,19 +20538,19 @@
         <v>923.87</v>
       </c>
       <c r="H204" s="6" t="str">
-        <f>PROPER(TRIM(C204))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I204" s="6" t="str">
-        <f>PROPER(TRIM(E204))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J204" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F204,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K204" s="6" t="str">
-        <f>IF(G204&gt;=1500,"High",IF(G204&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20416,19 +20577,19 @@
         <v>923.87</v>
       </c>
       <c r="H205" s="6" t="str">
-        <f>PROPER(TRIM(C205))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I205" s="6" t="str">
-        <f>PROPER(TRIM(E205))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J205" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F205,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K205" s="6" t="str">
-        <f>IF(G205&gt;=1500,"High",IF(G205&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20455,19 +20616,19 @@
         <v>508.34</v>
       </c>
       <c r="H206" s="6" t="str">
-        <f>PROPER(TRIM(C206))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I206" s="6" t="str">
-        <f>PROPER(TRIM(E206))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J206" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F206,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K206" s="6" t="str">
-        <f>IF(G206&gt;=1500,"High",IF(G206&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20494,19 +20655,19 @@
         <v>1067.9000000000001</v>
       </c>
       <c r="H207" s="6" t="str">
-        <f>PROPER(TRIM(C207))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I207" s="6" t="str">
-        <f>PROPER(TRIM(E207))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J207" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F207,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K207" s="6" t="str">
-        <f>IF(G207&gt;=1500,"High",IF(G207&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20530,19 +20691,19 @@
         <v>528.86</v>
       </c>
       <c r="H208" s="6" t="str">
-        <f>PROPER(TRIM(C208))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I208" s="6" t="str">
-        <f>PROPER(TRIM(E208))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J208" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F208,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K208" s="6" t="str">
-        <f>IF(G208&gt;=1500,"High",IF(G208&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20569,19 +20730,19 @@
         <v>930.02</v>
       </c>
       <c r="H209" s="6" t="str">
-        <f>PROPER(TRIM(C209))</f>
+        <f t="shared" si="12"/>
         <v>Missing</v>
       </c>
       <c r="I209" s="6" t="str">
-        <f>PROPER(TRIM(E209))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J209" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F209,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K209" s="6" t="str">
-        <f>IF(G209&gt;=1500,"High",IF(G209&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20608,19 +20769,19 @@
         <v>253.15</v>
       </c>
       <c r="H210" s="6" t="str">
-        <f>PROPER(TRIM(C210))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I210" s="6" t="str">
-        <f>PROPER(TRIM(E210))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J210" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F210,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K210" s="6" t="str">
-        <f>IF(G210&gt;=1500,"High",IF(G210&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20647,19 +20808,19 @@
         <v>855.02</v>
       </c>
       <c r="H211" s="6" t="str">
-        <f>PROPER(TRIM(C211))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I211" s="6" t="str">
-        <f>PROPER(TRIM(E211))</f>
+        <f t="shared" si="13"/>
         <v>Missing</v>
       </c>
       <c r="J211" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F211,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K211" s="6" t="str">
-        <f>IF(G211&gt;=1500,"High",IF(G211&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20686,19 +20847,19 @@
         <v>1281</v>
       </c>
       <c r="H212" s="6" t="str">
-        <f>PROPER(TRIM(C212))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I212" s="6" t="str">
-        <f>PROPER(TRIM(E212))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J212" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F212,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K212" s="6" t="str">
-        <f>IF(G212&gt;=1500,"High",IF(G212&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20725,19 +20886,19 @@
         <v>1164.05</v>
       </c>
       <c r="H213" s="6" t="str">
-        <f>PROPER(TRIM(C213))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I213" s="6" t="str">
-        <f>PROPER(TRIM(E213))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J213" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F213,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K213" s="6" t="str">
-        <f>IF(G213&gt;=1500,"High",IF(G213&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20764,19 +20925,19 @@
         <v>1170.92</v>
       </c>
       <c r="H214" s="6" t="str">
-        <f>PROPER(TRIM(C214))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I214" s="6" t="str">
-        <f>PROPER(TRIM(E214))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J214" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F214,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K214" s="6" t="str">
-        <f>IF(G214&gt;=1500,"High",IF(G214&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20803,19 +20964,19 @@
         <v>1021.22</v>
       </c>
       <c r="H215" s="6" t="str">
-        <f>PROPER(TRIM(C215))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I215" s="6" t="str">
-        <f>PROPER(TRIM(E215))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J215" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F215,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K215" s="6" t="str">
-        <f>IF(G215&gt;=1500,"High",IF(G215&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20842,19 +21003,19 @@
         <v>1315.27</v>
       </c>
       <c r="H216" s="6" t="str">
-        <f>PROPER(TRIM(C216))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I216" s="6" t="str">
-        <f>PROPER(TRIM(E216))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J216" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F216,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K216" s="6" t="str">
-        <f>IF(G216&gt;=1500,"High",IF(G216&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20881,19 +21042,19 @@
         <v>644.80999999999995</v>
       </c>
       <c r="H217" s="6" t="str">
-        <f>PROPER(TRIM(C217))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I217" s="6" t="str">
-        <f>PROPER(TRIM(E217))</f>
+        <f t="shared" si="13"/>
         <v>Garowe</v>
       </c>
       <c r="J217" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F217,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K217" s="6" t="str">
-        <f>IF(G217&gt;=1500,"High",IF(G217&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -20920,19 +21081,19 @@
         <v>854.23</v>
       </c>
       <c r="H218" s="6" t="str">
-        <f>PROPER(TRIM(C218))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I218" s="6" t="str">
-        <f>PROPER(TRIM(E218))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J218" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F218,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K218" s="6" t="str">
-        <f>IF(G218&gt;=1500,"High",IF(G218&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20959,19 +21120,19 @@
         <v>1371.98</v>
       </c>
       <c r="H219" s="6" t="str">
-        <f>PROPER(TRIM(C219))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I219" s="6" t="str">
-        <f>PROPER(TRIM(E219))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J219" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F219,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K219" s="6" t="str">
-        <f>IF(G219&gt;=1500,"High",IF(G219&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -20998,19 +21159,19 @@
         <v>558.07000000000005</v>
       </c>
       <c r="H220" s="6" t="str">
-        <f>PROPER(TRIM(C220))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I220" s="6" t="str">
-        <f>PROPER(TRIM(E220))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J220" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F220,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K220" s="6" t="str">
-        <f>IF(G220&gt;=1500,"High",IF(G220&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21037,19 +21198,19 @@
         <v>1069.08</v>
       </c>
       <c r="H221" s="6" t="str">
-        <f>PROPER(TRIM(C221))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I221" s="6" t="str">
-        <f>PROPER(TRIM(E221))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J221" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F221,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K221" s="6" t="str">
-        <f>IF(G221&gt;=1500,"High",IF(G221&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21076,19 +21237,19 @@
         <v>778.23</v>
       </c>
       <c r="H222" s="6" t="str">
-        <f>PROPER(TRIM(C222))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I222" s="6" t="str">
-        <f>PROPER(TRIM(E222))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J222" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F222,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K222" s="6" t="str">
-        <f>IF(G222&gt;=1500,"High",IF(G222&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21115,19 +21276,19 @@
         <v>216.93</v>
       </c>
       <c r="H223" s="6" t="str">
-        <f>PROPER(TRIM(C223))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I223" s="6" t="str">
-        <f>PROPER(TRIM(E223))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J223" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F223,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Missing</v>
       </c>
       <c r="K223" s="6" t="str">
-        <f>IF(G223&gt;=1500,"High",IF(G223&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21154,19 +21315,19 @@
         <v>794.1</v>
       </c>
       <c r="H224" s="6" t="str">
-        <f>PROPER(TRIM(C224))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I224" s="6" t="str">
-        <f>PROPER(TRIM(E224))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J224" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F224,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K224" s="6" t="str">
-        <f>IF(G224&gt;=1500,"High",IF(G224&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21193,19 +21354,19 @@
         <v>1377.65</v>
       </c>
       <c r="H225" s="6" t="str">
-        <f>PROPER(TRIM(C225))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I225" s="6" t="str">
-        <f>PROPER(TRIM(E225))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J225" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F225,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K225" s="6" t="str">
-        <f>IF(G225&gt;=1500,"High",IF(G225&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21232,19 +21393,19 @@
         <v>1321.69</v>
       </c>
       <c r="H226" s="6" t="str">
-        <f>PROPER(TRIM(C226))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I226" s="6" t="str">
-        <f>PROPER(TRIM(E226))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J226" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F226,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K226" s="6" t="str">
-        <f>IF(G226&gt;=1500,"High",IF(G226&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21271,19 +21432,19 @@
         <v>200.87</v>
       </c>
       <c r="H227" s="6" t="str">
-        <f>PROPER(TRIM(C227))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I227" s="6" t="str">
-        <f>PROPER(TRIM(E227))</f>
+        <f t="shared" si="13"/>
         <v>Baidoa</v>
       </c>
       <c r="J227" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F227,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K227" s="6" t="str">
-        <f>IF(G227&gt;=1500,"High",IF(G227&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21310,19 +21471,19 @@
         <v>727.81</v>
       </c>
       <c r="H228" s="6" t="str">
-        <f>PROPER(TRIM(C228))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I228" s="6" t="str">
-        <f>PROPER(TRIM(E228))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J228" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F228,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K228" s="6" t="str">
-        <f>IF(G228&gt;=1500,"High",IF(G228&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21349,19 +21510,19 @@
         <v>644.95000000000005</v>
       </c>
       <c r="H229" s="6" t="str">
-        <f>PROPER(TRIM(C229))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I229" s="6" t="str">
-        <f>PROPER(TRIM(E229))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J229" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F229,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K229" s="6" t="str">
-        <f>IF(G229&gt;=1500,"High",IF(G229&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21388,19 +21549,19 @@
         <v>1127.6500000000001</v>
       </c>
       <c r="H230" s="6" t="str">
-        <f>PROPER(TRIM(C230))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I230" s="6" t="str">
-        <f>PROPER(TRIM(E230))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J230" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F230,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K230" s="6" t="str">
-        <f>IF(G230&gt;=1500,"High",IF(G230&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21427,19 +21588,19 @@
         <v>727.06</v>
       </c>
       <c r="H231" s="6" t="str">
-        <f>PROPER(TRIM(C231))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I231" s="6" t="str">
-        <f>PROPER(TRIM(E231))</f>
+        <f t="shared" si="13"/>
         <v>Missing</v>
       </c>
       <c r="J231" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F231,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K231" s="6" t="str">
-        <f>IF(G231&gt;=1500,"High",IF(G231&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21466,19 +21627,19 @@
         <v>1411.64</v>
       </c>
       <c r="H232" s="6" t="str">
-        <f>PROPER(TRIM(C232))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I232" s="6" t="str">
-        <f>PROPER(TRIM(E232))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J232" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F232,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K232" s="6" t="str">
-        <f>IF(G232&gt;=1500,"High",IF(G232&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21505,19 +21666,19 @@
         <v>891.18</v>
       </c>
       <c r="H233" s="6" t="str">
-        <f>PROPER(TRIM(C233))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I233" s="6" t="str">
-        <f>PROPER(TRIM(E233))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J233" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F233,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K233" s="6" t="str">
-        <f>IF(G233&gt;=1500,"High",IF(G233&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21544,19 +21705,19 @@
         <v>1155.56</v>
       </c>
       <c r="H234" s="6" t="str">
-        <f>PROPER(TRIM(C234))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I234" s="6" t="str">
-        <f>PROPER(TRIM(E234))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J234" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F234,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K234" s="6" t="str">
-        <f>IF(G234&gt;=1500,"High",IF(G234&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21583,19 +21744,19 @@
         <v>116.1</v>
       </c>
       <c r="H235" s="6" t="str">
-        <f>PROPER(TRIM(C235))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I235" s="6" t="str">
-        <f>PROPER(TRIM(E235))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J235" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F235,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K235" s="6" t="str">
-        <f>IF(G235&gt;=1500,"High",IF(G235&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21622,19 +21783,19 @@
         <v>749.33</v>
       </c>
       <c r="H236" s="6" t="str">
-        <f>PROPER(TRIM(C236))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I236" s="6" t="str">
-        <f>PROPER(TRIM(E236))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J236" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F236,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K236" s="6" t="str">
-        <f>IF(G236&gt;=1500,"High",IF(G236&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21661,19 +21822,19 @@
         <v>732.86</v>
       </c>
       <c r="H237" s="6" t="str">
-        <f>PROPER(TRIM(C237))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I237" s="6" t="str">
-        <f>PROPER(TRIM(E237))</f>
+        <f t="shared" si="13"/>
         <v>Kismayo</v>
       </c>
       <c r="J237" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F237,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K237" s="6" t="str">
-        <f>IF(G237&gt;=1500,"High",IF(G237&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21700,19 +21861,19 @@
         <v>1263.1099999999999</v>
       </c>
       <c r="H238" s="6" t="str">
-        <f>PROPER(TRIM(C238))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I238" s="6" t="str">
-        <f>PROPER(TRIM(E238))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J238" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F238,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K238" s="6" t="str">
-        <f>IF(G238&gt;=1500,"High",IF(G238&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21739,19 +21900,19 @@
         <v>721.99</v>
       </c>
       <c r="H239" s="6" t="str">
-        <f>PROPER(TRIM(C239))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I239" s="6" t="str">
-        <f>PROPER(TRIM(E239))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J239" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F239,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K239" s="6" t="str">
-        <f>IF(G239&gt;=1500,"High",IF(G239&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21778,19 +21939,19 @@
         <v>169.21</v>
       </c>
       <c r="H240" s="6" t="str">
-        <f>PROPER(TRIM(C240))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I240" s="6" t="str">
-        <f>PROPER(TRIM(E240))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J240" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F240,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K240" s="6" t="str">
-        <f>IF(G240&gt;=1500,"High",IF(G240&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -21817,19 +21978,19 @@
         <v>934.22</v>
       </c>
       <c r="H241" s="6" t="str">
-        <f>PROPER(TRIM(C241))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I241" s="6" t="str">
-        <f>PROPER(TRIM(E241))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J241" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F241,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K241" s="6" t="str">
-        <f>IF(G241&gt;=1500,"High",IF(G241&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21856,19 +22017,19 @@
         <v>857.27</v>
       </c>
       <c r="H242" s="6" t="str">
-        <f>PROPER(TRIM(C242))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I242" s="6" t="str">
-        <f>PROPER(TRIM(E242))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J242" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F242,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Civil Servant</v>
       </c>
       <c r="K242" s="6" t="str">
-        <f>IF(G242&gt;=1500,"High",IF(G242&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21892,19 +22053,19 @@
         <v>917.25</v>
       </c>
       <c r="H243" s="6" t="str">
-        <f>PROPER(TRIM(C243))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I243" s="6" t="str">
-        <f>PROPER(TRIM(E243))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J243" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F243,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K243" s="6" t="str">
-        <f>IF(G243&gt;=1500,"High",IF(G243&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21931,19 +22092,19 @@
         <v>923.87</v>
       </c>
       <c r="H244" s="6" t="str">
-        <f>PROPER(TRIM(C244))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I244" s="6" t="str">
-        <f>PROPER(TRIM(E244))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J244" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F244,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K244" s="6" t="str">
-        <f>IF(G244&gt;=1500,"High",IF(G244&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -21970,19 +22131,19 @@
         <v>746.07</v>
       </c>
       <c r="H245" s="6" t="str">
-        <f>PROPER(TRIM(C245))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I245" s="6" t="str">
-        <f>PROPER(TRIM(E245))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J245" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F245,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K245" s="6" t="str">
-        <f>IF(G245&gt;=1500,"High",IF(G245&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22009,19 +22170,19 @@
         <v>294.94</v>
       </c>
       <c r="H246" s="6" t="str">
-        <f>PROPER(TRIM(C246))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I246" s="6" t="str">
-        <f>PROPER(TRIM(E246))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J246" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F246,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K246" s="6" t="str">
-        <f>IF(G246&gt;=1500,"High",IF(G246&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22048,19 +22209,19 @@
         <v>1137.32</v>
       </c>
       <c r="H247" s="6" t="str">
-        <f>PROPER(TRIM(C247))</f>
+        <f t="shared" si="12"/>
         <v>Missing</v>
       </c>
       <c r="I247" s="6" t="str">
-        <f>PROPER(TRIM(E247))</f>
+        <f t="shared" si="13"/>
         <v>Baidoa</v>
       </c>
       <c r="J247" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F247,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K247" s="6" t="str">
-        <f>IF(G247&gt;=1500,"High",IF(G247&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22087,19 +22248,19 @@
         <v>2015.04</v>
       </c>
       <c r="H248" s="6" t="str">
-        <f>PROPER(TRIM(C248))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I248" s="6" t="str">
-        <f>PROPER(TRIM(E248))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J248" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F248,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Business Owner</v>
       </c>
       <c r="K248" s="6" t="str">
-        <f>IF(G248&gt;=1500,"High",IF(G248&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>High</v>
       </c>
     </row>
@@ -22126,19 +22287,19 @@
         <v>255.08</v>
       </c>
       <c r="H249" s="6" t="str">
-        <f>PROPER(TRIM(C249))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I249" s="6" t="str">
-        <f>PROPER(TRIM(E249))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J249" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F249,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Missing</v>
       </c>
       <c r="K249" s="6" t="str">
-        <f>IF(G249&gt;=1500,"High",IF(G249&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22165,19 +22326,19 @@
         <v>1315.07</v>
       </c>
       <c r="H250" s="6" t="str">
-        <f>PROPER(TRIM(C250))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I250" s="6" t="str">
-        <f>PROPER(TRIM(E250))</f>
+        <f t="shared" si="13"/>
         <v>Bosaso</v>
       </c>
       <c r="J250" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F250,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K250" s="6" t="str">
-        <f>IF(G250&gt;=1500,"High",IF(G250&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22204,19 +22365,19 @@
         <v>923.87</v>
       </c>
       <c r="H251" s="6" t="str">
-        <f>PROPER(TRIM(C251))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I251" s="6" t="str">
-        <f>PROPER(TRIM(E251))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J251" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F251,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K251" s="6" t="str">
-        <f>IF(G251&gt;=1500,"High",IF(G251&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22243,19 +22404,19 @@
         <v>1143.8399999999999</v>
       </c>
       <c r="H252" s="6" t="str">
-        <f>PROPER(TRIM(C252))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I252" s="6" t="str">
-        <f>PROPER(TRIM(E252))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J252" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F252,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Self-Employed</v>
       </c>
       <c r="K252" s="6" t="str">
-        <f>IF(G252&gt;=1500,"High",IF(G252&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22282,19 +22443,19 @@
         <v>1244.97</v>
       </c>
       <c r="H253" s="6" t="str">
-        <f>PROPER(TRIM(C253))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I253" s="6" t="str">
-        <f>PROPER(TRIM(E253))</f>
+        <f t="shared" si="13"/>
         <v>Mogadishu</v>
       </c>
       <c r="J253" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F253,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Healthcare</v>
       </c>
       <c r="K253" s="6" t="str">
-        <f>IF(G253&gt;=1500,"High",IF(G253&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22321,19 +22482,19 @@
         <v>149.24</v>
       </c>
       <c r="H254" s="6" t="str">
-        <f>PROPER(TRIM(C254))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I254" s="6" t="str">
-        <f>PROPER(TRIM(E254))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J254" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F254,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Student</v>
       </c>
       <c r="K254" s="6" t="str">
-        <f>IF(G254&gt;=1500,"High",IF(G254&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22360,19 +22521,19 @@
         <v>216.82</v>
       </c>
       <c r="H255" s="6" t="str">
-        <f>PROPER(TRIM(C255))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I255" s="6" t="str">
-        <f>PROPER(TRIM(E255))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J255" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F255,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Missing</v>
       </c>
       <c r="K255" s="6" t="str">
-        <f>IF(G255&gt;=1500,"High",IF(G255&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22399,19 +22560,19 @@
         <v>1390.38</v>
       </c>
       <c r="H256" s="6" t="str">
-        <f>PROPER(TRIM(C256))</f>
+        <f t="shared" si="12"/>
         <v>Female</v>
       </c>
       <c r="I256" s="6" t="str">
-        <f>PROPER(TRIM(E256))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J256" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F256,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Engineer</v>
       </c>
       <c r="K256" s="6" t="str">
-        <f>IF(G256&gt;=1500,"High",IF(G256&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22438,19 +22599,19 @@
         <v>661.3</v>
       </c>
       <c r="H257" s="6" t="str">
-        <f>PROPER(TRIM(C257))</f>
+        <f t="shared" si="12"/>
         <v>Male</v>
       </c>
       <c r="I257" s="6" t="str">
-        <f>PROPER(TRIM(E257))</f>
+        <f t="shared" si="13"/>
         <v>Hargeisa</v>
       </c>
       <c r="J257" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F257,"CS","Civil Servant")))</f>
+        <f t="shared" si="14"/>
         <v>Teacher</v>
       </c>
       <c r="K257" s="6" t="str">
-        <f>IF(G257&gt;=1500,"High",IF(G257&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="15"/>
         <v>Low</v>
       </c>
     </row>
@@ -22477,19 +22638,19 @@
         <v>1046.17</v>
       </c>
       <c r="H258" s="6" t="str">
-        <f>PROPER(TRIM(C258))</f>
+        <f t="shared" ref="H258:H294" si="16">PROPER(TRIM(C258))</f>
         <v>Missing</v>
       </c>
       <c r="I258" s="6" t="str">
-        <f>PROPER(TRIM(E258))</f>
+        <f t="shared" ref="I258:I294" si="17">PROPER(TRIM(E258))</f>
         <v>Kismayo</v>
       </c>
       <c r="J258" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F258,"CS","Civil Servant")))</f>
+        <f t="shared" ref="J258:J294" si="18">PROPER(TRIM(SUBSTITUTE(F258,"CS","Civil Servant")))</f>
         <v>Self-Employed</v>
       </c>
       <c r="K258" s="6" t="str">
-        <f>IF(G258&gt;=1500,"High",IF(G258&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K258:K294" si="19">IF(G258&gt;=1500,"High",IF(G258&gt;=800,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -22516,19 +22677,19 @@
         <v>742.69</v>
       </c>
       <c r="H259" s="6" t="str">
-        <f>PROPER(TRIM(C259))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I259" s="6" t="str">
-        <f>PROPER(TRIM(E259))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J259" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F259,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Healthcare</v>
       </c>
       <c r="K259" s="6" t="str">
-        <f>IF(G259&gt;=1500,"High",IF(G259&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22555,19 +22716,19 @@
         <v>595.70000000000005</v>
       </c>
       <c r="H260" s="6" t="str">
-        <f>PROPER(TRIM(C260))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I260" s="6" t="str">
-        <f>PROPER(TRIM(E260))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J260" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F260,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K260" s="6" t="str">
-        <f>IF(G260&gt;=1500,"High",IF(G260&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22594,19 +22755,19 @@
         <v>201.16</v>
       </c>
       <c r="H261" s="6" t="str">
-        <f>PROPER(TRIM(C261))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I261" s="6" t="str">
-        <f>PROPER(TRIM(E261))</f>
+        <f t="shared" si="17"/>
         <v>Kismayo</v>
       </c>
       <c r="J261" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F261,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Student</v>
       </c>
       <c r="K261" s="6" t="str">
-        <f>IF(G261&gt;=1500,"High",IF(G261&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22633,19 +22794,19 @@
         <v>638.6</v>
       </c>
       <c r="H262" s="6" t="str">
-        <f>PROPER(TRIM(C262))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I262" s="6" t="str">
-        <f>PROPER(TRIM(E262))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J262" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F262,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K262" s="6" t="str">
-        <f>IF(G262&gt;=1500,"High",IF(G262&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22672,19 +22833,19 @@
         <v>2091.58</v>
       </c>
       <c r="H263" s="6" t="str">
-        <f>PROPER(TRIM(C263))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I263" s="6" t="str">
-        <f>PROPER(TRIM(E263))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J263" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F263,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K263" s="6" t="str">
-        <f>IF(G263&gt;=1500,"High",IF(G263&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>High</v>
       </c>
     </row>
@@ -22711,19 +22872,19 @@
         <v>2156</v>
       </c>
       <c r="H264" s="6" t="str">
-        <f>PROPER(TRIM(C264))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I264" s="6" t="str">
-        <f>PROPER(TRIM(E264))</f>
+        <f t="shared" si="17"/>
         <v>Baidoa</v>
       </c>
       <c r="J264" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F264,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K264" s="6" t="str">
-        <f>IF(G264&gt;=1500,"High",IF(G264&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>High</v>
       </c>
     </row>
@@ -22750,19 +22911,19 @@
         <v>719.42</v>
       </c>
       <c r="H265" s="6" t="str">
-        <f>PROPER(TRIM(C265))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I265" s="6" t="str">
-        <f>PROPER(TRIM(E265))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J265" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F265,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K265" s="6" t="str">
-        <f>IF(G265&gt;=1500,"High",IF(G265&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22789,19 +22950,19 @@
         <v>239.25</v>
       </c>
       <c r="H266" s="6" t="str">
-        <f>PROPER(TRIM(C266))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I266" s="6" t="str">
-        <f>PROPER(TRIM(E266))</f>
+        <f t="shared" si="17"/>
         <v>Baidoa</v>
       </c>
       <c r="J266" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F266,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Student</v>
       </c>
       <c r="K266" s="6" t="str">
-        <f>IF(G266&gt;=1500,"High",IF(G266&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22828,19 +22989,19 @@
         <v>1071.8599999999999</v>
       </c>
       <c r="H267" s="6" t="str">
-        <f>PROPER(TRIM(C267))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I267" s="6" t="str">
-        <f>PROPER(TRIM(E267))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J267" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F267,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K267" s="6" t="str">
-        <f>IF(G267&gt;=1500,"High",IF(G267&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -22864,19 +23025,19 @@
         <v>176.82</v>
       </c>
       <c r="H268" s="6" t="str">
-        <f>PROPER(TRIM(C268))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I268" s="6" t="str">
-        <f>PROPER(TRIM(E268))</f>
+        <f t="shared" si="17"/>
         <v>Hargeisa</v>
       </c>
       <c r="J268" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F268,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Student</v>
       </c>
       <c r="K268" s="6" t="str">
-        <f>IF(G268&gt;=1500,"High",IF(G268&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22903,19 +23064,19 @@
         <v>671.87</v>
       </c>
       <c r="H269" s="6" t="str">
-        <f>PROPER(TRIM(C269))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I269" s="6" t="str">
-        <f>PROPER(TRIM(E269))</f>
+        <f t="shared" si="17"/>
         <v>Bosaso</v>
       </c>
       <c r="J269" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F269,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Self-Employed</v>
       </c>
       <c r="K269" s="6" t="str">
-        <f>IF(G269&gt;=1500,"High",IF(G269&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22939,19 +23100,19 @@
         <v>586.78</v>
       </c>
       <c r="H270" s="6" t="str">
-        <f>PROPER(TRIM(C270))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I270" s="6" t="str">
-        <f>PROPER(TRIM(E270))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J270" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F270,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K270" s="6" t="str">
-        <f>IF(G270&gt;=1500,"High",IF(G270&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -22978,19 +23139,19 @@
         <v>901.36</v>
       </c>
       <c r="H271" s="6" t="str">
-        <f>PROPER(TRIM(C271))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I271" s="6" t="str">
-        <f>PROPER(TRIM(E271))</f>
+        <f t="shared" si="17"/>
         <v>Hargeisa</v>
       </c>
       <c r="J271" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F271,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K271" s="6" t="str">
-        <f>IF(G271&gt;=1500,"High",IF(G271&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23017,19 +23178,19 @@
         <v>1315.74</v>
       </c>
       <c r="H272" s="6" t="str">
-        <f>PROPER(TRIM(C272))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I272" s="6" t="str">
-        <f>PROPER(TRIM(E272))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J272" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F272,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K272" s="6" t="str">
-        <f>IF(G272&gt;=1500,"High",IF(G272&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23056,19 +23217,19 @@
         <v>632.38</v>
       </c>
       <c r="H273" s="6" t="str">
-        <f>PROPER(TRIM(C273))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I273" s="6" t="str">
-        <f>PROPER(TRIM(E273))</f>
+        <f t="shared" si="17"/>
         <v>Hargeisa</v>
       </c>
       <c r="J273" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F273,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K273" s="6" t="str">
-        <f>IF(G273&gt;=1500,"High",IF(G273&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23095,19 +23256,19 @@
         <v>1087.08</v>
       </c>
       <c r="H274" s="6" t="str">
-        <f>PROPER(TRIM(C274))</f>
+        <f t="shared" si="16"/>
         <v>Missing</v>
       </c>
       <c r="I274" s="6" t="str">
-        <f>PROPER(TRIM(E274))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J274" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F274,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Healthcare</v>
       </c>
       <c r="K274" s="6" t="str">
-        <f>IF(G274&gt;=1500,"High",IF(G274&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23134,19 +23295,19 @@
         <v>608.08000000000004</v>
       </c>
       <c r="H275" s="6" t="str">
-        <f>PROPER(TRIM(C275))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I275" s="6" t="str">
-        <f>PROPER(TRIM(E275))</f>
+        <f t="shared" si="17"/>
         <v>Bosaso</v>
       </c>
       <c r="J275" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F275,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K275" s="6" t="str">
-        <f>IF(G275&gt;=1500,"High",IF(G275&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23173,19 +23334,19 @@
         <v>647.6</v>
       </c>
       <c r="H276" s="6" t="str">
-        <f>PROPER(TRIM(C276))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I276" s="6" t="str">
-        <f>PROPER(TRIM(E276))</f>
+        <f t="shared" si="17"/>
         <v>Baidoa</v>
       </c>
       <c r="J276" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F276,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K276" s="6" t="str">
-        <f>IF(G276&gt;=1500,"High",IF(G276&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23212,19 +23373,19 @@
         <v>1961.76</v>
       </c>
       <c r="H277" s="6" t="str">
-        <f>PROPER(TRIM(C277))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I277" s="6" t="str">
-        <f>PROPER(TRIM(E277))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J277" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F277,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K277" s="6" t="str">
-        <f>IF(G277&gt;=1500,"High",IF(G277&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>High</v>
       </c>
     </row>
@@ -23251,19 +23412,19 @@
         <v>964.35</v>
       </c>
       <c r="H278" s="6" t="str">
-        <f>PROPER(TRIM(C278))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I278" s="6" t="str">
-        <f>PROPER(TRIM(E278))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J278" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F278,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K278" s="6" t="str">
-        <f>IF(G278&gt;=1500,"High",IF(G278&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23290,19 +23451,19 @@
         <v>753.73</v>
       </c>
       <c r="H279" s="6" t="str">
-        <f>PROPER(TRIM(C279))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I279" s="6" t="str">
-        <f>PROPER(TRIM(E279))</f>
+        <f t="shared" si="17"/>
         <v>Kismayo</v>
       </c>
       <c r="J279" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F279,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Self-Employed</v>
       </c>
       <c r="K279" s="6" t="str">
-        <f>IF(G279&gt;=1500,"High",IF(G279&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23329,19 +23490,19 @@
         <v>827.25</v>
       </c>
       <c r="H280" s="6" t="str">
-        <f>PROPER(TRIM(C280))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I280" s="6" t="str">
-        <f>PROPER(TRIM(E280))</f>
+        <f t="shared" si="17"/>
         <v>Baidoa</v>
       </c>
       <c r="J280" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F280,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K280" s="6" t="str">
-        <f>IF(G280&gt;=1500,"High",IF(G280&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23368,19 +23529,19 @@
         <v>442.74</v>
       </c>
       <c r="H281" s="6" t="str">
-        <f>PROPER(TRIM(C281))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I281" s="6" t="str">
-        <f>PROPER(TRIM(E281))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J281" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F281,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Self-Employed</v>
       </c>
       <c r="K281" s="6" t="str">
-        <f>IF(G281&gt;=1500,"High",IF(G281&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23407,19 +23568,19 @@
         <v>661.71</v>
       </c>
       <c r="H282" s="6" t="str">
-        <f>PROPER(TRIM(C282))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I282" s="6" t="str">
-        <f>PROPER(TRIM(E282))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J282" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F282,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K282" s="6" t="str">
-        <f>IF(G282&gt;=1500,"High",IF(G282&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23446,19 +23607,19 @@
         <v>978.74</v>
       </c>
       <c r="H283" s="6" t="str">
-        <f>PROPER(TRIM(C283))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I283" s="6" t="str">
-        <f>PROPER(TRIM(E283))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J283" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F283,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Healthcare</v>
       </c>
       <c r="K283" s="6" t="str">
-        <f>IF(G283&gt;=1500,"High",IF(G283&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23485,19 +23646,19 @@
         <v>645.54999999999995</v>
       </c>
       <c r="H284" s="6" t="str">
-        <f>PROPER(TRIM(C284))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I284" s="6" t="str">
-        <f>PROPER(TRIM(E284))</f>
+        <f t="shared" si="17"/>
         <v>Kismayo</v>
       </c>
       <c r="J284" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F284,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K284" s="6" t="str">
-        <f>IF(G284&gt;=1500,"High",IF(G284&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23524,19 +23685,19 @@
         <v>759.9</v>
       </c>
       <c r="H285" s="6" t="str">
-        <f>PROPER(TRIM(C285))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I285" s="6" t="str">
-        <f>PROPER(TRIM(E285))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J285" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F285,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K285" s="6" t="str">
-        <f>IF(G285&gt;=1500,"High",IF(G285&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23560,19 +23721,19 @@
         <v>1828.2</v>
       </c>
       <c r="H286" s="6" t="str">
-        <f>PROPER(TRIM(C286))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I286" s="6" t="str">
-        <f>PROPER(TRIM(E286))</f>
+        <f t="shared" si="17"/>
         <v>Hargeisa</v>
       </c>
       <c r="J286" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F286,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K286" s="6" t="str">
-        <f>IF(G286&gt;=1500,"High",IF(G286&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>High</v>
       </c>
     </row>
@@ -23599,19 +23760,19 @@
         <v>776.84</v>
       </c>
       <c r="H287" s="6" t="str">
-        <f>PROPER(TRIM(C287))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I287" s="6" t="str">
-        <f>PROPER(TRIM(E287))</f>
+        <f t="shared" si="17"/>
         <v>Bosaso</v>
       </c>
       <c r="J287" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F287,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K287" s="6" t="str">
-        <f>IF(G287&gt;=1500,"High",IF(G287&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23638,19 +23799,19 @@
         <v>1603.75</v>
       </c>
       <c r="H288" s="6" t="str">
-        <f>PROPER(TRIM(C288))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I288" s="6" t="str">
-        <f>PROPER(TRIM(E288))</f>
+        <f t="shared" si="17"/>
         <v>Kismayo</v>
       </c>
       <c r="J288" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F288,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K288" s="6" t="str">
-        <f>IF(G288&gt;=1500,"High",IF(G288&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>High</v>
       </c>
     </row>
@@ -23677,19 +23838,19 @@
         <v>618.42999999999995</v>
       </c>
       <c r="H289" s="6" t="str">
-        <f>PROPER(TRIM(C289))</f>
+        <f t="shared" si="16"/>
         <v>Female</v>
       </c>
       <c r="I289" s="6" t="str">
-        <f>PROPER(TRIM(E289))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J289" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F289,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Civil Servant</v>
       </c>
       <c r="K289" s="6" t="str">
-        <f>IF(G289&gt;=1500,"High",IF(G289&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23716,19 +23877,19 @@
         <v>325.43</v>
       </c>
       <c r="H290" s="6" t="str">
-        <f>PROPER(TRIM(C290))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I290" s="6" t="str">
-        <f>PROPER(TRIM(E290))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J290" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F290,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Teacher</v>
       </c>
       <c r="K290" s="6" t="str">
-        <f>IF(G290&gt;=1500,"High",IF(G290&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23755,19 +23916,19 @@
         <v>502.04</v>
       </c>
       <c r="H291" s="6" t="str">
-        <f>PROPER(TRIM(C291))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I291" s="6" t="str">
-        <f>PROPER(TRIM(E291))</f>
+        <f t="shared" si="17"/>
         <v>Mogadishu</v>
       </c>
       <c r="J291" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F291,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Healthcare</v>
       </c>
       <c r="K291" s="6" t="str">
-        <f>IF(G291&gt;=1500,"High",IF(G291&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23791,19 +23952,19 @@
         <v>268.75</v>
       </c>
       <c r="H292" s="6" t="str">
-        <f>PROPER(TRIM(C292))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I292" s="6" t="str">
-        <f>PROPER(TRIM(E292))</f>
+        <f t="shared" si="17"/>
         <v>Hargeisa</v>
       </c>
       <c r="J292" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F292,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Student</v>
       </c>
       <c r="K292" s="6" t="str">
-        <f>IF(G292&gt;=1500,"High",IF(G292&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23830,19 +23991,19 @@
         <v>1249.32</v>
       </c>
       <c r="H293" s="6" t="str">
-        <f>PROPER(TRIM(C293))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I293" s="6" t="str">
-        <f>PROPER(TRIM(E293))</f>
+        <f t="shared" si="17"/>
         <v>Bosaso</v>
       </c>
       <c r="J293" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F293,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Business Owner</v>
       </c>
       <c r="K293" s="6" t="str">
-        <f>IF(G293&gt;=1500,"High",IF(G293&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Medium</v>
       </c>
     </row>
@@ -23869,19 +24030,19 @@
         <v>632.26</v>
       </c>
       <c r="H294" s="6" t="str">
-        <f>PROPER(TRIM(C294))</f>
+        <f t="shared" si="16"/>
         <v>Male</v>
       </c>
       <c r="I294" s="6" t="str">
-        <f>PROPER(TRIM(E294))</f>
+        <f t="shared" si="17"/>
         <v>Garowe</v>
       </c>
       <c r="J294" s="6" t="str">
-        <f>PROPER(TRIM(SUBSTITUTE(F294,"CS","Civil Servant")))</f>
+        <f t="shared" si="18"/>
         <v>Engineer</v>
       </c>
       <c r="K294" s="6" t="str">
-        <f>IF(G294&gt;=1500,"High",IF(G294&gt;=800,"Medium","Low"))</f>
+        <f t="shared" si="19"/>
         <v>Low</v>
       </c>
     </row>
@@ -23890,10 +24051,10 @@
     <sortCondition ref="B2:B294"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23905,21 +24066,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
       </colorScale>
     </cfRule>
-    <cfRule type="dataBar" priority="6">
+    <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
+        <color rgb="FFFF555A"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -23927,13 +24088,25 @@
         </ext>
       </extLst>
     </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"Low"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"Low"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Medium"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="dataBar" priority="5">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
+        <color rgb="FFFFB628"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -23941,19 +24114,19 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -23967,7 +24140,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -23977,12 +24150,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="iconSet" priority="1">
+    <cfRule type="iconSet" priority="12">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
         <cfvo type="percent" val="67"/>
       </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+      <formula>"Medium"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23995,7 +24173,7 @@
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
+              <x14:borderColor rgb="FFFF555A"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
               <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
@@ -24008,7 +24186,7 @@
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
+              <x14:borderColor rgb="FFFFB628"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
               <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
@@ -24278,7 +24456,7 @@
       </c>
       <c r="B33" s="14">
         <f ca="1">TODAY()</f>
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>352</v>
@@ -24290,7 +24468,7 @@
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46249.679538310185</v>
+        <v>46250.476986689813</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>354</v>

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clean_Data '!$E$1:$E$294</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="7" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="368">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -1131,6 +1134,15 @@
   </si>
   <si>
     <t>Workdays from registration to today</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Monthly_Income</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1247,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1287,13 +1299,15 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="60% - Accent5" xfId="2" builtinId="48"/>
     <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -1342,210 +1356,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C6500"/>
       </font>
@@ -1566,6 +1376,1030 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Customer Demographic Data Analysis Data.xlsx]PivotTables!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$6:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Baidoa</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bosaso</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Garowe</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hargeisa</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kismayo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Missing</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mogadishu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$B$6:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>19068.93</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39854.100000000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17991.009999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38385.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30250.91</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13639.55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111503.65999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1030-4C9F-B67E-27CE8BEA77F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1898291759"/>
+        <c:axId val="1898292175"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1898291759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1898292175"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1898292175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1898291759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>195263</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5698,6 +6532,4532 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="hp" refreshedDate="46250.677500347221" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="293">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K294" sheet="Clean_Data "/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="Customer_ID" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Registration_Date" numFmtId="14">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2025-01-04T00:00:00" maxDate="2026-07-28T00:00:00"/>
+    </cacheField>
+    <cacheField name="Gender" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Female"/>
+        <s v="Male"/>
+        <s v="Missing"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="18" maxValue="123"/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems count="7">
+        <s v="Missing"/>
+        <s v="Mogadishu"/>
+        <s v="Baidoa"/>
+        <s v="Bosaso"/>
+        <s v="Hargeisa"/>
+        <s v="Kismayo"/>
+        <s v="Garowe"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Occupation" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Business Owner"/>
+        <s v="Healthcare"/>
+        <s v="Engineer"/>
+        <s v="Civil Servant"/>
+        <s v="student"/>
+        <s v="Teacher"/>
+        <s v="Self-Employed"/>
+        <s v="Missing "/>
+        <s v="CS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Monthly_Income" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="108.23" maxValue="10013" count="273">
+        <n v="1455.22"/>
+        <n v="1250.21"/>
+        <n v="602"/>
+        <n v="789.1"/>
+        <n v="1964.48"/>
+        <n v="1547.72"/>
+        <n v="881.22"/>
+        <n v="278.61"/>
+        <n v="923.87"/>
+        <n v="127.29"/>
+        <n v="312.77"/>
+        <n v="1015.92"/>
+        <n v="1024.44"/>
+        <n v="926.65"/>
+        <n v="2040.09"/>
+        <n v="836.87"/>
+        <n v="579.54999999999995"/>
+        <n v="954.9"/>
+        <n v="526.37"/>
+        <n v="1086.56"/>
+        <n v="210.96"/>
+        <n v="1214.6199999999999"/>
+        <n v="1215.9100000000001"/>
+        <n v="494.83"/>
+        <n v="646.07000000000005"/>
+        <n v="409.49"/>
+        <n v="835.61"/>
+        <n v="675.77"/>
+        <n v="1800.86"/>
+        <n v="1516.2"/>
+        <n v="952.9"/>
+        <n v="1144.9100000000001"/>
+        <n v="963.66"/>
+        <n v="1023.35"/>
+        <n v="457.6"/>
+        <n v="1300.93"/>
+        <n v="707.01"/>
+        <n v="265.87"/>
+        <n v="523.37"/>
+        <n v="1984.53"/>
+        <n v="389.22"/>
+        <n v="10013"/>
+        <n v="1235.8900000000001"/>
+        <n v="863.68"/>
+        <n v="1091.0999999999999"/>
+        <n v="396.11"/>
+        <n v="1852.82"/>
+        <n v="746.26"/>
+        <n v="661.71"/>
+        <n v="641.59"/>
+        <n v="10006"/>
+        <n v="799.53"/>
+        <n v="1470.86"/>
+        <n v="120.06"/>
+        <n v="680.77"/>
+        <n v="758.44"/>
+        <n v="129.81"/>
+        <n v="930.93"/>
+        <n v="1318.45"/>
+        <n v="920.19"/>
+        <n v="998.38"/>
+        <n v="622.54999999999995"/>
+        <n v="781.63"/>
+        <n v="1081.02"/>
+        <n v="752.98"/>
+        <n v="1436.28"/>
+        <n v="1041.8399999999999"/>
+        <n v="176.95"/>
+        <n v="895.53"/>
+        <n v="519"/>
+        <n v="267.12"/>
+        <n v="890.48"/>
+        <n v="836.33"/>
+        <n v="790.75"/>
+        <n v="868.55"/>
+        <n v="1075.0899999999999"/>
+        <n v="706.35"/>
+        <n v="453.74"/>
+        <n v="1316.09"/>
+        <n v="921.62"/>
+        <n v="870.42"/>
+        <n v="453.51"/>
+        <n v="1155.3399999999999"/>
+        <n v="256.8"/>
+        <n v="838.84"/>
+        <n v="919.61"/>
+        <n v="885.26"/>
+        <n v="464.6"/>
+        <n v="648.57000000000005"/>
+        <n v="756.75"/>
+        <n v="660.22"/>
+        <n v="275.93"/>
+        <n v="1032.69"/>
+        <n v="648.44000000000005"/>
+        <n v="108.23"/>
+        <n v="1137.1600000000001"/>
+        <n v="152.91999999999999"/>
+        <n v="1421.07"/>
+        <n v="444.76"/>
+        <n v="691.63"/>
+        <n v="785.37"/>
+        <n v="856.56"/>
+        <n v="167.65"/>
+        <n v="1064.4100000000001"/>
+        <n v="839.71"/>
+        <n v="481.21"/>
+        <n v="818.19"/>
+        <n v="944.96"/>
+        <n v="1672.71"/>
+        <n v="665.8"/>
+        <n v="183.1"/>
+        <n v="961.13"/>
+        <n v="1429.26"/>
+        <n v="1300.01"/>
+        <n v="1610.81"/>
+        <n v="508.66"/>
+        <n v="712.55"/>
+        <n v="1126.8900000000001"/>
+        <n v="895.93"/>
+        <n v="1386"/>
+        <n v="1481.76"/>
+        <n v="828.77"/>
+        <n v="721.11"/>
+        <n v="911.36"/>
+        <n v="1614.28"/>
+        <n v="1156.93"/>
+        <n v="1425.97"/>
+        <n v="677.55"/>
+        <n v="916.62"/>
+        <n v="1013.28"/>
+        <n v="656.1"/>
+        <n v="667.7"/>
+        <n v="969.34"/>
+        <n v="843.99"/>
+        <n v="1332.38"/>
+        <n v="1108.6199999999999"/>
+        <n v="897.29"/>
+        <n v="265.52"/>
+        <n v="316.74"/>
+        <n v="438.08"/>
+        <n v="1155.95"/>
+        <n v="796.52"/>
+        <n v="1200.17"/>
+        <n v="1996.92"/>
+        <n v="896.23"/>
+        <n v="295.45"/>
+        <n v="862.99"/>
+        <n v="947.64"/>
+        <n v="265.83999999999997"/>
+        <n v="728.45"/>
+        <n v="463.46"/>
+        <n v="1234.8800000000001"/>
+        <n v="790.7"/>
+        <n v="415.78"/>
+        <n v="872.34"/>
+        <n v="395.84"/>
+        <n v="247.93"/>
+        <n v="1045.8599999999999"/>
+        <n v="1396.84"/>
+        <n v="1086.6400000000001"/>
+        <n v="797.52"/>
+        <n v="374.63"/>
+        <n v="1651.76"/>
+        <n v="853.86"/>
+        <n v="1210.32"/>
+        <n v="624.91999999999996"/>
+        <n v="1229.76"/>
+        <n v="481.99"/>
+        <n v="638.53"/>
+        <n v="1509.47"/>
+        <n v="775.19"/>
+        <n v="599.34"/>
+        <n v="175.19"/>
+        <n v="748.35"/>
+        <n v="924.95"/>
+        <n v="853.76"/>
+        <n v="790.38"/>
+        <n v="455.83"/>
+        <n v="810.64"/>
+        <n v="128.41999999999999"/>
+        <n v="1956.52"/>
+        <n v="845.86"/>
+        <n v="306.45999999999998"/>
+        <n v="785.95"/>
+        <n v="922.87"/>
+        <n v="728.06"/>
+        <n v="527.12"/>
+        <n v="508.34"/>
+        <n v="1067.9000000000001"/>
+        <n v="528.86"/>
+        <n v="930.02"/>
+        <n v="253.15"/>
+        <n v="855.02"/>
+        <n v="1281"/>
+        <n v="1164.05"/>
+        <n v="1170.92"/>
+        <n v="1021.22"/>
+        <n v="1315.27"/>
+        <n v="644.80999999999995"/>
+        <n v="854.23"/>
+        <n v="1371.98"/>
+        <n v="558.07000000000005"/>
+        <n v="1069.08"/>
+        <n v="778.23"/>
+        <n v="216.93"/>
+        <n v="794.1"/>
+        <n v="1377.65"/>
+        <n v="1321.69"/>
+        <n v="200.87"/>
+        <n v="727.81"/>
+        <n v="644.95000000000005"/>
+        <n v="1127.6500000000001"/>
+        <n v="727.06"/>
+        <n v="1411.64"/>
+        <n v="891.18"/>
+        <n v="1155.56"/>
+        <n v="116.1"/>
+        <n v="749.33"/>
+        <n v="732.86"/>
+        <n v="1263.1099999999999"/>
+        <n v="721.99"/>
+        <n v="169.21"/>
+        <n v="934.22"/>
+        <n v="857.27"/>
+        <n v="917.25"/>
+        <n v="746.07"/>
+        <n v="294.94"/>
+        <n v="1137.32"/>
+        <n v="2015.04"/>
+        <n v="255.08"/>
+        <n v="1315.07"/>
+        <n v="1143.8399999999999"/>
+        <n v="1244.97"/>
+        <n v="149.24"/>
+        <n v="216.82"/>
+        <n v="1390.38"/>
+        <n v="661.3"/>
+        <n v="1046.17"/>
+        <n v="742.69"/>
+        <n v="595.70000000000005"/>
+        <n v="201.16"/>
+        <n v="638.6"/>
+        <n v="2091.58"/>
+        <n v="2156"/>
+        <n v="719.42"/>
+        <n v="239.25"/>
+        <n v="1071.8599999999999"/>
+        <n v="176.82"/>
+        <n v="671.87"/>
+        <n v="586.78"/>
+        <n v="901.36"/>
+        <n v="1315.74"/>
+        <n v="632.38"/>
+        <n v="1087.08"/>
+        <n v="608.08000000000004"/>
+        <n v="647.6"/>
+        <n v="1961.76"/>
+        <n v="964.35"/>
+        <n v="753.73"/>
+        <n v="827.25"/>
+        <n v="442.74"/>
+        <n v="978.74"/>
+        <n v="645.54999999999995"/>
+        <n v="759.9"/>
+        <n v="1828.2"/>
+        <n v="776.84"/>
+        <n v="1603.75"/>
+        <n v="618.42999999999995"/>
+        <n v="325.43"/>
+        <n v="502.04"/>
+        <n v="268.75"/>
+        <n v="1249.32"/>
+        <n v="632.26"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Gender_Clean" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City_Clean" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Occupation_Clean" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Income_Level" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="293">
+  <r>
+    <s v="CUS00148"/>
+    <d v="2025-01-04T00:00:00"/>
+    <x v="0"/>
+    <n v="46"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00196"/>
+    <d v="2025-01-05T00:00:00"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00115"/>
+    <d v="2025-01-07T00:00:00"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00006"/>
+    <d v="2025-01-08T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00103"/>
+    <d v="2025-01-08T00:00:00"/>
+    <x v="1"/>
+    <n v="66"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00157"/>
+    <d v="2025-01-10T00:00:00"/>
+    <x v="0"/>
+    <n v="51"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00076"/>
+    <d v="2025-01-10T00:00:00"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00067"/>
+    <d v="2025-01-13T00:00:00"/>
+    <x v="1"/>
+    <n v="19"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="7"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00287"/>
+    <d v="2025-01-14T00:00:00"/>
+    <x v="0"/>
+    <n v="19"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00257"/>
+    <d v="2025-01-16T00:00:00"/>
+    <x v="1"/>
+    <n v="43"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="9"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00279"/>
+    <d v="2025-01-17T00:00:00"/>
+    <x v="2"/>
+    <n v="18"/>
+    <x v="6"/>
+    <x v="4"/>
+    <x v="10"/>
+    <s v="Missing"/>
+    <s v="Garowe"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00270"/>
+    <d v="2025-01-19T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="11"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00005"/>
+    <d v="2025-01-20T00:00:00"/>
+    <x v="1"/>
+    <n v="49"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="12"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00186"/>
+    <d v="2025-01-21T00:00:00"/>
+    <x v="1"/>
+    <n v="53"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="13"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00252"/>
+    <d v="2025-01-22T00:00:00"/>
+    <x v="0"/>
+    <n v="70"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="14"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00030"/>
+    <d v="2025-01-23T00:00:00"/>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="15"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00235"/>
+    <d v="2025-01-24T00:00:00"/>
+    <x v="0"/>
+    <n v="19"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="16"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00052"/>
+    <d v="2025-01-25T00:00:00"/>
+    <x v="0"/>
+    <n v="63"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="17"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00058"/>
+    <d v="2025-02-03T00:00:00"/>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="18"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00181"/>
+    <d v="2025-02-03T00:00:00"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="19"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00206"/>
+    <d v="2025-02-06T00:00:00"/>
+    <x v="0"/>
+    <n v="20"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00230"/>
+    <d v="2025-02-08T00:00:00"/>
+    <x v="0"/>
+    <n v="62"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="20"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00025"/>
+    <d v="2025-02-15T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="21"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00211"/>
+    <d v="2025-02-15T00:00:00"/>
+    <x v="1"/>
+    <n v="66"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00207"/>
+    <d v="2025-02-17T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="6"/>
+    <x v="7"/>
+    <x v="23"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00203"/>
+    <d v="2025-02-18T00:00:00"/>
+    <x v="0"/>
+    <n v="35"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="24"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00202"/>
+    <d v="2025-02-21T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="25"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00223"/>
+    <d v="2025-02-27T00:00:00"/>
+    <x v="0"/>
+    <n v="34"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="26"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00231"/>
+    <d v="2025-02-27T00:00:00"/>
+    <x v="1"/>
+    <n v="54"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00292"/>
+    <d v="2025-03-03T00:00:00"/>
+    <x v="1"/>
+    <n v="46"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="27"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00156"/>
+    <d v="2025-03-04T00:00:00"/>
+    <x v="0"/>
+    <n v="37"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="28"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00072"/>
+    <d v="2025-03-05T00:00:00"/>
+    <x v="2"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="29"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00173"/>
+    <d v="2025-03-07T00:00:00"/>
+    <x v="2"/>
+    <n v="59"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="30"/>
+    <s v="Missing"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-03-12T00:00:00"/>
+    <x v="1"/>
+    <n v="21"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="31"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00218"/>
+    <d v="2025-03-13T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="32"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00137"/>
+    <d v="2025-03-15T00:00:00"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="33"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00208"/>
+    <d v="2025-03-15T00:00:00"/>
+    <x v="0"/>
+    <n v="66"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="34"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00259"/>
+    <d v="2025-03-16T00:00:00"/>
+    <x v="1"/>
+    <n v="21"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="35"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00136"/>
+    <d v="2025-03-18T00:00:00"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="36"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00081"/>
+    <d v="2025-03-19T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="37"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00111"/>
+    <d v="2025-03-25T00:00:00"/>
+    <x v="0"/>
+    <n v="48"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="38"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00138"/>
+    <d v="2025-03-26T00:00:00"/>
+    <x v="0"/>
+    <n v="22"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="39"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00276"/>
+    <d v="2025-03-28T00:00:00"/>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="40"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00277"/>
+    <d v="2025-03-28T00:00:00"/>
+    <x v="1"/>
+    <n v="39"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="41"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00080"/>
+    <d v="2025-03-29T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="42"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00124"/>
+    <d v="2025-03-31T00:00:00"/>
+    <x v="0"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="43"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00249"/>
+    <d v="2025-04-02T00:00:00"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="44"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00097"/>
+    <d v="2025-04-03T00:00:00"/>
+    <x v="1"/>
+    <n v="49"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00247"/>
+    <d v="2025-04-05T00:00:00"/>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="45"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00169"/>
+    <d v="2025-04-05T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="46"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00271"/>
+    <d v="2025-04-06T00:00:00"/>
+    <x v="0"/>
+    <n v="48"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="47"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00049"/>
+    <d v="2025-04-10T00:00:00"/>
+    <x v="0"/>
+    <n v="33"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="48"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00234"/>
+    <d v="2025-04-11T00:00:00"/>
+    <x v="2"/>
+    <n v="40"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="49"/>
+    <s v="Missing"/>
+    <s v="Kismayo"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00132"/>
+    <d v="2025-04-16T00:00:00"/>
+    <x v="2"/>
+    <n v="41"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="50"/>
+    <s v="Missing"/>
+    <s v="Bosaso"/>
+    <s v="Healthcare"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00119"/>
+    <d v="2025-04-16T00:00:00"/>
+    <x v="0"/>
+    <n v="65"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="51"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00027"/>
+    <d v="2025-04-18T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00258"/>
+    <d v="2025-04-20T00:00:00"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="52"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00079"/>
+    <d v="2025-04-21T00:00:00"/>
+    <x v="1"/>
+    <n v="39"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="53"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00121"/>
+    <d v="2025-04-24T00:00:00"/>
+    <x v="1"/>
+    <n v="38"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="54"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00288"/>
+    <d v="2025-04-24T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="55"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00002"/>
+    <d v="2025-04-24T00:00:00"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="56"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00226"/>
+    <d v="2025-04-25T00:00:00"/>
+    <x v="1"/>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="57"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00217"/>
+    <d v="2025-04-25T00:00:00"/>
+    <x v="1"/>
+    <n v="56"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="58"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-04-26T00:00:00"/>
+    <x v="1"/>
+    <n v="38"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="59"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00146"/>
+    <d v="2025-04-26T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="60"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00133"/>
+    <d v="2025-04-28T00:00:00"/>
+    <x v="0"/>
+    <n v="58"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="61"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00109"/>
+    <d v="2025-04-29T00:00:00"/>
+    <x v="0"/>
+    <n v="43"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="62"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00246"/>
+    <d v="2025-04-30T00:00:00"/>
+    <x v="0"/>
+    <n v="41"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="63"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00261"/>
+    <d v="2025-05-01T00:00:00"/>
+    <x v="0"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="64"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00149"/>
+    <d v="2025-05-01T00:00:00"/>
+    <x v="1"/>
+    <n v="55"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="65"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00227"/>
+    <d v="2025-05-03T00:00:00"/>
+    <x v="0"/>
+    <n v="37"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="66"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00262"/>
+    <d v="2025-05-03T00:00:00"/>
+    <x v="1"/>
+    <n v="67"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00245"/>
+    <d v="2025-05-04T00:00:00"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="67"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00091"/>
+    <d v="2025-05-14T00:00:00"/>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="68"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00017"/>
+    <d v="2025-05-15T00:00:00"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="69"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00187"/>
+    <d v="2025-05-18T00:00:00"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="70"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00128"/>
+    <d v="2025-05-24T00:00:00"/>
+    <x v="1"/>
+    <n v="21"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="71"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00134"/>
+    <d v="2025-05-25T00:00:00"/>
+    <x v="0"/>
+    <n v="38"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="72"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00012"/>
+    <d v="2025-05-27T00:00:00"/>
+    <x v="0"/>
+    <n v="65"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="73"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00166"/>
+    <d v="2025-05-28T00:00:00"/>
+    <x v="1"/>
+    <n v="41"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="74"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00224"/>
+    <d v="2025-05-30T00:00:00"/>
+    <x v="0"/>
+    <n v="48"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="75"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00241"/>
+    <d v="2025-06-01T00:00:00"/>
+    <x v="1"/>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="76"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00021"/>
+    <d v="2025-06-04T00:00:00"/>
+    <x v="0"/>
+    <n v="19"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00239"/>
+    <d v="2025-06-08T00:00:00"/>
+    <x v="2"/>
+    <n v="38"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="77"/>
+    <s v="Missing"/>
+    <s v="Baidoa"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00222"/>
+    <d v="2025-06-12T00:00:00"/>
+    <x v="0"/>
+    <n v="58"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="78"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00197"/>
+    <d v="2025-06-13T00:00:00"/>
+    <x v="0"/>
+    <n v="48"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="79"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00083"/>
+    <d v="2025-06-14T00:00:00"/>
+    <x v="1"/>
+    <n v="68"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="80"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00273"/>
+    <d v="2025-06-16T00:00:00"/>
+    <x v="0"/>
+    <n v="23"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="81"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00219"/>
+    <d v="2025-06-19T00:00:00"/>
+    <x v="0"/>
+    <n v="42"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="82"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00048"/>
+    <d v="2025-06-20T00:00:00"/>
+    <x v="1"/>
+    <n v="36"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="83"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00003"/>
+    <d v="2025-06-22T00:00:00"/>
+    <x v="0"/>
+    <n v="67"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00272"/>
+    <d v="2025-06-24T00:00:00"/>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="5"/>
+    <x v="7"/>
+    <x v="84"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Missing"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00189"/>
+    <d v="2025-06-25T00:00:00"/>
+    <x v="1"/>
+    <n v="28"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="85"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00043"/>
+    <d v="2025-06-25T00:00:00"/>
+    <x v="2"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="86"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00019"/>
+    <d v="2025-06-29T00:00:00"/>
+    <x v="1"/>
+    <n v="54"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="87"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00042"/>
+    <d v="2025-07-01T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="88"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00152"/>
+    <d v="2025-07-02T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="89"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00214"/>
+    <d v="2025-07-07T00:00:00"/>
+    <x v="0"/>
+    <n v="56"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="90"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00183"/>
+    <d v="2025-07-08T00:00:00"/>
+    <x v="0"/>
+    <n v="18"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="91"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00150"/>
+    <d v="2025-07-08T00:00:00"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="92"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00004"/>
+    <d v="2025-07-09T00:00:00"/>
+    <x v="0"/>
+    <n v="42"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="93"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00286"/>
+    <d v="2025-07-10T00:00:00"/>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="94"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00135"/>
+    <d v="2025-07-12T00:00:00"/>
+    <x v="0"/>
+    <n v="55"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="95"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00254"/>
+    <d v="2025-07-19T00:00:00"/>
+    <x v="1"/>
+    <n v="28"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="96"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00100"/>
+    <d v="2025-07-20T00:00:00"/>
+    <x v="0"/>
+    <n v="64"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="97"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00060"/>
+    <d v="2025-07-23T00:00:00"/>
+    <x v="0"/>
+    <n v="47"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="98"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00078"/>
+    <d v="2025-07-24T00:00:00"/>
+    <x v="0"/>
+    <n v="69"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="99"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00154"/>
+    <d v="2025-07-26T00:00:00"/>
+    <x v="0"/>
+    <n v="60"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="100"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00175"/>
+    <d v="2025-07-30T00:00:00"/>
+    <x v="0"/>
+    <n v="59"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="101"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00140"/>
+    <d v="2025-08-02T00:00:00"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="102"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00210"/>
+    <d v="2025-08-04T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="103"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00007"/>
+    <d v="2025-08-05T00:00:00"/>
+    <x v="1"/>
+    <n v="45"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="104"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00065"/>
+    <d v="2025-08-05T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="2"/>
+    <x v="7"/>
+    <x v="105"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00106"/>
+    <d v="2025-08-06T00:00:00"/>
+    <x v="1"/>
+    <n v="48"/>
+    <x v="4"/>
+    <x v="8"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00228"/>
+    <d v="2025-08-06T00:00:00"/>
+    <x v="1"/>
+    <n v="59"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00194"/>
+    <d v="2025-08-07T00:00:00"/>
+    <x v="1"/>
+    <n v="50"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="106"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00131"/>
+    <d v="2025-08-08T00:00:00"/>
+    <x v="0"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-08-09T00:00:00"/>
+    <x v="1"/>
+    <n v="53"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="107"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00160"/>
+    <d v="2025-08-10T00:00:00"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="108"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00053"/>
+    <d v="2025-08-12T00:00:00"/>
+    <x v="1"/>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="109"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00102"/>
+    <d v="2025-08-12T00:00:00"/>
+    <x v="1"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="110"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00180"/>
+    <d v="2025-08-14T00:00:00"/>
+    <x v="1"/>
+    <n v="61"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="111"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00255"/>
+    <d v="2025-08-15T00:00:00"/>
+    <x v="1"/>
+    <n v="21"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="112"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00221"/>
+    <d v="2025-08-15T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="113"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00268"/>
+    <d v="2025-08-15T00:00:00"/>
+    <x v="0"/>
+    <n v="49"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="114"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00275"/>
+    <d v="2025-08-15T00:00:00"/>
+    <x v="1"/>
+    <n v="59"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="115"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00122"/>
+    <d v="2025-08-17T00:00:00"/>
+    <x v="0"/>
+    <n v="60"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="116"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00118"/>
+    <d v="2025-08-21T00:00:00"/>
+    <x v="1"/>
+    <n v="60"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Student"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00182"/>
+    <d v="2025-08-23T00:00:00"/>
+    <x v="1"/>
+    <n v="43"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="117"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00237"/>
+    <d v="2025-08-23T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="118"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00171"/>
+    <d v="2025-08-24T00:00:00"/>
+    <x v="1"/>
+    <n v="39"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="119"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00209"/>
+    <d v="2025-08-26T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00143"/>
+    <d v="2025-08-27T00:00:00"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="120"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00056"/>
+    <d v="2025-08-30T00:00:00"/>
+    <x v="1"/>
+    <n v="67"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="121"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00285"/>
+    <d v="2025-08-31T00:00:00"/>
+    <x v="0"/>
+    <n v="22"/>
+    <x v="4"/>
+    <x v="7"/>
+    <x v="122"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00229"/>
+    <d v="2025-09-02T00:00:00"/>
+    <x v="0"/>
+    <n v="46"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="123"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-09-08T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="124"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00063"/>
+    <d v="2025-09-13T00:00:00"/>
+    <x v="0"/>
+    <n v="62"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="125"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00213"/>
+    <d v="2025-09-17T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="126"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00112"/>
+    <d v="2025-09-18T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="127"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00216"/>
+    <d v="2025-09-19T00:00:00"/>
+    <x v="0"/>
+    <n v="19"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="128"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00164"/>
+    <d v="2025-09-25T00:00:00"/>
+    <x v="0"/>
+    <n v="58"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="129"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00040"/>
+    <d v="2025-09-25T00:00:00"/>
+    <x v="0"/>
+    <n v="66"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="130"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00232"/>
+    <d v="2025-09-28T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="4"/>
+    <x v="7"/>
+    <x v="131"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00123"/>
+    <d v="2025-09-30T00:00:00"/>
+    <x v="0"/>
+    <n v="66"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="132"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00264"/>
+    <d v="2025-10-01T00:00:00"/>
+    <x v="1"/>
+    <n v="68"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="133"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00198"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="33"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="134"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00033"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="1"/>
+    <n v="54"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="135"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00139"/>
+    <d v="2025-10-04T00:00:00"/>
+    <x v="1"/>
+    <n v="27"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="136"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00077"/>
+    <d v="2025-10-07T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="137"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00153"/>
+    <d v="2025-10-08T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="138"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00144"/>
+    <d v="2025-10-11T00:00:00"/>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="139"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00069"/>
+    <d v="2025-10-12T00:00:00"/>
+    <x v="2"/>
+    <n v="24"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="140"/>
+    <s v="Missing"/>
+    <s v="Bosaso"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00086"/>
+    <d v="2025-10-13T00:00:00"/>
+    <x v="1"/>
+    <n v="123"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="141"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-10-15T00:00:00"/>
+    <x v="0"/>
+    <n v="41"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="142"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00256"/>
+    <d v="2025-10-20T00:00:00"/>
+    <x v="2"/>
+    <n v="21"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="143"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00088"/>
+    <d v="2025-10-21T00:00:00"/>
+    <x v="0"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="144"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00026"/>
+    <d v="2025-10-24T00:00:00"/>
+    <x v="0"/>
+    <n v="20"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="145"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00282"/>
+    <d v="2025-10-26T00:00:00"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="146"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-10-27T00:00:00"/>
+    <x v="1"/>
+    <n v="68"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="147"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00114"/>
+    <d v="2025-10-28T00:00:00"/>
+    <x v="1"/>
+    <n v="63"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="148"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00051"/>
+    <d v="2025-10-30T00:00:00"/>
+    <x v="0"/>
+    <n v="30"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="149"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00089"/>
+    <d v="2025-11-02T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="150"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00242"/>
+    <d v="2025-11-05T00:00:00"/>
+    <x v="0"/>
+    <n v="20"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="151"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00105"/>
+    <d v="2025-11-07T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="152"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00172"/>
+    <d v="2025-11-09T00:00:00"/>
+    <x v="0"/>
+    <n v="70"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="153"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00161"/>
+    <d v="2025-11-12T00:00:00"/>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="154"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00225"/>
+    <d v="2025-11-14T00:00:00"/>
+    <x v="2"/>
+    <n v="70"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="155"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00028"/>
+    <d v="2025-11-15T00:00:00"/>
+    <x v="1"/>
+    <n v="53"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="156"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00126"/>
+    <d v="2025-11-17T00:00:00"/>
+    <x v="2"/>
+    <n v="26"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="157"/>
+    <s v="Missing"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2025-11-21T00:00:00"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="158"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00125"/>
+    <d v="2025-11-21T00:00:00"/>
+    <x v="1"/>
+    <n v="35"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="159"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00110"/>
+    <d v="2025-11-22T00:00:00"/>
+    <x v="0"/>
+    <n v="50"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00001"/>
+    <d v="2025-11-23T00:00:00"/>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="160"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00289"/>
+    <d v="2025-11-30T00:00:00"/>
+    <x v="1"/>
+    <n v="41"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="161"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00274"/>
+    <d v="2025-12-07T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="162"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00167"/>
+    <d v="2025-12-07T00:00:00"/>
+    <x v="0"/>
+    <n v="37"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="163"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00260"/>
+    <d v="2025-12-07T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="164"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00047"/>
+    <d v="2025-12-09T00:00:00"/>
+    <x v="0"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="165"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00094"/>
+    <d v="2025-12-10T00:00:00"/>
+    <x v="1"/>
+    <n v="55"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="166"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00195"/>
+    <d v="2025-12-15T00:00:00"/>
+    <x v="1"/>
+    <n v="31"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="167"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00184"/>
+    <d v="2025-12-17T00:00:00"/>
+    <x v="2"/>
+    <n v="64"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="168"/>
+    <s v="Missing"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00107"/>
+    <d v="2025-12-23T00:00:00"/>
+    <x v="1"/>
+    <n v="46"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="169"/>
+    <s v="Male"/>
+    <s v="Missing"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00010"/>
+    <d v="2025-12-23T00:00:00"/>
+    <x v="1"/>
+    <n v="55"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="170"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00008"/>
+    <d v="2025-12-23T00:00:00"/>
+    <x v="0"/>
+    <n v="60"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="171"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00045"/>
+    <d v="2025-12-26T00:00:00"/>
+    <x v="1"/>
+    <n v="60"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="172"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00046"/>
+    <d v="2025-12-28T00:00:00"/>
+    <x v="0"/>
+    <n v="38"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="173"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00116"/>
+    <d v="2025-12-29T00:00:00"/>
+    <x v="0"/>
+    <n v="70"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="174"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00266"/>
+    <d v="2025-12-30T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="175"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00016"/>
+    <d v="2025-12-31T00:00:00"/>
+    <x v="2"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="176"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00035"/>
+    <d v="2025-12-31T00:00:00"/>
+    <x v="0"/>
+    <n v="41"/>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="177"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00269"/>
+    <d v="2026-01-04T00:00:00"/>
+    <x v="0"/>
+    <n v="65"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="178"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00141"/>
+    <d v="2026-01-09T00:00:00"/>
+    <x v="0"/>
+    <n v="57"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="179"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00087"/>
+    <d v="2026-01-11T00:00:00"/>
+    <x v="0"/>
+    <n v="70"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="180"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00200"/>
+    <d v="2026-01-15T00:00:00"/>
+    <x v="0"/>
+    <n v="21"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="181"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00054"/>
+    <d v="2026-01-15T00:00:00"/>
+    <x v="1"/>
+    <n v="63"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="182"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2026-01-16T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00165"/>
+    <d v="2026-01-17T00:00:00"/>
+    <x v="0"/>
+    <n v="37"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00095"/>
+    <d v="2026-01-19T00:00:00"/>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="183"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00284"/>
+    <d v="2026-01-19T00:00:00"/>
+    <x v="0"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="184"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00098"/>
+    <d v="2026-01-26T00:00:00"/>
+    <x v="0"/>
+    <n v="47"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="185"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00014"/>
+    <d v="2026-01-30T00:00:00"/>
+    <x v="0"/>
+    <n v="49"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="186"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00283"/>
+    <d v="2026-02-01T00:00:00"/>
+    <x v="1"/>
+    <n v="55"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00062"/>
+    <d v="2026-02-04T00:00:00"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00147"/>
+    <d v="2026-02-06T00:00:00"/>
+    <x v="1"/>
+    <n v="36"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="187"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00191"/>
+    <d v="2026-02-06T00:00:00"/>
+    <x v="0"/>
+    <n v="65"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="188"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2026-02-07T00:00:00"/>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="189"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00096"/>
+    <d v="2026-02-07T00:00:00"/>
+    <x v="2"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="190"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00073"/>
+    <d v="2026-02-08T00:00:00"/>
+    <x v="0"/>
+    <n v="46"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="191"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00248"/>
+    <d v="2026-02-11T00:00:00"/>
+    <x v="0"/>
+    <n v="30"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="192"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00240"/>
+    <d v="2026-02-12T00:00:00"/>
+    <x v="0"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="193"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00236"/>
+    <d v="2026-02-14T00:00:00"/>
+    <x v="0"/>
+    <n v="22"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="194"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00190"/>
+    <d v="2026-02-15T00:00:00"/>
+    <x v="0"/>
+    <n v="58"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="195"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00201"/>
+    <d v="2026-02-17T00:00:00"/>
+    <x v="0"/>
+    <n v="55"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="196"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00188"/>
+    <d v="2026-02-20T00:00:00"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="197"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00029"/>
+    <d v="2026-02-24T00:00:00"/>
+    <x v="1"/>
+    <n v="50"/>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="198"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00220"/>
+    <d v="2026-02-27T00:00:00"/>
+    <x v="0"/>
+    <n v="60"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="199"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00085"/>
+    <d v="2026-02-28T00:00:00"/>
+    <x v="0"/>
+    <n v="62"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="200"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00023"/>
+    <d v="2026-03-01T00:00:00"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="201"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00185"/>
+    <d v="2026-03-08T00:00:00"/>
+    <x v="0"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="202"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00013"/>
+    <d v="2026-03-09T00:00:00"/>
+    <x v="0"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="203"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00108"/>
+    <d v="2026-03-12T00:00:00"/>
+    <x v="0"/>
+    <n v="52"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="204"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00162"/>
+    <d v="2026-03-13T00:00:00"/>
+    <x v="0"/>
+    <n v="29"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="205"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00104"/>
+    <d v="2026-03-13T00:00:00"/>
+    <x v="1"/>
+    <n v="43"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="206"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00018"/>
+    <d v="2026-03-13T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="207"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00068"/>
+    <d v="2026-03-18T00:00:00"/>
+    <x v="1"/>
+    <n v="45"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="208"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00064"/>
+    <d v="2026-03-22T00:00:00"/>
+    <x v="1"/>
+    <n v="64"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="209"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00278"/>
+    <d v="2026-03-28T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="210"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00039"/>
+    <d v="2026-03-28T00:00:00"/>
+    <x v="0"/>
+    <n v="63"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="211"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00168"/>
+    <d v="2026-04-04T00:00:00"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="212"/>
+    <s v="Female"/>
+    <s v="Missing"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00142"/>
+    <d v="2026-04-12T00:00:00"/>
+    <x v="1"/>
+    <n v="24"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="213"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00015"/>
+    <d v="2026-04-15T00:00:00"/>
+    <x v="1"/>
+    <n v="70"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="214"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00024"/>
+    <d v="2026-04-17T00:00:00"/>
+    <x v="0"/>
+    <n v="18"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="215"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00127"/>
+    <d v="2026-04-21T00:00:00"/>
+    <x v="0"/>
+    <n v="46"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="216"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00145"/>
+    <d v="2026-04-24T00:00:00"/>
+    <x v="0"/>
+    <n v="57"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="217"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00243"/>
+    <d v="2026-04-25T00:00:00"/>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="218"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00032"/>
+    <d v="2026-04-25T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="219"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00050"/>
+    <d v="2026-05-04T00:00:00"/>
+    <x v="0"/>
+    <n v="18"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="220"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00267"/>
+    <d v="2026-05-04T00:00:00"/>
+    <x v="0"/>
+    <n v="43"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="221"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00066"/>
+    <d v="2026-05-06T00:00:00"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="222"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00253"/>
+    <d v="2026-05-08T00:00:00"/>
+    <x v="1"/>
+    <n v="67"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="223"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="0"/>
+    <n v="50"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="224"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00059"/>
+    <d v="2026-05-15T00:00:00"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="8"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00074"/>
+    <d v="2026-05-15T00:00:00"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="225"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00037"/>
+    <d v="2026-05-15T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="226"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00041"/>
+    <d v="2026-05-15T00:00:00"/>
+    <x v="2"/>
+    <n v="65"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="227"/>
+    <s v="Missing"/>
+    <s v="Baidoa"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00082"/>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="0"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="228"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00155"/>
+    <d v="2026-05-17T00:00:00"/>
+    <x v="0"/>
+    <n v="27"/>
+    <x v="4"/>
+    <x v="7"/>
+    <x v="229"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00233"/>
+    <d v="2026-05-17T00:00:00"/>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="230"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00061"/>
+    <d v="2026-05-19T00:00:00"/>
+    <x v="0"/>
+    <n v="53"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00250"/>
+    <d v="2026-05-21T00:00:00"/>
+    <x v="0"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="231"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00092"/>
+    <d v="2026-05-24T00:00:00"/>
+    <x v="1"/>
+    <n v="69"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="232"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00192"/>
+    <d v="2026-05-26T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="233"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00290"/>
+    <d v="2026-05-27T00:00:00"/>
+    <x v="0"/>
+    <n v="36"/>
+    <x v="4"/>
+    <x v="7"/>
+    <x v="234"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Missing"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00281"/>
+    <d v="2026-05-31T00:00:00"/>
+    <x v="0"/>
+    <n v="34"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="235"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00176"/>
+    <d v="2026-05-31T00:00:00"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="236"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00129"/>
+    <d v="2026-05-31T00:00:00"/>
+    <x v="2"/>
+    <n v="49"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="237"/>
+    <s v="Missing"/>
+    <s v="Kismayo"/>
+    <s v="Self-Employed"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00199"/>
+    <d v="2026-06-10T00:00:00"/>
+    <x v="1"/>
+    <n v="65"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="238"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00238"/>
+    <d v="2026-06-11T00:00:00"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="239"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00280"/>
+    <d v="2026-06-14T00:00:00"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="240"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00212"/>
+    <d v="2026-06-16T00:00:00"/>
+    <x v="1"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="241"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00178"/>
+    <d v="2026-06-17T00:00:00"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="242"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00075"/>
+    <d v="2026-06-17T00:00:00"/>
+    <x v="0"/>
+    <n v="47"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="243"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00070"/>
+    <d v="2026-06-24T00:00:00"/>
+    <x v="1"/>
+    <n v="38"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="244"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00093"/>
+    <d v="2026-07-02T00:00:00"/>
+    <x v="1"/>
+    <n v="59"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="245"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00193"/>
+    <d v="2026-07-07T00:00:00"/>
+    <x v="1"/>
+    <n v="61"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="246"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="0"/>
+    <n v="61"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="247"/>
+    <s v="Female"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00036"/>
+    <d v="2026-07-09T00:00:00"/>
+    <x v="0"/>
+    <n v="45"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="248"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <m/>
+    <d v="2026-07-19T00:00:00"/>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="249"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00163"/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="1"/>
+    <n v="53"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="250"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00291"/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="1"/>
+    <n v="19"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="251"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Engineer"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00084"/>
+    <d v="2026-07-25T00:00:00"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="252"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00011"/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="2"/>
+    <n v="70"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="253"/>
+    <s v="Missing"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00158"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="24"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="254"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00031"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="255"/>
+    <s v="Female"/>
+    <s v="Baidoa"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00215"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="256"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00265"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="257"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00090"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="258"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00034"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="39"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="259"/>
+    <s v="Male"/>
+    <s v="Baidoa"/>
+    <s v="Teacher"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00205"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="260"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Self-Employed"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00049"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="44"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="48"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00055"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="45"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="261"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Healthcare"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00057"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="46"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="262"/>
+    <s v="Male"/>
+    <s v="Kismayo"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00071"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="48"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="263"/>
+    <s v="Female"/>
+    <s v="Garowe"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <m/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="50"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="264"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Business Owner"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00020"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="53"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="265"/>
+    <s v="Female"/>
+    <s v="Bosaso"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00130"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="55"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="266"/>
+    <s v="Female"/>
+    <s v="Kismayo"/>
+    <s v="Engineer"/>
+    <s v="High"/>
+  </r>
+  <r>
+    <s v="CUS00022"/>
+    <s v="Missing"/>
+    <x v="0"/>
+    <n v="55"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="267"/>
+    <s v="Female"/>
+    <s v="Mogadishu"/>
+    <s v="Civil Servant"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00174"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="55"/>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="268"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Teacher"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00177"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="57"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="269"/>
+    <s v="Male"/>
+    <s v="Mogadishu"/>
+    <s v="Healthcare"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <m/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="63"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="270"/>
+    <s v="Male"/>
+    <s v="Hargeisa"/>
+    <s v="Student"/>
+    <s v="Low"/>
+  </r>
+  <r>
+    <s v="CUS00099"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="70"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="271"/>
+    <s v="Male"/>
+    <s v="Bosaso"/>
+    <s v="Business Owner"/>
+    <s v="Medium"/>
+  </r>
+  <r>
+    <s v="CUS00170"/>
+    <s v="Missing"/>
+    <x v="1"/>
+    <n v="107"/>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="272"/>
+    <s v="Male"/>
+    <s v="Garowe"/>
+    <s v="Engineer"/>
+    <s v="Low"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A5:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="165" showAll="0">
+      <items count="274">
+        <item x="94"/>
+        <item x="216"/>
+        <item x="53"/>
+        <item x="9"/>
+        <item x="179"/>
+        <item x="56"/>
+        <item x="233"/>
+        <item x="96"/>
+        <item x="102"/>
+        <item x="221"/>
+        <item x="172"/>
+        <item x="247"/>
+        <item x="67"/>
+        <item x="110"/>
+        <item x="208"/>
+        <item x="240"/>
+        <item x="20"/>
+        <item x="234"/>
+        <item x="204"/>
+        <item x="245"/>
+        <item x="156"/>
+        <item x="191"/>
+        <item x="229"/>
+        <item x="83"/>
+        <item x="137"/>
+        <item x="148"/>
+        <item x="37"/>
+        <item x="70"/>
+        <item x="270"/>
+        <item x="91"/>
+        <item x="7"/>
+        <item x="226"/>
+        <item x="145"/>
+        <item x="182"/>
+        <item x="10"/>
+        <item x="138"/>
+        <item x="268"/>
+        <item x="161"/>
+        <item x="40"/>
+        <item x="155"/>
+        <item x="45"/>
+        <item x="25"/>
+        <item x="153"/>
+        <item x="139"/>
+        <item x="260"/>
+        <item x="98"/>
+        <item x="81"/>
+        <item x="77"/>
+        <item x="177"/>
+        <item x="34"/>
+        <item x="150"/>
+        <item x="87"/>
+        <item x="105"/>
+        <item x="167"/>
+        <item x="23"/>
+        <item x="269"/>
+        <item x="187"/>
+        <item x="115"/>
+        <item x="69"/>
+        <item x="38"/>
+        <item x="18"/>
+        <item x="186"/>
+        <item x="189"/>
+        <item x="201"/>
+        <item x="16"/>
+        <item x="249"/>
+        <item x="239"/>
+        <item x="171"/>
+        <item x="2"/>
+        <item x="254"/>
+        <item x="267"/>
+        <item x="61"/>
+        <item x="165"/>
+        <item x="272"/>
+        <item x="252"/>
+        <item x="168"/>
+        <item x="241"/>
+        <item x="49"/>
+        <item x="198"/>
+        <item x="210"/>
+        <item x="262"/>
+        <item x="24"/>
+        <item x="255"/>
+        <item x="93"/>
+        <item x="88"/>
+        <item x="130"/>
+        <item x="90"/>
+        <item x="236"/>
+        <item x="48"/>
+        <item x="109"/>
+        <item x="131"/>
+        <item x="248"/>
+        <item x="27"/>
+        <item x="127"/>
+        <item x="54"/>
+        <item x="99"/>
+        <item x="76"/>
+        <item x="36"/>
+        <item x="116"/>
+        <item x="244"/>
+        <item x="122"/>
+        <item x="220"/>
+        <item x="212"/>
+        <item x="209"/>
+        <item x="185"/>
+        <item x="149"/>
+        <item x="218"/>
+        <item x="238"/>
+        <item x="225"/>
+        <item x="47"/>
+        <item x="173"/>
+        <item x="217"/>
+        <item x="64"/>
+        <item x="258"/>
+        <item x="89"/>
+        <item x="55"/>
+        <item x="263"/>
+        <item x="170"/>
+        <item x="265"/>
+        <item x="203"/>
+        <item x="62"/>
+        <item x="100"/>
+        <item x="183"/>
+        <item x="3"/>
+        <item x="176"/>
+        <item x="152"/>
+        <item x="73"/>
+        <item x="205"/>
+        <item x="141"/>
+        <item x="160"/>
+        <item x="51"/>
+        <item x="178"/>
+        <item x="106"/>
+        <item x="259"/>
+        <item x="121"/>
+        <item x="26"/>
+        <item x="72"/>
+        <item x="15"/>
+        <item x="84"/>
+        <item x="104"/>
+        <item x="133"/>
+        <item x="181"/>
+        <item x="175"/>
+        <item x="163"/>
+        <item x="199"/>
+        <item x="192"/>
+        <item x="101"/>
+        <item x="223"/>
+        <item x="146"/>
+        <item x="43"/>
+        <item x="74"/>
+        <item x="80"/>
+        <item x="154"/>
+        <item x="6"/>
+        <item x="86"/>
+        <item x="71"/>
+        <item x="214"/>
+        <item x="68"/>
+        <item x="118"/>
+        <item x="144"/>
+        <item x="136"/>
+        <item x="250"/>
+        <item x="123"/>
+        <item x="128"/>
+        <item x="224"/>
+        <item x="85"/>
+        <item x="59"/>
+        <item x="79"/>
+        <item x="184"/>
+        <item x="8"/>
+        <item x="174"/>
+        <item x="13"/>
+        <item x="190"/>
+        <item x="57"/>
+        <item x="222"/>
+        <item x="107"/>
+        <item x="147"/>
+        <item x="30"/>
+        <item x="17"/>
+        <item x="111"/>
+        <item x="32"/>
+        <item x="257"/>
+        <item x="132"/>
+        <item x="261"/>
+        <item x="60"/>
+        <item x="129"/>
+        <item x="11"/>
+        <item x="196"/>
+        <item x="33"/>
+        <item x="12"/>
+        <item x="92"/>
+        <item x="66"/>
+        <item x="157"/>
+        <item x="237"/>
+        <item x="103"/>
+        <item x="188"/>
+        <item x="202"/>
+        <item x="246"/>
+        <item x="75"/>
+        <item x="63"/>
+        <item x="19"/>
+        <item x="159"/>
+        <item x="253"/>
+        <item x="44"/>
+        <item x="135"/>
+        <item x="117"/>
+        <item x="211"/>
+        <item x="95"/>
+        <item x="227"/>
+        <item x="231"/>
+        <item x="31"/>
+        <item x="82"/>
+        <item x="215"/>
+        <item x="140"/>
+        <item x="125"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="142"/>
+        <item x="164"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="166"/>
+        <item x="151"/>
+        <item x="42"/>
+        <item x="232"/>
+        <item x="271"/>
+        <item x="1"/>
+        <item x="219"/>
+        <item x="193"/>
+        <item x="113"/>
+        <item x="35"/>
+        <item x="230"/>
+        <item x="197"/>
+        <item x="251"/>
+        <item x="78"/>
+        <item x="58"/>
+        <item x="207"/>
+        <item x="134"/>
+        <item x="200"/>
+        <item x="206"/>
+        <item x="119"/>
+        <item x="235"/>
+        <item x="158"/>
+        <item x="213"/>
+        <item x="97"/>
+        <item x="126"/>
+        <item x="112"/>
+        <item x="65"/>
+        <item x="0"/>
+        <item x="52"/>
+        <item x="120"/>
+        <item x="169"/>
+        <item x="29"/>
+        <item x="5"/>
+        <item x="266"/>
+        <item x="114"/>
+        <item x="124"/>
+        <item x="162"/>
+        <item x="108"/>
+        <item x="28"/>
+        <item x="264"/>
+        <item x="46"/>
+        <item x="180"/>
+        <item x="256"/>
+        <item x="4"/>
+        <item x="39"/>
+        <item x="143"/>
+        <item x="228"/>
+        <item x="14"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="50"/>
+        <item x="41"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24051,7 +29411,7 @@
     <sortCondition ref="B2:B294"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="colorScale" priority="20">
@@ -24159,7 +29519,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24468,7 +29828,7 @@
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46250.476986689813</v>
+        <v>46250.679481944448</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>354</v>
@@ -24541,10 +29901,93 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A5:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="186" width="7.5703125" customWidth="1"/>
+    <col min="273" max="274" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:2">
+      <c r="A5" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="20">
+        <v>19068.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="20">
+        <v>39854.100000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="20">
+        <v>17991.009999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="20">
+        <v>38385.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="20">
+        <v>30250.91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B11" s="20">
+        <v>13639.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20">
+        <v>111503.65999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="20">
+        <v>270693.18999999994</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="12" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="375">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -1142,7 +1142,28 @@
     <t>Grand Total</t>
   </si>
   <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
     <t>Sum of Monthly_Income</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Count of Customer_ID</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Average of Monthly_Income</t>
   </si>
 </sst>
 </file>
@@ -1310,6 +1331,16 @@
   <dxfs count="6">
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C6500"/>
       </font>
       <fill>
@@ -1332,16 +1363,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1397,6 +1418,34 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Total Income by City</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1431,6 +1480,66 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent2"/>
@@ -1858,13 +1967,4229 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Customer Demographic Data Analysis Data.xlsx]PivotTables!PivotTable4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Income by Occupation</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="1.3888888888888888E-2"/>
+              <c:y val="-0.31944444444444448"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="1.1111111111111112E-2"/>
+              <c:y val="-0.18055555555555555"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="2.7777777777777779E-3"/>
+              <c:y val="-6.4814814814814811E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0"/>
+              <c:y val="-0.23148148148148148"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="1.6666666666666566E-2"/>
+              <c:y val="-0.2361111111111111"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-1.0185067526415994E-16"/>
+              <c:y val="-9.2592592592592671E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="1.3888888888888888E-2"/>
+              <c:y val="-0.23148148148148157"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-2.7777777777777779E-3"/>
+              <c:y val="-9.7222222222222224E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="8.3333333333333332E-3"/>
+              <c:y val="-0.18518518518518526"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$B$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$A$28:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Business Owner</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Civil Servant</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Engineer</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Healthcare</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Missing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Self-Employed</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Student</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Teacher</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$B$28:$B$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>63062.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30275.03000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43298.039999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41695.880000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9200.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>42372.009999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11241.05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29549.109999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5E02-43F0-9255-F974DF501E5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1701217007"/>
+        <c:axId val="1701212847"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1701217007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1701212847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1701212847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1701217007"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Customer Demographic Data Analysis Data.xlsx]PivotTables!PivotTable3</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t> Gender × City (Rows + Columns)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$L$6:$L$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Female</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$K$8:$K$15</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Baidoa</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bosaso</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Garowe</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hargeisa</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kismayo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Missing</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mogadishu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$L$8:$L$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>53</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2FCA-488C-BB5E-38EE7C9EA65C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$M$6:$M$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Male</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$K$8:$K$15</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Baidoa</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bosaso</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Garowe</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hargeisa</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kismayo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Missing</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mogadishu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$M$8:$M$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2FCA-488C-BB5E-38EE7C9EA65C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$N$6:$N$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Missing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$K$8:$K$15</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Baidoa</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bosaso</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Garowe</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hargeisa</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kismayo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Missing</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mogadishu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$N$8:$N$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2FCA-488C-BB5E-38EE7C9EA65C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1906634287"/>
+        <c:axId val="1906618895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1906634287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1906618895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1906618895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1906634287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Customer Demographic Data Analysis Data.xlsx]PivotTables!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Filters By City</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$L$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Customer_ID</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$K$34:$K$37</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>High</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Low</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Medium</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$L$34:$L$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>131</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-320E-4F01-B14B-128E60129C59}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$M$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average of Monthly_Income</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$K$34:$K$37</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>High</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Low</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Medium</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$M$34:$M$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2563.3863636363635</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>518.12446969696919</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1049.6853237410066</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-320E-4F01-B14B-128E60129C59}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1906192703"/>
+        <c:axId val="1906203519"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1906192703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1906203519"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1906203519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1906192703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2374,13 +6699,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>195263</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2394,6 +6719,96 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6864,10 +11279,23 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Occupation_Clean" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="8">
+        <s v="Business Owner"/>
+        <s v="Healthcare"/>
+        <s v="Engineer"/>
+        <s v="Civil Servant"/>
+        <s v="Student"/>
+        <s v="Teacher"/>
+        <s v="Self-Employed"/>
+        <s v="Missing"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Income_Level" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Medium"/>
+        <s v="Low"/>
+        <s v="High"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -6890,8 +11318,8 @@
     <x v="0"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00196"/>
@@ -6903,8 +11331,8 @@
     <x v="1"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00115"/>
@@ -6916,8 +11344,8 @@
     <x v="2"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00006"/>
@@ -6929,8 +11357,8 @@
     <x v="3"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00103"/>
@@ -6942,8 +11370,8 @@
     <x v="4"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00157"/>
@@ -6955,8 +11383,8 @@
     <x v="5"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00076"/>
@@ -6968,8 +11396,8 @@
     <x v="6"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00067"/>
@@ -6981,8 +11409,8 @@
     <x v="7"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00287"/>
@@ -6994,8 +11422,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Medium"/>
+    <x v="4"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00257"/>
@@ -7007,8 +11435,8 @@
     <x v="9"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00279"/>
@@ -7020,8 +11448,8 @@
     <x v="10"/>
     <s v="Missing"/>
     <s v="Garowe"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00270"/>
@@ -7033,8 +11461,8 @@
     <x v="11"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00005"/>
@@ -7046,8 +11474,8 @@
     <x v="12"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00186"/>
@@ -7059,8 +11487,8 @@
     <x v="13"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00252"/>
@@ -7072,8 +11500,8 @@
     <x v="14"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00030"/>
@@ -7085,8 +11513,8 @@
     <x v="15"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00235"/>
@@ -7098,8 +11526,8 @@
     <x v="16"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00052"/>
@@ -7111,8 +11539,8 @@
     <x v="17"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00058"/>
@@ -7124,8 +11552,8 @@
     <x v="18"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00181"/>
@@ -7137,8 +11565,8 @@
     <x v="19"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00206"/>
@@ -7150,8 +11578,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00230"/>
@@ -7163,8 +11591,8 @@
     <x v="20"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00025"/>
@@ -7176,8 +11604,8 @@
     <x v="21"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00211"/>
@@ -7189,8 +11617,8 @@
     <x v="22"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00207"/>
@@ -7202,8 +11630,8 @@
     <x v="23"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00203"/>
@@ -7215,8 +11643,8 @@
     <x v="24"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00202"/>
@@ -7228,8 +11656,8 @@
     <x v="25"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00223"/>
@@ -7241,8 +11669,8 @@
     <x v="26"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00231"/>
@@ -7254,8 +11682,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00292"/>
@@ -7267,8 +11695,8 @@
     <x v="27"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00156"/>
@@ -7280,8 +11708,8 @@
     <x v="28"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00072"/>
@@ -7293,8 +11721,8 @@
     <x v="29"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="High"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00173"/>
@@ -7306,8 +11734,8 @@
     <x v="30"/>
     <s v="Missing"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -7319,8 +11747,8 @@
     <x v="31"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00218"/>
@@ -7332,8 +11760,8 @@
     <x v="32"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00137"/>
@@ -7345,8 +11773,8 @@
     <x v="33"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00208"/>
@@ -7358,8 +11786,8 @@
     <x v="34"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00259"/>
@@ -7371,8 +11799,8 @@
     <x v="35"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Medium"/>
+    <x v="7"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00136"/>
@@ -7384,8 +11812,8 @@
     <x v="36"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00081"/>
@@ -7397,8 +11825,8 @@
     <x v="37"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00111"/>
@@ -7410,8 +11838,8 @@
     <x v="38"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00138"/>
@@ -7423,8 +11851,8 @@
     <x v="39"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00276"/>
@@ -7436,8 +11864,8 @@
     <x v="40"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00277"/>
@@ -7449,8 +11877,8 @@
     <x v="41"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="High"/>
+    <x v="6"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00080"/>
@@ -7462,8 +11890,8 @@
     <x v="42"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00124"/>
@@ -7475,8 +11903,8 @@
     <x v="43"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Medium"/>
+    <x v="7"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00249"/>
@@ -7488,8 +11916,8 @@
     <x v="44"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00097"/>
@@ -7501,8 +11929,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Medium"/>
+    <x v="4"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00247"/>
@@ -7514,8 +11942,8 @@
     <x v="45"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00169"/>
@@ -7527,8 +11955,8 @@
     <x v="46"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00271"/>
@@ -7540,8 +11968,8 @@
     <x v="47"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00049"/>
@@ -7553,8 +11981,8 @@
     <x v="48"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00234"/>
@@ -7566,8 +11994,8 @@
     <x v="49"/>
     <s v="Missing"/>
     <s v="Kismayo"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00132"/>
@@ -7579,8 +12007,8 @@
     <x v="50"/>
     <s v="Missing"/>
     <s v="Bosaso"/>
-    <s v="Healthcare"/>
-    <s v="High"/>
+    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00119"/>
@@ -7592,8 +12020,8 @@
     <x v="51"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00027"/>
@@ -7605,8 +12033,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00258"/>
@@ -7618,8 +12046,8 @@
     <x v="52"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00079"/>
@@ -7631,8 +12059,8 @@
     <x v="53"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00121"/>
@@ -7644,8 +12072,8 @@
     <x v="54"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00288"/>
@@ -7657,8 +12085,8 @@
     <x v="55"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00002"/>
@@ -7670,8 +12098,8 @@
     <x v="56"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00226"/>
@@ -7683,8 +12111,8 @@
     <x v="57"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00217"/>
@@ -7696,8 +12124,8 @@
     <x v="58"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -7709,8 +12137,8 @@
     <x v="59"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00146"/>
@@ -7722,8 +12150,8 @@
     <x v="60"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00133"/>
@@ -7735,8 +12163,8 @@
     <x v="61"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00109"/>
@@ -7748,8 +12176,8 @@
     <x v="62"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00246"/>
@@ -7761,8 +12189,8 @@
     <x v="63"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00261"/>
@@ -7774,8 +12202,8 @@
     <x v="64"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00149"/>
@@ -7787,8 +12215,8 @@
     <x v="65"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00227"/>
@@ -7800,8 +12228,8 @@
     <x v="66"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00262"/>
@@ -7813,8 +12241,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00245"/>
@@ -7826,8 +12254,8 @@
     <x v="67"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00091"/>
@@ -7839,8 +12267,8 @@
     <x v="68"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00017"/>
@@ -7852,8 +12280,8 @@
     <x v="69"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00187"/>
@@ -7865,8 +12293,8 @@
     <x v="70"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00128"/>
@@ -7878,8 +12306,8 @@
     <x v="71"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00134"/>
@@ -7891,8 +12319,8 @@
     <x v="72"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00012"/>
@@ -7904,8 +12332,8 @@
     <x v="73"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00166"/>
@@ -7917,8 +12345,8 @@
     <x v="74"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00224"/>
@@ -7930,8 +12358,8 @@
     <x v="75"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00241"/>
@@ -7943,8 +12371,8 @@
     <x v="76"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00021"/>
@@ -7956,8 +12384,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00239"/>
@@ -7969,8 +12397,8 @@
     <x v="77"/>
     <s v="Missing"/>
     <s v="Baidoa"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00222"/>
@@ -7982,8 +12410,8 @@
     <x v="78"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00197"/>
@@ -7995,8 +12423,8 @@
     <x v="79"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00083"/>
@@ -8008,8 +12436,8 @@
     <x v="80"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00273"/>
@@ -8021,8 +12449,8 @@
     <x v="81"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00219"/>
@@ -8034,8 +12462,8 @@
     <x v="82"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00048"/>
@@ -8047,8 +12475,8 @@
     <x v="83"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00003"/>
@@ -8060,8 +12488,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00272"/>
@@ -8073,8 +12501,8 @@
     <x v="84"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Missing"/>
-    <s v="Medium"/>
+    <x v="7"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00189"/>
@@ -8086,8 +12514,8 @@
     <x v="85"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00043"/>
@@ -8099,8 +12527,8 @@
     <x v="86"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00019"/>
@@ -8112,8 +12540,8 @@
     <x v="87"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00042"/>
@@ -8125,8 +12553,8 @@
     <x v="88"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00152"/>
@@ -8138,8 +12566,8 @@
     <x v="89"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00214"/>
@@ -8151,8 +12579,8 @@
     <x v="90"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00183"/>
@@ -8164,8 +12592,8 @@
     <x v="91"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00150"/>
@@ -8177,8 +12605,8 @@
     <x v="92"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00004"/>
@@ -8190,8 +12618,8 @@
     <x v="93"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00286"/>
@@ -8203,8 +12631,8 @@
     <x v="94"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00135"/>
@@ -8216,8 +12644,8 @@
     <x v="95"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00254"/>
@@ -8229,8 +12657,8 @@
     <x v="96"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00100"/>
@@ -8242,8 +12670,8 @@
     <x v="97"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00060"/>
@@ -8255,8 +12683,8 @@
     <x v="98"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00078"/>
@@ -8268,8 +12696,8 @@
     <x v="99"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00154"/>
@@ -8281,8 +12709,8 @@
     <x v="100"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00175"/>
@@ -8294,8 +12722,8 @@
     <x v="101"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00140"/>
@@ -8307,8 +12735,8 @@
     <x v="102"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00210"/>
@@ -8320,8 +12748,8 @@
     <x v="103"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00007"/>
@@ -8333,8 +12761,8 @@
     <x v="104"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00065"/>
@@ -8346,8 +12774,8 @@
     <x v="105"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00106"/>
@@ -8359,8 +12787,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00228"/>
@@ -8372,8 +12800,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00194"/>
@@ -8385,8 +12813,8 @@
     <x v="106"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00131"/>
@@ -8398,8 +12826,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Medium"/>
+    <x v="4"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -8411,8 +12839,8 @@
     <x v="107"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00160"/>
@@ -8424,8 +12852,8 @@
     <x v="108"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00053"/>
@@ -8437,8 +12865,8 @@
     <x v="109"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00102"/>
@@ -8450,8 +12878,8 @@
     <x v="110"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00180"/>
@@ -8463,8 +12891,8 @@
     <x v="111"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00255"/>
@@ -8476,8 +12904,8 @@
     <x v="112"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00221"/>
@@ -8489,8 +12917,8 @@
     <x v="113"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00268"/>
@@ -8502,8 +12930,8 @@
     <x v="114"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="High"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00275"/>
@@ -8515,8 +12943,8 @@
     <x v="115"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00122"/>
@@ -8528,8 +12956,8 @@
     <x v="116"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00118"/>
@@ -8541,8 +12969,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Student"/>
-    <s v="Medium"/>
+    <x v="4"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00182"/>
@@ -8554,8 +12982,8 @@
     <x v="117"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00237"/>
@@ -8567,8 +12995,8 @@
     <x v="118"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00171"/>
@@ -8580,8 +13008,8 @@
     <x v="119"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00209"/>
@@ -8593,8 +13021,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00143"/>
@@ -8606,8 +13034,8 @@
     <x v="120"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00056"/>
@@ -8619,8 +13047,8 @@
     <x v="121"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00285"/>
@@ -8632,8 +13060,8 @@
     <x v="122"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00229"/>
@@ -8645,8 +13073,8 @@
     <x v="123"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Medium"/>
+    <x v="7"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -8658,8 +13086,8 @@
     <x v="124"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00063"/>
@@ -8671,8 +13099,8 @@
     <x v="125"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00213"/>
@@ -8684,8 +13112,8 @@
     <x v="126"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00112"/>
@@ -8697,8 +13125,8 @@
     <x v="127"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00216"/>
@@ -8710,8 +13138,8 @@
     <x v="128"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00164"/>
@@ -8723,8 +13151,8 @@
     <x v="129"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00040"/>
@@ -8736,8 +13164,8 @@
     <x v="130"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00232"/>
@@ -8749,8 +13177,8 @@
     <x v="131"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00123"/>
@@ -8762,8 +13190,8 @@
     <x v="132"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00264"/>
@@ -8775,8 +13203,8 @@
     <x v="133"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Medium"/>
+    <x v="7"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00198"/>
@@ -8788,8 +13216,8 @@
     <x v="134"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00033"/>
@@ -8801,8 +13229,8 @@
     <x v="135"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00139"/>
@@ -8814,8 +13242,8 @@
     <x v="136"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00077"/>
@@ -8827,8 +13255,8 @@
     <x v="137"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00153"/>
@@ -8840,8 +13268,8 @@
     <x v="138"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00144"/>
@@ -8853,8 +13281,8 @@
     <x v="139"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00069"/>
@@ -8866,8 +13294,8 @@
     <x v="140"/>
     <s v="Missing"/>
     <s v="Bosaso"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00086"/>
@@ -8879,8 +13307,8 @@
     <x v="141"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -8892,8 +13320,8 @@
     <x v="142"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00256"/>
@@ -8905,8 +13333,8 @@
     <x v="143"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00088"/>
@@ -8918,8 +13346,8 @@
     <x v="144"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00026"/>
@@ -8931,8 +13359,8 @@
     <x v="145"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00282"/>
@@ -8944,8 +13372,8 @@
     <x v="146"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -8957,8 +13385,8 @@
     <x v="147"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00114"/>
@@ -8970,8 +13398,8 @@
     <x v="148"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00051"/>
@@ -8983,8 +13411,8 @@
     <x v="149"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00089"/>
@@ -8996,8 +13424,8 @@
     <x v="150"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00242"/>
@@ -9009,8 +13437,8 @@
     <x v="151"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00105"/>
@@ -9022,8 +13450,8 @@
     <x v="152"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00172"/>
@@ -9035,8 +13463,8 @@
     <x v="153"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00161"/>
@@ -9048,8 +13476,8 @@
     <x v="154"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00225"/>
@@ -9061,8 +13489,8 @@
     <x v="155"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00028"/>
@@ -9074,8 +13502,8 @@
     <x v="156"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00126"/>
@@ -9087,8 +13515,8 @@
     <x v="157"/>
     <s v="Missing"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -9100,8 +13528,8 @@
     <x v="158"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00125"/>
@@ -9113,8 +13541,8 @@
     <x v="159"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00110"/>
@@ -9126,8 +13554,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00001"/>
@@ -9139,8 +13567,8 @@
     <x v="160"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00289"/>
@@ -9152,8 +13580,8 @@
     <x v="161"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00274"/>
@@ -9165,8 +13593,8 @@
     <x v="162"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00167"/>
@@ -9178,8 +13606,8 @@
     <x v="163"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00260"/>
@@ -9191,8 +13619,8 @@
     <x v="164"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00047"/>
@@ -9204,8 +13632,8 @@
     <x v="165"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00094"/>
@@ -9217,8 +13645,8 @@
     <x v="166"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00195"/>
@@ -9230,8 +13658,8 @@
     <x v="167"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00184"/>
@@ -9243,8 +13671,8 @@
     <x v="168"/>
     <s v="Missing"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00107"/>
@@ -9256,8 +13684,8 @@
     <x v="169"/>
     <s v="Male"/>
     <s v="Missing"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00010"/>
@@ -9269,8 +13697,8 @@
     <x v="170"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Low"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00008"/>
@@ -9282,8 +13710,8 @@
     <x v="171"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00045"/>
@@ -9295,8 +13723,8 @@
     <x v="172"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00046"/>
@@ -9308,8 +13736,8 @@
     <x v="173"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00116"/>
@@ -9321,8 +13749,8 @@
     <x v="174"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00266"/>
@@ -9334,8 +13762,8 @@
     <x v="175"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00016"/>
@@ -9347,8 +13775,8 @@
     <x v="176"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00035"/>
@@ -9360,8 +13788,8 @@
     <x v="177"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00269"/>
@@ -9373,8 +13801,8 @@
     <x v="178"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00141"/>
@@ -9386,8 +13814,8 @@
     <x v="179"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00087"/>
@@ -9399,8 +13827,8 @@
     <x v="180"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00200"/>
@@ -9412,8 +13840,8 @@
     <x v="181"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00054"/>
@@ -9425,8 +13853,8 @@
     <x v="182"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -9438,8 +13866,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00165"/>
@@ -9451,8 +13879,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Medium"/>
+    <x v="4"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00095"/>
@@ -9464,8 +13892,8 @@
     <x v="183"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00284"/>
@@ -9477,8 +13905,8 @@
     <x v="184"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00098"/>
@@ -9490,8 +13918,8 @@
     <x v="185"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00014"/>
@@ -9503,8 +13931,8 @@
     <x v="186"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00283"/>
@@ -9516,8 +13944,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00062"/>
@@ -9529,8 +13957,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00147"/>
@@ -9542,8 +13970,8 @@
     <x v="187"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Low"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00191"/>
@@ -9555,8 +13983,8 @@
     <x v="188"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -9568,8 +13996,8 @@
     <x v="189"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00096"/>
@@ -9581,8 +14009,8 @@
     <x v="190"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00073"/>
@@ -9594,8 +14022,8 @@
     <x v="191"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00248"/>
@@ -9607,8 +14035,8 @@
     <x v="192"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00240"/>
@@ -9620,8 +14048,8 @@
     <x v="193"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00236"/>
@@ -9633,8 +14061,8 @@
     <x v="194"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00190"/>
@@ -9646,8 +14074,8 @@
     <x v="195"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00201"/>
@@ -9659,8 +14087,8 @@
     <x v="196"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00188"/>
@@ -9672,8 +14100,8 @@
     <x v="197"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00029"/>
@@ -9685,8 +14113,8 @@
     <x v="198"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00220"/>
@@ -9698,8 +14126,8 @@
     <x v="199"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00085"/>
@@ -9711,8 +14139,8 @@
     <x v="200"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00023"/>
@@ -9724,8 +14152,8 @@
     <x v="201"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00185"/>
@@ -9737,8 +14165,8 @@
     <x v="202"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00013"/>
@@ -9750,8 +14178,8 @@
     <x v="203"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00108"/>
@@ -9763,8 +14191,8 @@
     <x v="204"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00162"/>
@@ -9776,8 +14204,8 @@
     <x v="205"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00104"/>
@@ -9789,8 +14217,8 @@
     <x v="206"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00018"/>
@@ -9802,8 +14230,8 @@
     <x v="207"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00068"/>
@@ -9815,8 +14243,8 @@
     <x v="208"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00064"/>
@@ -9828,8 +14256,8 @@
     <x v="209"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00278"/>
@@ -9841,8 +14269,8 @@
     <x v="210"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Low"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00039"/>
@@ -9854,8 +14282,8 @@
     <x v="211"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00168"/>
@@ -9867,8 +14295,8 @@
     <x v="212"/>
     <s v="Female"/>
     <s v="Missing"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00142"/>
@@ -9880,8 +14308,8 @@
     <x v="213"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00015"/>
@@ -9893,8 +14321,8 @@
     <x v="214"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00024"/>
@@ -9906,8 +14334,8 @@
     <x v="215"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00127"/>
@@ -9919,8 +14347,8 @@
     <x v="216"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00145"/>
@@ -9932,8 +14360,8 @@
     <x v="217"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00243"/>
@@ -9945,8 +14373,8 @@
     <x v="218"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00032"/>
@@ -9958,8 +14386,8 @@
     <x v="219"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00050"/>
@@ -9971,8 +14399,8 @@
     <x v="220"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00267"/>
@@ -9984,8 +14412,8 @@
     <x v="221"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00066"/>
@@ -9997,8 +14425,8 @@
     <x v="222"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00253"/>
@@ -10010,8 +14438,8 @@
     <x v="223"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -10023,8 +14451,8 @@
     <x v="224"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00059"/>
@@ -10036,8 +14464,8 @@
     <x v="8"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00074"/>
@@ -10049,8 +14477,8 @@
     <x v="225"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="Low"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00037"/>
@@ -10062,8 +14490,8 @@
     <x v="226"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00041"/>
@@ -10075,8 +14503,8 @@
     <x v="227"/>
     <s v="Missing"/>
     <s v="Baidoa"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00082"/>
@@ -10088,8 +14516,8 @@
     <x v="228"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00155"/>
@@ -10101,8 +14529,8 @@
     <x v="229"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00233"/>
@@ -10114,8 +14542,8 @@
     <x v="230"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00061"/>
@@ -10127,8 +14555,8 @@
     <x v="8"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00250"/>
@@ -10140,8 +14568,8 @@
     <x v="231"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00092"/>
@@ -10153,8 +14581,8 @@
     <x v="232"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00192"/>
@@ -10166,8 +14594,8 @@
     <x v="233"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00290"/>
@@ -10179,8 +14607,8 @@
     <x v="234"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Missing"/>
-    <s v="Low"/>
+    <x v="7"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00281"/>
@@ -10192,8 +14620,8 @@
     <x v="235"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00176"/>
@@ -10205,8 +14633,8 @@
     <x v="236"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00129"/>
@@ -10218,8 +14646,8 @@
     <x v="237"/>
     <s v="Missing"/>
     <s v="Kismayo"/>
-    <s v="Self-Employed"/>
-    <s v="Medium"/>
+    <x v="6"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00199"/>
@@ -10231,8 +14659,8 @@
     <x v="238"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Low"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00238"/>
@@ -10244,8 +14672,8 @@
     <x v="239"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00280"/>
@@ -10257,8 +14685,8 @@
     <x v="240"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00212"/>
@@ -10270,8 +14698,8 @@
     <x v="241"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00178"/>
@@ -10283,8 +14711,8 @@
     <x v="242"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00075"/>
@@ -10296,8 +14724,8 @@
     <x v="243"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00070"/>
@@ -10309,8 +14737,8 @@
     <x v="244"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00093"/>
@@ -10322,8 +14750,8 @@
     <x v="245"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00193"/>
@@ -10335,8 +14763,8 @@
     <x v="246"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <m/>
@@ -10348,8 +14776,8 @@
     <x v="247"/>
     <s v="Female"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00036"/>
@@ -10361,8 +14789,8 @@
     <x v="248"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -10374,8 +14802,8 @@
     <x v="249"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00163"/>
@@ -10387,8 +14815,8 @@
     <x v="250"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00291"/>
@@ -10400,8 +14828,8 @@
     <x v="251"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Engineer"/>
-    <s v="Medium"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00084"/>
@@ -10413,8 +14841,8 @@
     <x v="252"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00011"/>
@@ -10426,8 +14854,8 @@
     <x v="253"/>
     <s v="Missing"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00158"/>
@@ -10439,8 +14867,8 @@
     <x v="254"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00031"/>
@@ -10452,8 +14880,8 @@
     <x v="255"/>
     <s v="Female"/>
     <s v="Baidoa"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00215"/>
@@ -10465,8 +14893,8 @@
     <x v="256"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00265"/>
@@ -10478,8 +14906,8 @@
     <x v="257"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Medium"/>
+    <x v="3"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00090"/>
@@ -10491,8 +14919,8 @@
     <x v="258"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00034"/>
@@ -10504,8 +14932,8 @@
     <x v="259"/>
     <s v="Male"/>
     <s v="Baidoa"/>
-    <s v="Teacher"/>
-    <s v="Medium"/>
+    <x v="5"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00205"/>
@@ -10517,8 +14945,8 @@
     <x v="260"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Self-Employed"/>
-    <s v="Low"/>
+    <x v="6"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00049"/>
@@ -10530,8 +14958,8 @@
     <x v="48"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00055"/>
@@ -10543,8 +14971,8 @@
     <x v="261"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Healthcare"/>
-    <s v="Medium"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00057"/>
@@ -10556,8 +14984,8 @@
     <x v="262"/>
     <s v="Male"/>
     <s v="Kismayo"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00071"/>
@@ -10569,8 +14997,8 @@
     <x v="263"/>
     <s v="Female"/>
     <s v="Garowe"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -10582,8 +15010,8 @@
     <x v="264"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Business Owner"/>
-    <s v="High"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00020"/>
@@ -10595,8 +15023,8 @@
     <x v="265"/>
     <s v="Female"/>
     <s v="Bosaso"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00130"/>
@@ -10608,8 +15036,8 @@
     <x v="266"/>
     <s v="Female"/>
     <s v="Kismayo"/>
-    <s v="Engineer"/>
-    <s v="High"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="CUS00022"/>
@@ -10621,8 +15049,8 @@
     <x v="267"/>
     <s v="Female"/>
     <s v="Mogadishu"/>
-    <s v="Civil Servant"/>
-    <s v="Low"/>
+    <x v="3"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00174"/>
@@ -10634,8 +15062,8 @@
     <x v="268"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Teacher"/>
-    <s v="Low"/>
+    <x v="5"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00177"/>
@@ -10647,8 +15075,8 @@
     <x v="269"/>
     <s v="Male"/>
     <s v="Mogadishu"/>
-    <s v="Healthcare"/>
-    <s v="Low"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -10660,8 +15088,8 @@
     <x v="270"/>
     <s v="Male"/>
     <s v="Hargeisa"/>
-    <s v="Student"/>
-    <s v="Low"/>
+    <x v="4"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="CUS00099"/>
@@ -10673,8 +15101,8 @@
     <x v="271"/>
     <s v="Male"/>
     <s v="Bosaso"/>
-    <s v="Business Owner"/>
-    <s v="Medium"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="CUS00170"/>
@@ -10686,14 +15114,355 @@
     <x v="272"/>
     <s v="Male"/>
     <s v="Garowe"/>
-    <s v="Engineer"/>
-    <s v="Low"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="K33:M37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of Monthly_Income" fld="6" subtotal="average" baseField="10" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A27:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="K6:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A5:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -11049,8 +15818,19 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="4" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -29426,6 +34206,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"Low"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+      <formula>"Low"</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -29448,20 +34240,18 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>"Low"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"Low"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"High"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Medium"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
@@ -29473,16 +34263,6 @@
           <x14:id>{11A4E547-5A7A-44F7-9AAB-C31D35F57467}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
@@ -29500,6 +34280,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="iconSet" priority="12">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -29510,16 +34297,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="iconSet" priority="12">
-      <iconSet iconSet="3Arrows">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29828,7 +34608,7 @@
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46250.679481944448</v>
+        <v>46250.705280555558</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>354</v>
@@ -29901,93 +34681,376 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:B13"/>
+  <dimension ref="A5:O37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="186" width="7.5703125" customWidth="1"/>
+    <col min="6" max="10" width="7.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="16" max="186" width="7.5703125" customWidth="1"/>
     <col min="273" max="274" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="275" max="275" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:15">
       <c r="A5" s="19" t="s">
         <v>365</v>
       </c>
       <c r="B5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="20">
         <v>19068.93</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="K6" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="20">
         <v>39854.100000000006</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="K7" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B8" s="20">
         <v>17991.009999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="K8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="20">
+        <v>12</v>
+      </c>
+      <c r="M8" s="20">
+        <v>9</v>
+      </c>
+      <c r="N8" s="20">
+        <v>3</v>
+      </c>
+      <c r="O8" s="20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="20">
         <v>38385.03</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="K9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="20">
+        <v>16</v>
+      </c>
+      <c r="M9" s="20">
+        <v>16</v>
+      </c>
+      <c r="N9" s="20">
+        <v>3</v>
+      </c>
+      <c r="O9" s="20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="20">
         <v>30250.91</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="K10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="20">
+        <v>10</v>
+      </c>
+      <c r="M10" s="20">
+        <v>10</v>
+      </c>
+      <c r="N10" s="20">
+        <v>1</v>
+      </c>
+      <c r="O10" s="20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="6" t="s">
         <v>312</v>
       </c>
       <c r="B11" s="20">
         <v>13639.55</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="K11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="20">
+        <v>23</v>
+      </c>
+      <c r="M11" s="20">
+        <v>19</v>
+      </c>
+      <c r="N11" s="20">
+        <v>1</v>
+      </c>
+      <c r="O11" s="20">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="20">
         <v>111503.65999999997</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="K12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="20">
+        <v>14</v>
+      </c>
+      <c r="M12" s="20">
+        <v>19</v>
+      </c>
+      <c r="N12" s="20">
+        <v>2</v>
+      </c>
+      <c r="O12" s="20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="6" t="s">
         <v>366</v>
       </c>
       <c r="B13" s="20">
         <v>270693.18999999994</v>
       </c>
+      <c r="K13" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="L13" s="20">
+        <v>10</v>
+      </c>
+      <c r="M13" s="20">
+        <v>6</v>
+      </c>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="K14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="20">
+        <v>53</v>
+      </c>
+      <c r="M14" s="20">
+        <v>45</v>
+      </c>
+      <c r="N14" s="20">
+        <v>7</v>
+      </c>
+      <c r="O14" s="20">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="K15" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="L15" s="20">
+        <v>138</v>
+      </c>
+      <c r="M15" s="20">
+        <v>124</v>
+      </c>
+      <c r="N15" s="20">
+        <v>17</v>
+      </c>
+      <c r="O15" s="20">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="20">
+        <v>63062.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="20">
+        <v>30275.03000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="20">
+        <v>43298.039999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="20">
+        <v>41695.880000000005</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L31" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" s="20">
+        <v>9200.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="20">
+        <v>42372.009999999995</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="L33" t="s">
+        <v>372</v>
+      </c>
+      <c r="M33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="20">
+        <v>11241.05</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="L34" s="20">
+        <v>20</v>
+      </c>
+      <c r="M34" s="20">
+        <v>2563.3863636363635</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="20">
+        <v>29549.109999999993</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="L35" s="20">
+        <v>128</v>
+      </c>
+      <c r="M35" s="20">
+        <v>518.12446969696919</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B36" s="20">
+        <v>270693.19</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="L36" s="20">
+        <v>131</v>
+      </c>
+      <c r="M36" s="20">
+        <v>1049.6853237410066</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="K37" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="L37" s="20">
+        <v>279</v>
+      </c>
+      <c r="M37" s="20">
+        <v>923.86754266211562</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -3928,7 +3928,7 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>Filters By City</a:t>
+              <a:t>Income Level by City — Customer Count &amp; Average Income</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -6789,11 +6789,11 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>89647</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Deero DS Course\Practical Excel Data Analytics Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="375">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -1494,7 +1494,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1532,9 +1531,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2167,9 +2164,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2220,9 +2215,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2273,9 +2266,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2326,9 +2317,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2379,9 +2368,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2432,9 +2419,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2485,9 +2470,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2538,9 +2521,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2591,9 +2572,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -4555,6 +4534,415 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Customer Demographic Data Analysis Data.xlsx]PivotTables!PivotTable1</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Gender distribution</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTables!$U$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTables!$T$6:$T$9</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Female</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Male</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Missing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTables!$U$6:$U$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>125509.16000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120191.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24992.530000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C5EA-46A9-8762-3FB99EFEF823}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
@@ -4639,6 +5027,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6692,6 +7120,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6809,6 +7756,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22409</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>96370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>347381</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15121,41 +16098,30 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="K33:M37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="T5:U9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
         <item x="0"/>
         <item x="1"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="10"/>
+    <field x="2"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -15171,23 +16137,11 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Average of Monthly_Income" fld="6" subtotal="average" baseField="10" baseItem="0"/>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
@@ -15199,11 +16153,11 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
+    <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -15219,7 +16173,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A27:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -15325,7 +16279,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="K6:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -15414,44 +16368,6 @@
   <dataFields count="1">
     <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -15462,7 +16378,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A5:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -15840,6 +16756,104 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="K33:M37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of Monthly_Income" fld="6" subtotal="average" baseField="10" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -22875,7 +23889,7 @@
         <v>Healthcare</v>
       </c>
       <c r="K3" s="6" t="str">
-        <f t="shared" ref="K2:K65" si="3">IF(G3&gt;=1500,"High",IF(G3&gt;=800,"Medium","Low"))</f>
+        <f t="shared" ref="K3:K65" si="3">IF(G3&gt;=1500,"High",IF(G3&gt;=800,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
@@ -34596,7 +35610,7 @@
       </c>
       <c r="B33" s="14">
         <f ca="1">TODAY()</f>
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>352</v>
@@ -34608,7 +35622,7 @@
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46250.705280555558</v>
+        <v>46251.511161921298</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>354</v>
@@ -34668,7 +35682,7 @@
       </c>
       <c r="B39" s="6">
         <f ca="1">NETWORKDAYS('[2]Clean_Data '!B2,TODAY())</f>
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>364</v>
@@ -34681,7 +35695,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:O37"/>
+  <dimension ref="A5:U37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -34695,20 +35709,29 @@
     <col min="13" max="13" width="26.7109375" customWidth="1"/>
     <col min="14" max="14" width="7.85546875" customWidth="1"/>
     <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="186" width="7.5703125" customWidth="1"/>
+    <col min="16" max="19" width="7.5703125" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="23.140625" customWidth="1"/>
+    <col min="22" max="186" width="7.5703125" customWidth="1"/>
     <col min="273" max="274" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="275" max="275" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:21">
       <c r="A5" s="19" t="s">
         <v>365</v>
       </c>
       <c r="B5" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="T5" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="U5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -34721,8 +35744,14 @@
       <c r="L6" s="19" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="T6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="20">
+        <v>125509.16000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -34744,8 +35773,14 @@
       <c r="O7" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="T7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="U7" s="20">
+        <v>120191.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="6" t="s">
         <v>74</v>
       </c>
@@ -34767,8 +35802,14 @@
       <c r="O8" s="20">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="T8" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="U8" s="20">
+        <v>24992.530000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
@@ -34790,8 +35831,14 @@
       <c r="O9" s="20">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="T9" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="U9" s="20">
+        <v>270693.19000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
@@ -34814,7 +35861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:21">
       <c r="A11" s="6" t="s">
         <v>312</v>
       </c>
@@ -34837,7 +35884,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:21">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
@@ -34860,7 +35907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:21">
       <c r="A13" s="6" t="s">
         <v>366</v>
       </c>
@@ -34881,7 +35928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:21">
       <c r="K14" s="6" t="s">
         <v>9</v>
       </c>
@@ -34898,7 +35945,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:21">
       <c r="K15" s="6" t="s">
         <v>366</v>
       </c>
@@ -35050,7 +36097,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
+++ b/Practical Excel Data Analytics Project/Customer Demographic Data Analysis Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -2214,7 +2214,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2262,7 +2261,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2300,9 +2298,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2377,7 +2373,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -2625,7 +2620,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8164,6 +8158,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8325,6 +8320,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -8362,7 +8358,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -8437,6 +8435,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -8657,6 +8656,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9068,6 +9068,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -9105,7 +9106,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -9293,7 +9296,9 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -9359,6 +9364,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9488,6 +9494,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9649,6 +9656,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -9686,7 +9694,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -9761,6 +9771,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -10008,6 +10019,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10959,6 +10971,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11100,6 +11113,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -11137,7 +11151,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -11212,6 +11228,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
@@ -14176,7 +14193,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14224,7 +14240,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -14262,9 +14277,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -14339,7 +14352,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -14560,7 +14572,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14812,7 +14823,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -14850,9 +14860,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -15030,9 +15038,7 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -15098,7 +15104,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -28483,372 +28488,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A91:B100" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="V37:W51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A15:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Monthly_Income" fld="6" baseField="4" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A37:B46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -29052,457 +28691,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="M17:Q26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="1" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="V16:W20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="M42:O47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Average of Monthly_Income" fld="6" subtotal="average" baseField="10" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A58:B62" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -29640,7 +28829,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="U92:V106" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -29836,7 +29025,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="L91:M95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -30012,6 +29201,822 @@
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
   </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="M17:Q26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="V37:W51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="V16:W20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="M42:O47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of Monthly_Income" fld="6" subtotal="average" baseField="10" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A91:B100" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A15:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly_Income" fld="6" baseField="4" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
 </file>
 
@@ -51212,7 +51217,7 @@
       </c>
       <c r="B33" s="14">
         <f ca="1">TODAY()</f>
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>351</v>
@@ -51224,7 +51229,7 @@
       </c>
       <c r="B34" s="15">
         <f ca="1">NOW()</f>
-        <v>46257.685527546295</v>
+        <v>46258.574520833332</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>353</v>
@@ -51284,7 +51289,7 @@
       </c>
       <c r="B39" s="6">
         <f ca="1">NETWORKDAYS('[1]Clean_Data '!B2,TODAY())</f>
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>363</v>
@@ -54048,7 +54053,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" ht="30">
       <c r="A45" s="30" t="s">
         <v>413</v>
       </c>
